--- a/public/data/stem/Datos_monitor_stem.xlsx
+++ b/public/data/stem/Datos_monitor_stem.xlsx
@@ -5,23 +5,25 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\End User\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\End User\Desktop\Comunicado STEM\Monitor_Comunicado_STEM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84DA0439-47E5-4B1A-8F78-BF2AE9E5E489}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81A7B2CA-2610-4E5B-8BF6-BCC613887F43}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="5" xr2:uid="{C147F3D5-0D56-471B-BD30-6AEC8CB769A6}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="902" xr2:uid="{C147F3D5-0D56-471B-BD30-6AEC8CB769A6}"/>
   </bookViews>
   <sheets>
-    <sheet name="PISA" sheetId="2" r:id="rId1"/>
-    <sheet name="Matematicas" sheetId="1" r:id="rId2"/>
-    <sheet name="Áreas" sheetId="3" r:id="rId3"/>
-    <sheet name="Mapa_matrícula" sheetId="4" r:id="rId4"/>
-    <sheet name="Mapa_profesionistas" sheetId="5" r:id="rId5"/>
-    <sheet name="Mercado_laboral" sheetId="6" r:id="rId6"/>
+    <sheet name="Portada" sheetId="7" r:id="rId1"/>
+    <sheet name="PISA_general" sheetId="2" r:id="rId2"/>
+    <sheet name="PISA_matematicas" sheetId="1" r:id="rId3"/>
+    <sheet name="Matrícula_áreas" sheetId="3" r:id="rId4"/>
+    <sheet name="Mapa_matrícula" sheetId="4" r:id="rId5"/>
+    <sheet name="Mapa_profesionistas" sheetId="5" r:id="rId6"/>
+    <sheet name="Mercado_laboral" sheetId="6" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">Mapa_profesionistas!$A$1:$D$33</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">Mapa_matrícula!$A$2:$D$34</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">Mapa_profesionistas!$A$2:$D$34</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -136,126 +138,126 @@
     <bk>
       <extLst>
         <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="163"/>
+          <xlrd:rvb i="162"/>
         </ext>
       </extLst>
     </bk>
     <bk>
       <extLst>
         <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="176"/>
+          <xlrd:rvb i="177"/>
         </ext>
       </extLst>
     </bk>
     <bk>
       <extLst>
         <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="189"/>
+          <xlrd:rvb i="191"/>
         </ext>
       </extLst>
     </bk>
     <bk>
       <extLst>
         <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="267"/>
+          <xlrd:rvb i="204"/>
         </ext>
       </extLst>
     </bk>
     <bk>
       <extLst>
         <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="280"/>
+          <xlrd:rvb i="282"/>
         </ext>
       </extLst>
     </bk>
     <bk>
       <extLst>
         <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="293"/>
+          <xlrd:rvb i="295"/>
         </ext>
       </extLst>
     </bk>
     <bk>
       <extLst>
         <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="306"/>
+          <xlrd:rvb i="308"/>
         </ext>
       </extLst>
     </bk>
     <bk>
       <extLst>
         <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="319"/>
+          <xlrd:rvb i="321"/>
         </ext>
       </extLst>
     </bk>
     <bk>
       <extLst>
         <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="332"/>
+          <xlrd:rvb i="334"/>
         </ext>
       </extLst>
     </bk>
     <bk>
       <extLst>
         <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="345"/>
+          <xlrd:rvb i="347"/>
         </ext>
       </extLst>
     </bk>
     <bk>
       <extLst>
         <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="358"/>
+          <xlrd:rvb i="360"/>
         </ext>
       </extLst>
     </bk>
     <bk>
       <extLst>
         <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="369"/>
+          <xlrd:rvb i="373"/>
         </ext>
       </extLst>
     </bk>
     <bk>
       <extLst>
         <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="382"/>
+          <xlrd:rvb i="384"/>
         </ext>
       </extLst>
     </bk>
     <bk>
       <extLst>
         <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="395"/>
+          <xlrd:rvb i="397"/>
         </ext>
       </extLst>
     </bk>
     <bk>
       <extLst>
         <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="408"/>
+          <xlrd:rvb i="410"/>
         </ext>
       </extLst>
     </bk>
     <bk>
       <extLst>
         <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="421"/>
+          <xlrd:rvb i="423"/>
         </ext>
       </extLst>
     </bk>
     <bk>
       <extLst>
         <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="435"/>
+          <xlrd:rvb i="436"/>
         </ext>
       </extLst>
     </bk>
     <bk>
       <extLst>
         <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="449"/>
+          <xlrd:rvb i="450"/>
         </ext>
       </extLst>
     </bk>
@@ -376,7 +378,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="53">
   <si>
     <t>Hombres</t>
   </si>
@@ -411,31 +413,10 @@
     <t>Educación</t>
   </si>
   <si>
-    <t>Ciencias De La Salud</t>
-  </si>
-  <si>
-    <t>Ciencias Sociales Y Derecho</t>
-  </si>
-  <si>
     <t>Artes Y Humanidades</t>
   </si>
   <si>
-    <t>Administración Y Negocios</t>
-  </si>
-  <si>
     <t>Servicios</t>
-  </si>
-  <si>
-    <t>Ciencias Naturales, Matemáticas Y Estadística</t>
-  </si>
-  <si>
-    <t>Agronomía Y Veterinaria</t>
-  </si>
-  <si>
-    <t>Ingeniería, Manufactura Y Construcción</t>
-  </si>
-  <si>
-    <t>Tecnologías De La Información</t>
   </si>
   <si>
     <t>Proporción</t>
@@ -479,15 +460,97 @@
   <si>
     <t>Total profesionistas</t>
   </si>
+  <si>
+    <t>Monitor Mujeres en la economía en México - Mujeres en STEM</t>
+  </si>
+  <si>
+    <t>Ciencias de la salud</t>
+  </si>
+  <si>
+    <t>Ciencias sociales y  derecho</t>
+  </si>
+  <si>
+    <t>Administración y negocios</t>
+  </si>
+  <si>
+    <t>Ciencias naturales, matemáticas y estadística</t>
+  </si>
+  <si>
+    <t>Agronomía y veterinaria</t>
+  </si>
+  <si>
+    <t>Ingeniería, manufactura y construcción</t>
+  </si>
+  <si>
+    <t>Tecnologías de la información</t>
+  </si>
+  <si>
+    <t>Fuente: Elaborado por el IMCO con datos de PISA.</t>
+  </si>
+  <si>
+    <t>Fuente: Elaborado por el IMCO con datos de PISA.2022</t>
+  </si>
+  <si>
+    <t>Fuente: Elaborado por el IMCO con datos de los anuarios estadísticos de la ANUIES para el ciclo escolar 2024-2025</t>
+  </si>
+  <si>
+    <t>Fuente: Elaborado por el IMCO con datos de la ENOE al 3T de 2025 del INEGI.</t>
+  </si>
+  <si>
+    <t>Histórico de puntajes obtenidos por México en pruebas PISA entre 2003 y 2022</t>
+  </si>
+  <si>
+    <t>Nivel de desempeño en pruebas PISA 2022 en matemáticas por sexo</t>
+  </si>
+  <si>
+    <t>Distribución de matrícula de licenciatura entre hombres y mujeres por área de estudio</t>
+  </si>
+  <si>
+    <t>Categoría</t>
+  </si>
+  <si>
+    <t>Proporción de mujeres que estudian una carrera STEM respecto al total de alumnas de licenciatura del estado</t>
+  </si>
+  <si>
+    <t>Proporción de profesionistas STEM respecto al total de profesionistas mujeres por estado</t>
+  </si>
+  <si>
+    <t>regresar al incio</t>
+  </si>
+  <si>
+    <t>PISA_general</t>
+  </si>
+  <si>
+    <t>PISA_matematicas</t>
+  </si>
+  <si>
+    <t>Matrícula_áreas</t>
+  </si>
+  <si>
+    <t>Mapa_matrícula</t>
+  </si>
+  <si>
+    <t>Mapa_profesionistas</t>
+  </si>
+  <si>
+    <t>Mercado_laboral</t>
+  </si>
+  <si>
+    <t>Hoja</t>
+  </si>
+  <si>
+    <t>Descripción</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="0.0%"/>
+    <numFmt numFmtId="170" formatCode="&quot;$&quot;#,##0.00"/>
   </numFmts>
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="12" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -504,30 +567,87 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF111111"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="28"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="0"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
     <font>
+      <b/>
+      <sz val="14"/>
+      <color theme="0"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
       <sz val="12"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
+      <color theme="0"/>
+      <name val="Arial"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="2"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <sz val="12"/>
       <color theme="1"/>
-      <name val="Arial"/>
+      <name val="Aptos Narrow"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF111111"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="2">
@@ -558,30 +678,52 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="170" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="centerContinuous"/>
+    </xf>
+    <xf numFmtId="170" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="centerContinuous"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
@@ -598,6 +740,72 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>952500</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>94780</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>1273</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Imagen 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{87EEA62B-0BE1-4BCF-B90A-50BF0DC64DAF}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill rotWithShape="1">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect l="6735" t="28142" r="8829" b="34884"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="3329940" y="0"/>
+          <a:ext cx="5901220" cy="2561593"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/richData/rdRichValueTypes.xml><?xml version="1.0" encoding="utf-8"?>
@@ -967,47 +1175,40 @@
     <v t="r">145</v>
   </a>
   <a r="4">
+    <v t="r">155</v>
     <v t="r">156</v>
     <v t="r">157</v>
     <v t="r">158</v>
-    <v t="r">159</v>
   </a>
-  <a r="4">
+  <a r="6">
     <v t="r">169</v>
     <v t="r">170</v>
     <v t="r">171</v>
     <v t="r">172</v>
+    <v t="r">173</v>
+    <v t="r">171</v>
   </a>
   <a r="4">
-    <v t="r">182</v>
-    <v t="r">183</v>
     <v t="r">184</v>
     <v t="r">185</v>
+    <v t="r">186</v>
+    <v t="r">187</v>
+  </a>
+  <a r="4">
+    <v t="r">197</v>
+    <v t="r">198</v>
+    <v t="r">199</v>
+    <v t="r">200</v>
   </a>
   <a r="1">
     <v t="s">Español mexicano</v>
   </a>
   <a r="2">
-    <v t="r">206</v>
-    <v t="r">207</v>
+    <v t="r">221</v>
+    <v t="r">222</v>
   </a>
   <a r="32">
-    <v t="r">193</v>
-    <v t="r">227</v>
-    <v t="r">228</v>
-    <v t="r">229</v>
-    <v t="r">230</v>
-    <v t="r">231</v>
-    <v t="r">232</v>
-    <v t="r">233</v>
-    <v t="r">234</v>
-    <v t="r">235</v>
-    <v t="r">236</v>
-    <v t="r">237</v>
-    <v t="r">238</v>
-    <v t="r">239</v>
-    <v t="r">240</v>
-    <v t="r">241</v>
+    <v t="r">208</v>
     <v t="r">242</v>
     <v t="r">243</v>
     <v t="r">244</v>
@@ -1024,6 +1225,21 @@
     <v t="r">255</v>
     <v t="r">256</v>
     <v t="r">257</v>
+    <v t="r">258</v>
+    <v t="r">259</v>
+    <v t="r">260</v>
+    <v t="r">261</v>
+    <v t="r">262</v>
+    <v t="r">263</v>
+    <v t="r">264</v>
+    <v t="r">265</v>
+    <v t="r">266</v>
+    <v t="r">267</v>
+    <v t="r">268</v>
+    <v t="r">269</v>
+    <v t="r">270</v>
+    <v t="r">271</v>
+    <v t="r">272</v>
   </a>
   <a r="4">
     <v t="s">Hora estándar del centro</v>
@@ -1032,93 +1248,85 @@
     <v t="s">Horario del este de América del Norte</v>
   </a>
   <a r="4">
-    <v t="r">273</v>
-    <v t="r">274</v>
-    <v t="r">275</v>
-    <v t="r">276</v>
+    <v t="r">288</v>
+    <v t="r">289</v>
+    <v t="r">290</v>
+    <v t="r">291</v>
   </a>
   <a r="4">
-    <v t="r">286</v>
-    <v t="r">287</v>
-    <v t="r">288</v>
-    <v t="r">289</v>
+    <v t="r">301</v>
+    <v t="r">302</v>
+    <v t="r">303</v>
+    <v t="r">304</v>
   </a>
   <a r="4">
-    <v t="r">299</v>
-    <v t="r">300</v>
-    <v t="r">301</v>
-    <v t="r">302</v>
+    <v t="r">314</v>
+    <v t="r">315</v>
+    <v t="r">316</v>
+    <v t="r">317</v>
   </a>
   <a r="4">
-    <v t="r">312</v>
-    <v t="r">313</v>
-    <v t="r">314</v>
-    <v t="r">315</v>
+    <v t="r">327</v>
+    <v t="r">328</v>
+    <v t="r">329</v>
+    <v t="r">330</v>
   </a>
   <a r="4">
-    <v t="r">325</v>
-    <v t="r">326</v>
-    <v t="r">327</v>
-    <v t="r">328</v>
+    <v t="r">340</v>
+    <v t="r">341</v>
+    <v t="r">342</v>
+    <v t="r">343</v>
   </a>
   <a r="4">
-    <v t="r">338</v>
-    <v t="r">339</v>
-    <v t="r">340</v>
-    <v t="r">341</v>
+    <v t="r">353</v>
+    <v t="r">354</v>
+    <v t="r">355</v>
+    <v t="r">356</v>
   </a>
   <a r="4">
-    <v t="r">351</v>
-    <v t="r">352</v>
-    <v t="r">353</v>
-    <v t="r">354</v>
+    <v t="r">366</v>
+    <v t="r">367</v>
+    <v t="r">368</v>
+    <v t="r">369</v>
   </a>
   <a r="1">
-    <v t="r">365</v>
+    <v t="r">380</v>
   </a>
   <a r="4">
-    <v t="r">375</v>
-    <v t="r">376</v>
-    <v t="r">377</v>
-    <v t="r">378</v>
+    <v t="r">390</v>
+    <v t="r">391</v>
+    <v t="r">392</v>
+    <v t="r">393</v>
   </a>
   <a r="4">
-    <v t="r">388</v>
-    <v t="r">389</v>
-    <v t="r">390</v>
-    <v t="r">391</v>
+    <v t="r">403</v>
+    <v t="r">404</v>
+    <v t="r">405</v>
+    <v t="r">406</v>
   </a>
   <a r="4">
-    <v t="r">401</v>
-    <v t="r">402</v>
-    <v t="r">403</v>
-    <v t="r">404</v>
+    <v t="r">416</v>
+    <v t="r">417</v>
+    <v t="r">418</v>
+    <v t="r">419</v>
   </a>
   <a r="4">
-    <v t="r">414</v>
-    <v t="r">415</v>
-    <v t="r">416</v>
-    <v t="r">417</v>
-  </a>
-  <a r="4">
-    <v t="r">428</v>
     <v t="r">429</v>
     <v t="r">430</v>
     <v t="r">431</v>
+    <v t="r">432</v>
   </a>
   <a r="4">
-    <v t="r">442</v>
     <v t="r">443</v>
     <v t="r">444</v>
     <v t="r">445</v>
+    <v t="r">446</v>
   </a>
-  <a r="6">
-    <v t="r">456</v>
+  <a r="4">
     <v t="r">457</v>
     <v t="r">458</v>
     <v t="r">459</v>
     <v t="r">460</v>
-    <v t="r">458</v>
   </a>
   <a r="4">
     <v t="r">470</v>
@@ -2155,31 +2363,31 @@
   </rv>
   <rv s="0">
     <v>536870912</v>
-    <v>Guanajuato</v>
-    <v>9eaf00cd-2b5c-3655-adbc-dc91f1f0fca3</v>
+    <v>Estado de Guerrero</v>
+    <v>86638283-e8d0-0d69-1241-dc688f82149b</v>
     <v>es-ES</v>
     <v>Map</v>
   </rv>
   <rv s="1">
-    <fb>30607</fb>
-    <v>11</v>
-  </rv>
-  <rv s="0">
-    <v>536870912</v>
-    <v>Guanajuato</v>
-    <v>b09ae8a2-6b75-001f-91b5-e744c3f9ec50</v>
-    <v>es-MX</v>
-    <v>Map</v>
-  </rv>
-  <rv s="0">
-    <v>536870912</v>
-    <v>León de Los Aldama</v>
-    <v>c1e69947-32e6-b8cb-ce9b-12039989d544</v>
-    <v>es-MX</v>
-    <v>Map</v>
-  </rv>
-  <rv s="1">
-    <fb>1526991</fb>
+    <fb>63596</fb>
+    <v>11</v>
+  </rv>
+  <rv s="0">
+    <v>536870912</v>
+    <v>Chilpancingo de los Bravo</v>
+    <v>7b0553f5-2151-2c84-42ef-98b265edef92</v>
+    <v>es-MX</v>
+    <v>Map</v>
+  </rv>
+  <rv s="0">
+    <v>536870912</v>
+    <v>Acapulco de Juárez</v>
+    <v>f717fc5c-69cf-4b5d-9d03-93b688ff0a17</v>
+    <v>es-MX</v>
+    <v>Map</v>
+  </rv>
+  <rv s="1">
+    <fb>918131</fb>
     <v>11</v>
   </rv>
   <rv s="2">
@@ -2188,112 +2396,6 @@
     <v>43</v>
     <v>7</v>
     <v>0</v>
-    <v>Image of Guanajuato</v>
-  </rv>
-  <rv s="3">
-    <v>https://www.bing.com/search?q=Guanajuato&amp;form=skydnc</v>
-    <v>Aprenda más con Bing</v>
-  </rv>
-  <rv s="0">
-    <v>805306368</v>
-    <v>Diego Sinhue Rodríguez Vallejo (Gobernador)</v>
-    <v>722adb87-4850-53cf-c958-6235a1328dfe</v>
-    <v>es-MX</v>
-    <v>Generic</v>
-  </rv>
-  <rv s="0">
-    <v>805306368</v>
-    <v>José Erandi Bermúdez Méndez (Senado)</v>
-    <v>e1693082-a6f2-af51-3323-fdf62d9c3e64</v>
-    <v>es-MX</v>
-    <v>Generic</v>
-  </rv>
-  <rv s="0">
-    <v>805306368</v>
-    <v>Alejandra Noemí Reynoso Sánchez (Senado)</v>
-    <v>79cce70e-b047-d129-4aec-53895d1b2542</v>
-    <v>es-MX</v>
-    <v>Generic</v>
-  </rv>
-  <rv s="0">
-    <v>805306368</v>
-    <v>Martha Lucía Micher Camarena (Senado)</v>
-    <v>49135855-4e4e-d86e-5b5d-d9e7fdcdc99b</v>
-    <v>es-MX</v>
-    <v>Generic</v>
-  </rv>
-  <rv s="4">
-    <v>14</v>
-  </rv>
-  <rv s="1">
-    <fb>5853677</fb>
-    <v>11</v>
-  </rv>
-  <rv s="6">
-    <v>#VALUE!</v>
-    <v>es-ES</v>
-    <v>9eaf00cd-2b5c-3655-adbc-dc91f1f0fca3</v>
-    <v>536870912</v>
-    <v>1</v>
-    <v>45</v>
-    <v>4</v>
-    <v>18</v>
-    <v>Guanajuato</v>
-    <v>7</v>
-    <v>8</v>
-    <v>Map</v>
-    <v>9</v>
-    <v>46</v>
-    <v>MX-GUA</v>
-    <v>136</v>
-    <v>137</v>
-    <v>138</v>
-    <v>Guanajuato, oficialmente Estado Libre y Soberano de Guanajuato, es uno de los treinta y un estados que junto con la Ciudad de México conforman México. Su capital es la ciudad homónima y su ciudad más poblada es León de Los Aldama. Se divide en ...</v>
-    <v>139</v>
-    <v>140</v>
-    <v>141</v>
-    <v>146</v>
-    <v>Guanajuato</v>
-    <v>11</v>
-    <v>147</v>
-    <v>Guanajuato</v>
-    <v>mdp/vdpid/12977</v>
-  </rv>
-  <rv s="0">
-    <v>536870912</v>
-    <v>Estado de Guerrero</v>
-    <v>86638283-e8d0-0d69-1241-dc688f82149b</v>
-    <v>es-ES</v>
-    <v>Map</v>
-  </rv>
-  <rv s="1">
-    <fb>63596</fb>
-    <v>11</v>
-  </rv>
-  <rv s="0">
-    <v>536870912</v>
-    <v>Chilpancingo de los Bravo</v>
-    <v>7b0553f5-2151-2c84-42ef-98b265edef92</v>
-    <v>es-MX</v>
-    <v>Map</v>
-  </rv>
-  <rv s="0">
-    <v>536870912</v>
-    <v>Acapulco de Juárez</v>
-    <v>f717fc5c-69cf-4b5d-9d03-93b688ff0a17</v>
-    <v>es-MX</v>
-    <v>Map</v>
-  </rv>
-  <rv s="1">
-    <fb>918131</fb>
-    <v>11</v>
-  </rv>
-  <rv s="2">
-    <v>11</v>
-    <v>9</v>
-    <v>47</v>
-    <v>7</v>
-    <v>0</v>
     <v>Image of Estado de Guerrero</v>
   </rv>
   <rv s="3">
@@ -2329,7 +2431,7 @@
     <v>Generic</v>
   </rv>
   <rv s="4">
-    <v>15</v>
+    <v>14</v>
   </rv>
   <rv s="1">
     <fb>3533251</fb>
@@ -2341,7 +2443,7 @@
     <v>86638283-e8d0-0d69-1241-dc688f82149b</v>
     <v>536870912</v>
     <v>1</v>
-    <v>49</v>
+    <v>45</v>
     <v>4</v>
     <v>18</v>
     <v>Estado de Guerrero</v>
@@ -2351,17 +2453,17 @@
     <v>9</v>
     <v>46</v>
     <v>MX-GRO</v>
-    <v>150</v>
-    <v>151</v>
-    <v>152</v>
+    <v>136</v>
+    <v>137</v>
+    <v>138</v>
     <v>Guerrero, oficialmente Estado Libre y Soberano de Guerrero, es uno de los treinta y un estados que, junto con la Ciudad de México, conforman México. Su capital es Chilpancingo de los Bravo y su ciudad más poblada es Acapulco de Juárez.</v>
-    <v>153</v>
-    <v>154</v>
-    <v>155</v>
-    <v>160</v>
+    <v>139</v>
+    <v>140</v>
+    <v>141</v>
+    <v>146</v>
     <v>Estado de Guerrero</v>
     <v>11</v>
-    <v>161</v>
+    <v>147</v>
     <v>Estado de Guerrero</v>
     <v>mdp/vdpid/13062</v>
   </rv>
@@ -2385,6 +2487,113 @@
   </rv>
   <rv s="1">
     <fb>793123</fb>
+    <v>11</v>
+  </rv>
+  <rv s="2">
+    <v>11</v>
+    <v>9</v>
+    <v>47</v>
+    <v>7</v>
+    <v>0</v>
+    <v>Image of Estado de Hidalgo</v>
+  </rv>
+  <rv s="3">
+    <v>https://www.bing.com/search?q=Estado+de+Hidalgo&amp;form=skydnc</v>
+    <v>Aprenda más con Bing</v>
+  </rv>
+  <rv s="0">
+    <v>805306368</v>
+    <v>Julio Menchaca Salazar (Gobernador)</v>
+    <v>9fb683ad-88e7-c1b6-fc91-eae79b999b22</v>
+    <v>es-MX</v>
+    <v>Generic</v>
+  </rv>
+  <rv s="0">
+    <v>805306368</v>
+    <v>Navor Rojas (Senado)</v>
+    <v>60a27f7a-578a-04a1-e5eb-7c4859ed680e</v>
+    <v>es-MX</v>
+    <v>Generic</v>
+  </rv>
+  <rv s="0">
+    <v>805306368</v>
+    <v>María Merced González González (Senado)</v>
+    <v>09c83650-39b8-e78a-9b85-276ab656e7be</v>
+    <v>es-MX</v>
+    <v>Generic</v>
+  </rv>
+  <rv s="0">
+    <v>805306368</v>
+    <v>Nuvia Mayorga (Senado)</v>
+    <v>728fa283-2f12-3f1f-a77c-35a24667771d</v>
+    <v>es-MX</v>
+    <v>Generic</v>
+  </rv>
+  <rv s="4">
+    <v>15</v>
+  </rv>
+  <rv s="1">
+    <fb>3082841</fb>
+    <v>11</v>
+  </rv>
+  <rv s="5">
+    <v>#VALUE!</v>
+    <v>es-ES</v>
+    <v>76baa939-e01a-077d-0c83-522220d05a5b</v>
+    <v>536870912</v>
+    <v>1</v>
+    <v>49</v>
+    <v>4</v>
+    <v>5</v>
+    <v>Estado de Hidalgo</v>
+    <v>7</v>
+    <v>8</v>
+    <v>Map</v>
+    <v>9</v>
+    <v>10</v>
+    <v>MX-HID</v>
+    <v>150</v>
+    <v>151</v>
+    <v>151</v>
+    <v>Hidalgo, oficialmente Estado Libre y Soberano de Hidalgo, es uno de los treinta y un estados que, junto con la Ciudad de México, conforman México. Su capital y ciudad más poblada es Pachuca de Soto. Está dividido en ochenta y cuatro municipios.</v>
+    <v>152</v>
+    <v>153</v>
+    <v>154</v>
+    <v>159</v>
+    <v>Estado de Hidalgo</v>
+    <v>11</v>
+    <v>160</v>
+    <v>Estado de Hidalgo</v>
+    <v>mdp/vdpid/13937</v>
+    <v>13</v>
+  </rv>
+  <rv s="0">
+    <v>536870912</v>
+    <v>Estado de Veracruz</v>
+    <v>10381f79-264a-f2fd-08f8-cc5377683832</v>
+    <v>es-ES</v>
+    <v>Map</v>
+  </rv>
+  <rv s="1">
+    <fb>71820</fb>
+    <v>11</v>
+  </rv>
+  <rv s="0">
+    <v>536870912</v>
+    <v>Xalapa-Enríquez</v>
+    <v>decfec25-d20c-79d7-63e6-b65f2cd5bf1a</v>
+    <v>es-MX</v>
+    <v>Map</v>
+  </rv>
+  <rv s="0">
+    <v>536870912</v>
+    <v>Veracruz</v>
+    <v>2db7ec30-1035-4400-73cf-1a3e7764446c</v>
+    <v>es-MX</v>
+    <v>Map</v>
+  </rv>
+  <rv s="1">
+    <fb>2299245</fb>
     <v>11</v>
   </rv>
   <rv s="2">
@@ -2393,37 +2602,44 @@
     <v>50</v>
     <v>7</v>
     <v>0</v>
-    <v>Image of Estado de Hidalgo</v>
+    <v>Image of Estado de Veracruz</v>
   </rv>
   <rv s="3">
-    <v>https://www.bing.com/search?q=Estado+de+Hidalgo&amp;form=skydnc</v>
+    <v>https://www.bing.com/search?q=Veracruz+de+Ignacio+de+la+Llave&amp;form=skydnc</v>
     <v>Aprenda más con Bing</v>
   </rv>
   <rv s="0">
     <v>805306368</v>
-    <v>Julio Menchaca Salazar (Gobernador)</v>
-    <v>9fb683ad-88e7-c1b6-fc91-eae79b999b22</v>
-    <v>es-MX</v>
-    <v>Generic</v>
-  </rv>
-  <rv s="0">
-    <v>805306368</v>
-    <v>Navor Rojas (Senado)</v>
-    <v>60a27f7a-578a-04a1-e5eb-7c4859ed680e</v>
-    <v>es-MX</v>
-    <v>Generic</v>
-  </rv>
-  <rv s="0">
-    <v>805306368</v>
-    <v>María Merced González González (Senado)</v>
-    <v>09c83650-39b8-e78a-9b85-276ab656e7be</v>
-    <v>es-MX</v>
-    <v>Generic</v>
-  </rv>
-  <rv s="0">
-    <v>805306368</v>
-    <v>Nuvia Mayorga (Senado)</v>
-    <v>728fa283-2f12-3f1f-a77c-35a24667771d</v>
+    <v>Rocío Nahle (Gobernador)</v>
+    <v>48a4aa04-48b8-2287-13d9-67b6b96043d2</v>
+    <v>es-MX</v>
+    <v>Generic</v>
+  </rv>
+  <rv s="0">
+    <v>805306368</v>
+    <v>Raquel Bonilla Herrera (Senado)</v>
+    <v>76e8052a-c72a-6efe-748d-c8731c829e79</v>
+    <v>es-MX</v>
+    <v>Generic</v>
+  </rv>
+  <rv s="0">
+    <v>805306368</v>
+    <v>nb (Senado)</v>
+    <v>3d15599c-d922-ccf7-021b-17b425cc31c5</v>
+    <v>es-MX</v>
+    <v>Generic</v>
+  </rv>
+  <rv s="0">
+    <v>805306368</v>
+    <v>Manuel Huerta Ladrón de Guevara (Senado)</v>
+    <v>ecd4d6f6-19b0-fc84-fe9f-ebe7e5947d9a</v>
+    <v>es-MX</v>
+    <v>Generic</v>
+  </rv>
+  <rv s="0">
+    <v>805306368</v>
+    <v>Miguel Ángel Yunes Márquez (Senado)</v>
+    <v>ac46d84a-f4f2-4a03-a110-5e1bd9013e62</v>
     <v>es-MX</v>
     <v>Generic</v>
   </rv>
@@ -2431,60 +2647,67 @@
     <v>16</v>
   </rv>
   <rv s="1">
-    <fb>3082841</fb>
+    <fb>8062579</fb>
     <v>11</v>
   </rv>
   <rv s="5">
     <v>#VALUE!</v>
     <v>es-ES</v>
-    <v>76baa939-e01a-077d-0c83-522220d05a5b</v>
+    <v>10381f79-264a-f2fd-08f8-cc5377683832</v>
     <v>536870912</v>
     <v>1</v>
     <v>52</v>
     <v>4</v>
     <v>5</v>
-    <v>Estado de Hidalgo</v>
+    <v>Estado de Veracruz</v>
     <v>7</v>
     <v>8</v>
     <v>Map</v>
     <v>9</v>
     <v>10</v>
-    <v>MX-HID</v>
+    <v>MX-VER</v>
+    <v>163</v>
     <v>164</v>
     <v>165</v>
-    <v>165</v>
-    <v>Hidalgo, oficialmente Estado Libre y Soberano de Hidalgo, es uno de los treinta y un estados que, junto con la Ciudad de México, conforman México. Su capital y ciudad más poblada es Pachuca de Soto. Está dividido en ochenta y cuatro municipios.</v>
+    <v>Veracruz, oficialmente llamado Estado Libre y Soberano de Veracruz de Ignacio de la Llave, es uno de los treinta y un estados que, junto con la Ciudad de México, conforman México. Su capital es Xalapa-Enríquez y su ciudad más poblada es ...</v>
     <v>166</v>
     <v>167</v>
     <v>168</v>
-    <v>173</v>
-    <v>Estado de Hidalgo</v>
-    <v>11</v>
     <v>174</v>
-    <v>Estado de Hidalgo</v>
-    <v>mdp/vdpid/13937</v>
+    <v>Estado de Veracruz</v>
+    <v>11</v>
+    <v>175</v>
+    <v>Estado de Veracruz</v>
+    <v>mdp/vdpid/34963</v>
     <v>13</v>
   </rv>
   <rv s="0">
     <v>536870912</v>
-    <v>Jalisco</v>
-    <v>18c29bf9-bbf0-e90f-10f3-c48c9791339b</v>
+    <v>Guanajuato</v>
+    <v>9eaf00cd-2b5c-3655-adbc-dc91f1f0fca3</v>
     <v>es-ES</v>
     <v>Map</v>
   </rv>
   <rv s="1">
-    <fb>78588</fb>
-    <v>11</v>
-  </rv>
-  <rv s="0">
-    <v>536870912</v>
-    <v>Guadalajara</v>
-    <v>bde57fba-2206-ac66-4407-b25eb03c3813</v>
-    <v>es-MX</v>
-    <v>Map</v>
-  </rv>
-  <rv s="1">
-    <fb>2253064</fb>
+    <fb>30607</fb>
+    <v>11</v>
+  </rv>
+  <rv s="0">
+    <v>536870912</v>
+    <v>Guanajuato</v>
+    <v>b09ae8a2-6b75-001f-91b5-e744c3f9ec50</v>
+    <v>es-MX</v>
+    <v>Map</v>
+  </rv>
+  <rv s="0">
+    <v>536870912</v>
+    <v>León de Los Aldama</v>
+    <v>c1e69947-32e6-b8cb-ce9b-12039989d544</v>
+    <v>es-MX</v>
+    <v>Map</v>
+  </rv>
+  <rv s="1">
+    <fb>1526991</fb>
     <v>11</v>
   </rv>
   <rv s="2">
@@ -2493,6 +2716,105 @@
     <v>53</v>
     <v>7</v>
     <v>0</v>
+    <v>Image of Guanajuato</v>
+  </rv>
+  <rv s="3">
+    <v>https://www.bing.com/search?q=Guanajuato&amp;form=skydnc</v>
+    <v>Aprenda más con Bing</v>
+  </rv>
+  <rv s="0">
+    <v>805306368</v>
+    <v>Diego Sinhue Rodríguez Vallejo (Gobernador)</v>
+    <v>722adb87-4850-53cf-c958-6235a1328dfe</v>
+    <v>es-MX</v>
+    <v>Generic</v>
+  </rv>
+  <rv s="0">
+    <v>805306368</v>
+    <v>José Erandi Bermúdez Méndez (Senado)</v>
+    <v>e1693082-a6f2-af51-3323-fdf62d9c3e64</v>
+    <v>es-MX</v>
+    <v>Generic</v>
+  </rv>
+  <rv s="0">
+    <v>805306368</v>
+    <v>Alejandra Noemí Reynoso Sánchez (Senado)</v>
+    <v>79cce70e-b047-d129-4aec-53895d1b2542</v>
+    <v>es-MX</v>
+    <v>Generic</v>
+  </rv>
+  <rv s="0">
+    <v>805306368</v>
+    <v>Martha Lucía Micher Camarena (Senado)</v>
+    <v>49135855-4e4e-d86e-5b5d-d9e7fdcdc99b</v>
+    <v>es-MX</v>
+    <v>Generic</v>
+  </rv>
+  <rv s="4">
+    <v>17</v>
+  </rv>
+  <rv s="1">
+    <fb>5853677</fb>
+    <v>11</v>
+  </rv>
+  <rv s="6">
+    <v>#VALUE!</v>
+    <v>es-ES</v>
+    <v>9eaf00cd-2b5c-3655-adbc-dc91f1f0fca3</v>
+    <v>536870912</v>
+    <v>1</v>
+    <v>55</v>
+    <v>4</v>
+    <v>18</v>
+    <v>Guanajuato</v>
+    <v>7</v>
+    <v>8</v>
+    <v>Map</v>
+    <v>9</v>
+    <v>46</v>
+    <v>MX-GUA</v>
+    <v>178</v>
+    <v>179</v>
+    <v>180</v>
+    <v>Guanajuato, oficialmente Estado Libre y Soberano de Guanajuato, es uno de los treinta y un estados que junto con la Ciudad de México conforman México. Su capital es la ciudad homónima y su ciudad más poblada es León de Los Aldama. Se divide en ...</v>
+    <v>181</v>
+    <v>182</v>
+    <v>183</v>
+    <v>188</v>
+    <v>Guanajuato</v>
+    <v>11</v>
+    <v>189</v>
+    <v>Guanajuato</v>
+    <v>mdp/vdpid/12977</v>
+  </rv>
+  <rv s="0">
+    <v>536870912</v>
+    <v>Jalisco</v>
+    <v>18c29bf9-bbf0-e90f-10f3-c48c9791339b</v>
+    <v>es-ES</v>
+    <v>Map</v>
+  </rv>
+  <rv s="1">
+    <fb>78588</fb>
+    <v>11</v>
+  </rv>
+  <rv s="0">
+    <v>536870912</v>
+    <v>Guadalajara</v>
+    <v>bde57fba-2206-ac66-4407-b25eb03c3813</v>
+    <v>es-MX</v>
+    <v>Map</v>
+  </rv>
+  <rv s="1">
+    <fb>2253064</fb>
+    <v>11</v>
+  </rv>
+  <rv s="2">
+    <v>14</v>
+    <v>9</v>
+    <v>56</v>
+    <v>7</v>
+    <v>0</v>
     <v>Image of Jalisco</v>
   </rv>
   <rv s="3">
@@ -2528,7 +2850,7 @@
     <v>Generic</v>
   </rv>
   <rv s="4">
-    <v>17</v>
+    <v>18</v>
   </rv>
   <rv s="1">
     <fb>8348151</fb>
@@ -2540,7 +2862,7 @@
     <v>18c29bf9-bbf0-e90f-10f3-c48c9791339b</v>
     <v>536870912</v>
     <v>1</v>
-    <v>55</v>
+    <v>58</v>
     <v>4</v>
     <v>5</v>
     <v>Jalisco</v>
@@ -2550,17 +2872,17 @@
     <v>9</v>
     <v>10</v>
     <v>MX-JAL</v>
-    <v>177</v>
-    <v>178</v>
-    <v>178</v>
+    <v>192</v>
+    <v>193</v>
+    <v>193</v>
     <v>Jalisco oficialmente Estado Libre y Soberano de Jalisco es uno de los treinta y un estados que, junto con la Ciudad de México, conforman México. Su municipio más poblado es Zapopan y su capital y ciudad más poblada es Guadalajara. Está dividido ...</v>
-    <v>179</v>
-    <v>180</v>
-    <v>181</v>
-    <v>186</v>
+    <v>194</v>
+    <v>195</v>
+    <v>196</v>
+    <v>201</v>
     <v>Jalisco</v>
     <v>11</v>
-    <v>187</v>
+    <v>202</v>
     <v>Jalisco</v>
     <v>mdp/vdpid/15353</v>
     <v>13</v>
@@ -2578,11 +2900,11 @@
   </rv>
   <rv s="1">
     <fb>0.339249458255099</fb>
-    <v>76</v>
+    <v>79</v>
   </rv>
   <rv s="1">
     <fb>3.6359614212704998E-2</fb>
-    <v>76</v>
+    <v>79</v>
   </rv>
   <rv s="0">
     <v>536870912</v>
@@ -2593,50 +2915,50 @@
   </rv>
   <rv s="1">
     <fb>413618820000</fb>
-    <v>77</v>
+    <v>80</v>
   </rv>
   <rv s="1">
     <fb>52</fb>
-    <v>78</v>
+    <v>81</v>
   </rv>
   <rv s="1">
     <fb>90.426207910940704</fb>
+    <v>82</v>
+  </rv>
+  <rv s="1">
+    <fb>2157.32394883914</fb>
+    <v>11</v>
+  </rv>
+  <rv s="1">
+    <fb>486405.54800000001</fb>
+    <v>11</v>
+  </rv>
+  <rv s="1">
+    <fb>74.992000000000004</fb>
+    <v>82</v>
+  </rv>
+  <rv s="1">
+    <fb>0.41370018680000004</fb>
     <v>79</v>
   </rv>
-  <rv s="1">
-    <fb>2157.32394883914</fb>
-    <v>11</v>
-  </rv>
-  <rv s="1">
-    <fb>486405.54800000001</fb>
-    <v>11</v>
-  </rv>
-  <rv s="1">
-    <fb>74.992000000000004</fb>
-    <v>79</v>
-  </rv>
-  <rv s="1">
-    <fb>0.41370018680000004</fb>
-    <v>76</v>
-  </rv>
   <rv s="4">
-    <v>18</v>
+    <v>19</v>
   </rv>
   <rv s="2">
-    <v>14</v>
+    <v>15</v>
     <v>9</v>
-    <v>58</v>
+    <v>61</v>
     <v>7</v>
     <v>0</v>
     <v>Image of México</v>
   </rv>
   <rv s="1">
     <fb>0.130829255322402</fb>
-    <v>76</v>
+    <v>79</v>
   </rv>
   <rv s="1">
     <fb>141.54252296997399</fb>
-    <v>80</v>
+    <v>83</v>
   </rv>
   <rv s="3">
     <v>https://www.bing.com/search?q=M%c3%a9xico&amp;form=skydnc</v>
@@ -2657,79 +2979,79 @@
     <v>Generic</v>
   </rv>
   <rv s="4">
-    <v>19</v>
+    <v>20</v>
   </rv>
   <rv s="1">
     <fb>1.0577000999999999</fb>
-    <v>76</v>
+    <v>79</v>
   </rv>
   <rv s="1">
     <fb>0.40228960000000002</fb>
-    <v>76</v>
+    <v>79</v>
   </rv>
   <rv s="1">
     <fb>2.3826999999999998</fb>
-    <v>81</v>
+    <v>84</v>
   </rv>
   <rv s="1">
     <fb>11</fb>
+    <v>82</v>
+  </rv>
+  <rv s="1">
+    <fb>1258286717124.53</fb>
+    <v>80</v>
+  </rv>
+  <rv s="1">
+    <fb>127504125</fb>
+    <v>11</v>
+  </rv>
+  <rv s="1">
+    <fb>102626859</fb>
+    <v>11</v>
+  </rv>
+  <rv s="1">
+    <fb>0.36399999999999999</fb>
     <v>79</v>
   </rv>
   <rv s="1">
-    <fb>1258286717124.53</fb>
-    <v>77</v>
-  </rv>
-  <rv s="1">
-    <fb>127504125</fb>
-    <v>11</v>
-  </rv>
-  <rv s="1">
-    <fb>102626859</fb>
-    <v>11</v>
-  </rv>
-  <rv s="1">
-    <fb>0.36399999999999999</fb>
-    <v>76</v>
-  </rv>
-  <rv s="1">
     <fb>0.02</fb>
-    <v>76</v>
+    <v>79</v>
   </rv>
   <rv s="1">
     <fb>0.51700000000000002</fb>
-    <v>76</v>
+    <v>79</v>
   </rv>
   <rv s="1">
     <fb>5.4000000000000006E-2</fb>
-    <v>76</v>
+    <v>79</v>
   </rv>
   <rv s="1">
     <fb>0.2</fb>
-    <v>76</v>
+    <v>79</v>
   </rv>
   <rv s="1">
     <fb>0.60680000305175807</fb>
-    <v>76</v>
+    <v>79</v>
   </rv>
   <rv s="1">
     <fb>9.5000000000000001E-2</fb>
-    <v>76</v>
+    <v>79</v>
   </rv>
   <rv s="1">
     <fb>0.13500000000000001</fb>
-    <v>76</v>
+    <v>79</v>
   </rv>
   <rv s="1">
     <fb>0.73</fb>
+    <v>85</v>
+  </rv>
+  <rv s="1">
+    <fb>33</fb>
     <v>82</v>
   </rv>
   <rv s="1">
-    <fb>33</fb>
-    <v>79</v>
-  </rv>
-  <rv s="1">
     <fb>0.49</fb>
-    <v>82</v>
+    <v>85</v>
   </rv>
   <rv s="0">
     <v>536870912</v>
@@ -2949,7 +3271,7 @@
     <v>Map</v>
   </rv>
   <rv s="4">
-    <v>20</v>
+    <v>21</v>
   </rv>
   <rv s="1">
     <fb>336000</fb>
@@ -2957,26 +3279,26 @@
   </rv>
   <rv s="1">
     <fb>3.4249999523162801E-2</fb>
-    <v>83</v>
+    <v>86</v>
   </rv>
   <rv s="1">
     <fb>2.129</fb>
-    <v>81</v>
+    <v>84</v>
   </rv>
   <rv s="1">
     <fb>0.55100000000000005</fb>
-    <v>76</v>
+    <v>79</v>
   </rv>
   <rv s="1">
     <fb>17.602</fb>
-    <v>81</v>
+    <v>84</v>
   </rv>
   <rv s="1">
     <fb>0.54649553743666202</fb>
-    <v>76</v>
+    <v>79</v>
   </rv>
   <rv s="4">
-    <v>21</v>
+    <v>22</v>
   </rv>
   <rv s="8">
     <v>#VALUE!</v>
@@ -2984,67 +3306,67 @@
     <v>8e475659-4bdc-d912-6494-affce0096bc1</v>
     <v>536870912</v>
     <v>1</v>
-    <v>72</v>
-    <v>73</v>
-    <v>74</v>
+    <v>75</v>
+    <v>76</v>
+    <v>77</v>
     <v>México</v>
     <v>7</v>
     <v>8</v>
     <v>Map</v>
     <v>9</v>
-    <v>75</v>
+    <v>78</v>
     <v>MX</v>
-    <v>190</v>
-    <v>191</v>
-    <v>192</v>
-    <v>193</v>
-    <v>194</v>
-    <v>193</v>
-    <v>195</v>
-    <v>MXN</v>
-    <v>196</v>
-    <v>197</v>
-    <v>México, oficialmente Estados Unidos Mexicanos, es un país soberano ubicado en la parte meridional de América del Norte; su capital y ciudad más poblada es la Ciudad de México. De acuerdo con la constitución vigente, su forma de gobierno consiste ...</v>
-    <v>198</v>
-    <v>199</v>
-    <v>200</v>
-    <v>Himno Nacional Mexicano</v>
-    <v>201</v>
-    <v>202</v>
-    <v>203</v>
-    <v>204</v>
     <v>205</v>
+    <v>206</v>
+    <v>207</v>
     <v>208</v>
     <v>209</v>
+    <v>208</v>
     <v>210</v>
+    <v>MXN</v>
     <v>211</v>
     <v>212</v>
-    <v>México</v>
-    <v>Estaos Xuníos Mexicanos</v>
+    <v>México, oficialmente Estados Unidos Mexicanos, es un país soberano ubicado en la parte meridional de América del Norte; su capital y ciudad más poblada es la Ciudad de México. De acuerdo con la constitución vigente, su forma de gobierno consiste ...</v>
     <v>213</v>
     <v>214</v>
     <v>215</v>
+    <v>Himno Nacional Mexicano</v>
     <v>216</v>
     <v>217</v>
     <v>218</v>
     <v>219</v>
     <v>220</v>
-    <v>221</v>
-    <v>222</v>
     <v>223</v>
     <v>224</v>
     <v>225</v>
     <v>226</v>
-    <v>258</v>
-    <v>259</v>
-    <v>260</v>
-    <v>261</v>
-    <v>262</v>
-    <v>263</v>
-    <v>264</v>
+    <v>227</v>
+    <v>México</v>
+    <v>Estaos Xuníos Mexicanos</v>
+    <v>228</v>
+    <v>229</v>
+    <v>230</v>
+    <v>231</v>
+    <v>232</v>
+    <v>233</v>
+    <v>234</v>
+    <v>235</v>
+    <v>236</v>
+    <v>237</v>
+    <v>238</v>
+    <v>239</v>
+    <v>240</v>
+    <v>241</v>
+    <v>273</v>
+    <v>274</v>
+    <v>275</v>
+    <v>276</v>
+    <v>277</v>
+    <v>278</v>
+    <v>279</v>
     <v>México</v>
     <v>mdp/vdpid/166</v>
-    <v>265</v>
+    <v>280</v>
   </rv>
   <rv s="0">
     <v>536870912</v>
@@ -3066,106 +3388,6 @@
   </rv>
   <rv s="1">
     <fb>1297475</fb>
-    <v>11</v>
-  </rv>
-  <rv s="2">
-    <v>15</v>
-    <v>9</v>
-    <v>84</v>
-    <v>7</v>
-    <v>0</v>
-    <v>Image of Michoacán</v>
-  </rv>
-  <rv s="3">
-    <v>https://www.bing.com/search?q=Michoac%c3%a1n&amp;form=skydnc</v>
-    <v>Aprenda más con Bing</v>
-  </rv>
-  <rv s="0">
-    <v>805306368</v>
-    <v>Alfredo Ramírez Bedolla (Gobernador)</v>
-    <v>776fa03f-3e61-0cbd-141e-fb086db9347d</v>
-    <v>es-MX</v>
-    <v>Generic</v>
-  </rv>
-  <rv s="0">
-    <v>805306368</v>
-    <v>Cristóbal Arias Solís (Senado)</v>
-    <v>348c61e8-e0f1-4175-a1f0-197bc23b7fad</v>
-    <v>es-MX</v>
-    <v>Generic</v>
-  </rv>
-  <rv s="0">
-    <v>805306368</v>
-    <v>Blanca Estela Piña Gudiño (Senado)</v>
-    <v>56922cb8-8b74-b967-4458-0c85d4e225d8</v>
-    <v>es-MX</v>
-    <v>Generic</v>
-  </rv>
-  <rv s="0">
-    <v>805306368</v>
-    <v>Antonio García Conejo (Senado)</v>
-    <v>5b976e85-1a8d-4304-b735-da7c5b7013f6</v>
-    <v>es-MX</v>
-    <v>Generic</v>
-  </rv>
-  <rv s="4">
-    <v>22</v>
-  </rv>
-  <rv s="1">
-    <fb>4584471</fb>
-    <v>11</v>
-  </rv>
-  <rv s="5">
-    <v>#VALUE!</v>
-    <v>es-ES</v>
-    <v>33ec3160-5b7b-5fef-defd-4574b6b819d6</v>
-    <v>536870912</v>
-    <v>1</v>
-    <v>86</v>
-    <v>4</v>
-    <v>5</v>
-    <v>Michoacán</v>
-    <v>7</v>
-    <v>8</v>
-    <v>Map</v>
-    <v>9</v>
-    <v>46</v>
-    <v>MX-MIC</v>
-    <v>268</v>
-    <v>269</v>
-    <v>269</v>
-    <v>Michoacán oficialmente Estado Libre y Soberano de Michoacán de Ocampo, es uno de los treinta y un estados que, junto con la Ciudad de México, conforman México. Su capital y su ciudad más poblada es Morelia, que lleva su nombre actual en honor a ...</v>
-    <v>270</v>
-    <v>271</v>
-    <v>272</v>
-    <v>277</v>
-    <v>Michoacán</v>
-    <v>11</v>
-    <v>278</v>
-    <v>Michoacán</v>
-    <v>mdp/vdpid/41699</v>
-    <v>93</v>
-  </rv>
-  <rv s="0">
-    <v>536870912</v>
-    <v>Morelos</v>
-    <v>457cd12b-12ce-71c2-81d5-f60ba9645b36</v>
-    <v>es-ES</v>
-    <v>Map</v>
-  </rv>
-  <rv s="1">
-    <fb>4879</fb>
-    <v>11</v>
-  </rv>
-  <rv s="0">
-    <v>536870912</v>
-    <v>Cuernavaca</v>
-    <v>b1a4ba2a-4e50-beb1-5101-91d322c0acad</v>
-    <v>es-MX</v>
-    <v>Map</v>
-  </rv>
-  <rv s="1">
-    <fb>559134</fb>
     <v>11</v>
   </rv>
   <rv s="2">
@@ -3174,37 +3396,37 @@
     <v>87</v>
     <v>7</v>
     <v>0</v>
-    <v>Image of Morelos</v>
+    <v>Image of Michoacán</v>
   </rv>
   <rv s="3">
-    <v>https://www.bing.com/search?q=Morelos&amp;form=skydnc</v>
+    <v>https://www.bing.com/search?q=Michoac%c3%a1n&amp;form=skydnc</v>
     <v>Aprenda más con Bing</v>
   </rv>
   <rv s="0">
     <v>805306368</v>
-    <v>Margarita González Saravia (Gobernador)</v>
-    <v>7ef508a7-8262-2f22-96e7-821cae755d84</v>
-    <v>es-MX</v>
-    <v>Generic</v>
-  </rv>
-  <rv s="0">
-    <v>805306368</v>
-    <v>Lucía Meza Guzmán (Senado)</v>
-    <v>bc7c7e82-808a-50dc-3bca-9644b99b7eb4</v>
-    <v>es-MX</v>
-    <v>Generic</v>
-  </rv>
-  <rv s="0">
-    <v>805306368</v>
-    <v>Sergio Pérez Flores (Senado)</v>
-    <v>0ac2ac8f-9d88-0857-4f9b-0f6c3f086a42</v>
-    <v>es-MX</v>
-    <v>Generic</v>
-  </rv>
-  <rv s="0">
-    <v>805306368</v>
-    <v>Ángel García Yáñez (Senado)</v>
-    <v>bf1f9e7a-2aab-24f5-f2ec-7dcbcc199603</v>
+    <v>Alfredo Ramírez Bedolla (Gobernador)</v>
+    <v>776fa03f-3e61-0cbd-141e-fb086db9347d</v>
+    <v>es-MX</v>
+    <v>Generic</v>
+  </rv>
+  <rv s="0">
+    <v>805306368</v>
+    <v>Cristóbal Arias Solís (Senado)</v>
+    <v>348c61e8-e0f1-4175-a1f0-197bc23b7fad</v>
+    <v>es-MX</v>
+    <v>Generic</v>
+  </rv>
+  <rv s="0">
+    <v>805306368</v>
+    <v>Blanca Estela Piña Gudiño (Senado)</v>
+    <v>56922cb8-8b74-b967-4458-0c85d4e225d8</v>
+    <v>es-MX</v>
+    <v>Generic</v>
+  </rv>
+  <rv s="0">
+    <v>805306368</v>
+    <v>Antonio García Conejo (Senado)</v>
+    <v>5b976e85-1a8d-4304-b735-da7c5b7013f6</v>
     <v>es-MX</v>
     <v>Generic</v>
   </rv>
@@ -3212,60 +3434,60 @@
     <v>23</v>
   </rv>
   <rv s="1">
-    <fb>1971520</fb>
+    <fb>4584471</fb>
     <v>11</v>
   </rv>
   <rv s="5">
     <v>#VALUE!</v>
     <v>es-ES</v>
-    <v>457cd12b-12ce-71c2-81d5-f60ba9645b36</v>
+    <v>33ec3160-5b7b-5fef-defd-4574b6b819d6</v>
     <v>536870912</v>
     <v>1</v>
     <v>89</v>
     <v>4</v>
     <v>5</v>
-    <v>Morelos</v>
+    <v>Michoacán</v>
     <v>7</v>
     <v>8</v>
     <v>Map</v>
     <v>9</v>
-    <v>10</v>
-    <v>MX-MOR</v>
-    <v>281</v>
-    <v>282</v>
-    <v>282</v>
-    <v>Morelos, oficialmente Estado Libre y Soberano de Morelos, es uno de los treinta y un estados que, junto con la Ciudad de México, conforman México. Su capital y ciudad más poblada es Cuernavaca. Está dividido en treinta y seis municipios.</v>
+    <v>46</v>
+    <v>MX-MIC</v>
     <v>283</v>
     <v>284</v>
+    <v>284</v>
+    <v>Michoacán oficialmente Estado Libre y Soberano de Michoacán de Ocampo, es uno de los treinta y un estados que, junto con la Ciudad de México, conforman México. Su capital y su ciudad más poblada es Morelia, que lleva su nombre actual en honor a ...</v>
     <v>285</v>
-    <v>290</v>
+    <v>286</v>
+    <v>287</v>
+    <v>292</v>
+    <v>Michoacán</v>
+    <v>11</v>
+    <v>293</v>
+    <v>Michoacán</v>
+    <v>mdp/vdpid/41699</v>
+    <v>93</v>
+  </rv>
+  <rv s="0">
+    <v>536870912</v>
     <v>Morelos</v>
-    <v>11</v>
-    <v>291</v>
-    <v>Morelos</v>
-    <v>mdp/vdpid/8315667</v>
-    <v>13</v>
-  </rv>
-  <rv s="0">
-    <v>536870912</v>
-    <v>Nayarit</v>
-    <v>d5ab8703-9922-20b7-03c7-acb17f76b03e</v>
+    <v>457cd12b-12ce-71c2-81d5-f60ba9645b36</v>
     <v>es-ES</v>
     <v>Map</v>
   </rv>
   <rv s="1">
-    <fb>27857</fb>
-    <v>11</v>
-  </rv>
-  <rv s="0">
-    <v>536870912</v>
-    <v>Tepic</v>
-    <v>c052f44f-a430-5a91-309a-c0e138b315bb</v>
-    <v>es-MX</v>
-    <v>Map</v>
-  </rv>
-  <rv s="1">
-    <fb>368262</fb>
+    <fb>4879</fb>
+    <v>11</v>
+  </rv>
+  <rv s="0">
+    <v>536870912</v>
+    <v>Cuernavaca</v>
+    <v>b1a4ba2a-4e50-beb1-5101-91d322c0acad</v>
+    <v>es-MX</v>
+    <v>Map</v>
+  </rv>
+  <rv s="1">
+    <fb>559134</fb>
     <v>11</v>
   </rv>
   <rv s="2">
@@ -3274,37 +3496,37 @@
     <v>90</v>
     <v>7</v>
     <v>0</v>
-    <v>Image of Nayarit</v>
+    <v>Image of Morelos</v>
   </rv>
   <rv s="3">
-    <v>https://www.bing.com/search?q=Nayarit&amp;form=skydnc</v>
+    <v>https://www.bing.com/search?q=Morelos&amp;form=skydnc</v>
     <v>Aprenda más con Bing</v>
   </rv>
   <rv s="0">
     <v>805306368</v>
-    <v>Miguel Ángel Navarro Quintero (Gobernador)</v>
-    <v>9c7bfc9a-aa60-6546-e3c6-45cbd406ee3a</v>
-    <v>es-MX</v>
-    <v>Generic</v>
-  </rv>
-  <rv s="0">
-    <v>805306368</v>
-    <v>Cora Cecilia Pinedo Alonso (Senado)</v>
-    <v>f837885e-514f-5905-b5c5-521ab79af917</v>
-    <v>es-MX</v>
-    <v>Generic</v>
-  </rv>
-  <rv s="0">
-    <v>805306368</v>
-    <v>Rosa Elena Jiménez Arteaga (Senado)</v>
-    <v>5122a1ed-f756-bfd1-92cc-bebc3513d078</v>
-    <v>es-MX</v>
-    <v>Generic</v>
-  </rv>
-  <rv s="0">
-    <v>805306368</v>
-    <v>Gloria Núñez Sánchez (Senado)</v>
-    <v>f66c991c-0fb0-29ef-7c75-1e3dad276c5d</v>
+    <v>Margarita González Saravia (Gobernador)</v>
+    <v>7ef508a7-8262-2f22-96e7-821cae755d84</v>
+    <v>es-MX</v>
+    <v>Generic</v>
+  </rv>
+  <rv s="0">
+    <v>805306368</v>
+    <v>Lucía Meza Guzmán (Senado)</v>
+    <v>bc7c7e82-808a-50dc-3bca-9644b99b7eb4</v>
+    <v>es-MX</v>
+    <v>Generic</v>
+  </rv>
+  <rv s="0">
+    <v>805306368</v>
+    <v>Sergio Pérez Flores (Senado)</v>
+    <v>0ac2ac8f-9d88-0857-4f9b-0f6c3f086a42</v>
+    <v>es-MX</v>
+    <v>Generic</v>
+  </rv>
+  <rv s="0">
+    <v>805306368</v>
+    <v>Ángel García Yáñez (Senado)</v>
+    <v>bf1f9e7a-2aab-24f5-f2ec-7dcbcc199603</v>
     <v>es-MX</v>
     <v>Generic</v>
   </rv>
@@ -3312,60 +3534,60 @@
     <v>24</v>
   </rv>
   <rv s="1">
-    <fb>1235456</fb>
+    <fb>1971520</fb>
     <v>11</v>
   </rv>
   <rv s="5">
     <v>#VALUE!</v>
     <v>es-ES</v>
-    <v>d5ab8703-9922-20b7-03c7-acb17f76b03e</v>
+    <v>457cd12b-12ce-71c2-81d5-f60ba9645b36</v>
     <v>536870912</v>
     <v>1</v>
     <v>92</v>
     <v>4</v>
     <v>5</v>
-    <v>Nayarit</v>
+    <v>Morelos</v>
     <v>7</v>
     <v>8</v>
     <v>Map</v>
     <v>9</v>
     <v>10</v>
-    <v>MX-NAY</v>
-    <v>294</v>
-    <v>295</v>
-    <v>295</v>
-    <v>Nayarit, oficialmente Estado Libre y Soberano de Nayarit, es uno de los treinta y un estados que, junto con la Ciudad de México, conforman México. Su capital y ciudad más poblada es Tepic. Está dividido en veinte municipios.</v>
+    <v>MX-MOR</v>
     <v>296</v>
     <v>297</v>
+    <v>297</v>
+    <v>Morelos, oficialmente Estado Libre y Soberano de Morelos, es uno de los treinta y un estados que, junto con la Ciudad de México, conforman México. Su capital y ciudad más poblada es Cuernavaca. Está dividido en treinta y seis municipios.</v>
     <v>298</v>
-    <v>303</v>
+    <v>299</v>
+    <v>300</v>
+    <v>305</v>
+    <v>Morelos</v>
+    <v>11</v>
+    <v>306</v>
+    <v>Morelos</v>
+    <v>mdp/vdpid/8315667</v>
+    <v>13</v>
+  </rv>
+  <rv s="0">
+    <v>536870912</v>
     <v>Nayarit</v>
-    <v>11</v>
-    <v>304</v>
-    <v>Nayarit</v>
-    <v>mdp/vdpid/22833</v>
-    <v>83</v>
-  </rv>
-  <rv s="0">
-    <v>536870912</v>
-    <v>Nuevo León</v>
-    <v>1696b325-bf35-b9aa-28db-3304c1996498</v>
+    <v>d5ab8703-9922-20b7-03c7-acb17f76b03e</v>
     <v>es-ES</v>
     <v>Map</v>
   </rv>
   <rv s="1">
-    <fb>64156</fb>
-    <v>11</v>
-  </rv>
-  <rv s="0">
-    <v>536870912</v>
-    <v>Monterrey</v>
-    <v>7efc18c0-8c1d-eee3-2e2c-94beca244838</v>
-    <v>es-MX</v>
-    <v>Map</v>
-  </rv>
-  <rv s="1">
-    <fb>1430074</fb>
+    <fb>27857</fb>
+    <v>11</v>
+  </rv>
+  <rv s="0">
+    <v>536870912</v>
+    <v>Tepic</v>
+    <v>c052f44f-a430-5a91-309a-c0e138b315bb</v>
+    <v>es-MX</v>
+    <v>Map</v>
+  </rv>
+  <rv s="1">
+    <fb>368262</fb>
     <v>11</v>
   </rv>
   <rv s="2">
@@ -3374,37 +3596,37 @@
     <v>93</v>
     <v>7</v>
     <v>0</v>
-    <v>Image of Nuevo León</v>
+    <v>Image of Nayarit</v>
   </rv>
   <rv s="3">
-    <v>https://www.bing.com/search?q=Nuevo+Le%c3%b3n&amp;form=skydnc</v>
+    <v>https://www.bing.com/search?q=Nayarit&amp;form=skydnc</v>
     <v>Aprenda más con Bing</v>
   </rv>
   <rv s="0">
     <v>805306368</v>
-    <v>Samuel García (Gobernador)</v>
-    <v>54db8350-11f4-b808-4a4a-0698afc4f266</v>
-    <v>es-MX</v>
-    <v>Generic</v>
-  </rv>
-  <rv s="0">
-    <v>805306368</v>
-    <v>Luis David Ortíz Salinas (Senado)</v>
-    <v>18c286c4-64fd-19f9-fc7b-75e8fdfe8da5</v>
-    <v>es-MX</v>
-    <v>Generic</v>
-  </rv>
-  <rv s="0">
-    <v>805306368</v>
-    <v>Indira Kempis Martínez (Senado)</v>
-    <v>629dbce8-fc3f-30d3-d506-fe39dfc99c2b</v>
-    <v>es-MX</v>
-    <v>Generic</v>
-  </rv>
-  <rv s="0">
-    <v>805306368</v>
-    <v>Víctor Fuentes Solís (Senado)</v>
-    <v>36559353-006d-4597-a0d2-90f276433167</v>
+    <v>Miguel Ángel Navarro Quintero (Gobernador)</v>
+    <v>9c7bfc9a-aa60-6546-e3c6-45cbd406ee3a</v>
+    <v>es-MX</v>
+    <v>Generic</v>
+  </rv>
+  <rv s="0">
+    <v>805306368</v>
+    <v>Cora Cecilia Pinedo Alonso (Senado)</v>
+    <v>f837885e-514f-5905-b5c5-521ab79af917</v>
+    <v>es-MX</v>
+    <v>Generic</v>
+  </rv>
+  <rv s="0">
+    <v>805306368</v>
+    <v>Rosa Elena Jiménez Arteaga (Senado)</v>
+    <v>5122a1ed-f756-bfd1-92cc-bebc3513d078</v>
+    <v>es-MX</v>
+    <v>Generic</v>
+  </rv>
+  <rv s="0">
+    <v>805306368</v>
+    <v>Gloria Núñez Sánchez (Senado)</v>
+    <v>f66c991c-0fb0-29ef-7c75-1e3dad276c5d</v>
     <v>es-MX</v>
     <v>Generic</v>
   </rv>
@@ -3412,59 +3634,60 @@
     <v>25</v>
   </rv>
   <rv s="1">
-    <fb>5189970</fb>
-    <v>11</v>
-  </rv>
-  <rv s="6">
+    <fb>1235456</fb>
+    <v>11</v>
+  </rv>
+  <rv s="5">
     <v>#VALUE!</v>
     <v>es-ES</v>
-    <v>1696b325-bf35-b9aa-28db-3304c1996498</v>
+    <v>d5ab8703-9922-20b7-03c7-acb17f76b03e</v>
     <v>536870912</v>
     <v>1</v>
     <v>95</v>
     <v>4</v>
-    <v>18</v>
-    <v>Nuevo León</v>
+    <v>5</v>
+    <v>Nayarit</v>
     <v>7</v>
     <v>8</v>
     <v>Map</v>
     <v>9</v>
-    <v>46</v>
-    <v>MX-NLE</v>
-    <v>307</v>
-    <v>308</v>
-    <v>308</v>
-    <v>Nuevo León, oficialmente Estado Libre y Soberano de Nuevo León, es uno de los treinta y un estados que, junto con la Ciudad de México, conforman México. Su capital y ciudad más poblada es Monterrey. Está dividido en cincuenta y un municipios.</v>
+    <v>10</v>
+    <v>MX-NAY</v>
     <v>309</v>
     <v>310</v>
+    <v>310</v>
+    <v>Nayarit, oficialmente Estado Libre y Soberano de Nayarit, es uno de los treinta y un estados que, junto con la Ciudad de México, conforman México. Su capital y ciudad más poblada es Tepic. Está dividido en veinte municipios.</v>
     <v>311</v>
-    <v>316</v>
+    <v>312</v>
+    <v>313</v>
+    <v>318</v>
+    <v>Nayarit</v>
+    <v>11</v>
+    <v>319</v>
+    <v>Nayarit</v>
+    <v>mdp/vdpid/22833</v>
+    <v>83</v>
+  </rv>
+  <rv s="0">
+    <v>536870912</v>
     <v>Nuevo León</v>
-    <v>11</v>
-    <v>317</v>
-    <v>Nuevo León</v>
-    <v>mdp/vdpid/23942</v>
-  </rv>
-  <rv s="0">
-    <v>536870912</v>
-    <v>Oaxaca</v>
-    <v>2a651e2b-4cd2-6315-971b-6bddb30dfb4d</v>
+    <v>1696b325-bf35-b9aa-28db-3304c1996498</v>
     <v>es-ES</v>
     <v>Map</v>
   </rv>
   <rv s="1">
-    <fb>93793</fb>
-    <v>11</v>
-  </rv>
-  <rv s="0">
-    <v>536870912</v>
-    <v>Oaxaca de Juárez</v>
-    <v>cd8d901e-f100-1e0b-99df-6dc2beae5986</v>
-    <v>es-MX</v>
-    <v>Map</v>
-  </rv>
-  <rv s="1">
-    <fb>1090998</fb>
+    <fb>64156</fb>
+    <v>11</v>
+  </rv>
+  <rv s="0">
+    <v>536870912</v>
+    <v>Monterrey</v>
+    <v>7efc18c0-8c1d-eee3-2e2c-94beca244838</v>
+    <v>es-MX</v>
+    <v>Map</v>
+  </rv>
+  <rv s="1">
+    <fb>1430074</fb>
     <v>11</v>
   </rv>
   <rv s="2">
@@ -3473,37 +3696,37 @@
     <v>96</v>
     <v>7</v>
     <v>0</v>
-    <v>Image of Oaxaca</v>
+    <v>Image of Nuevo León</v>
   </rv>
   <rv s="3">
-    <v>https://www.bing.com/search?q=Oaxaca&amp;form=skydnc</v>
+    <v>https://www.bing.com/search?q=Nuevo+Le%c3%b3n&amp;form=skydnc</v>
     <v>Aprenda más con Bing</v>
   </rv>
   <rv s="0">
     <v>805306368</v>
-    <v>Salomón Jara Cruz (Gobernador)</v>
-    <v>bb5061df-261e-d82a-cf18-5cb9030d70e9</v>
-    <v>es-MX</v>
-    <v>Generic</v>
-  </rv>
-  <rv s="0">
-    <v>805306368</v>
-    <v>Susana Harp (Senado)</v>
-    <v>174b85a8-b36c-2c60-1216-067ddb5b3c5e</v>
-    <v>es-MX</v>
-    <v>Generic</v>
-  </rv>
-  <rv s="0">
-    <v>805306368</v>
-    <v>Adolfo Gómez Hernández (Senado)</v>
-    <v>bdea6849-fc18-c52e-1de9-8235854b4537</v>
-    <v>es-MX</v>
-    <v>Generic</v>
-  </rv>
-  <rv s="0">
-    <v>805306368</v>
-    <v>Raúl Bolaños-Cacho Cué (Senado)</v>
-    <v>550f511a-e23f-93dd-cd6d-68e7179a10b7</v>
+    <v>Samuel García (Gobernador)</v>
+    <v>54db8350-11f4-b808-4a4a-0698afc4f266</v>
+    <v>es-MX</v>
+    <v>Generic</v>
+  </rv>
+  <rv s="0">
+    <v>805306368</v>
+    <v>Luis David Ortíz Salinas (Senado)</v>
+    <v>18c286c4-64fd-19f9-fc7b-75e8fdfe8da5</v>
+    <v>es-MX</v>
+    <v>Generic</v>
+  </rv>
+  <rv s="0">
+    <v>805306368</v>
+    <v>Indira Kempis Martínez (Senado)</v>
+    <v>629dbce8-fc3f-30d3-d506-fe39dfc99c2b</v>
+    <v>es-MX</v>
+    <v>Generic</v>
+  </rv>
+  <rv s="0">
+    <v>805306368</v>
+    <v>Víctor Fuentes Solís (Senado)</v>
+    <v>36559353-006d-4597-a0d2-90f276433167</v>
     <v>es-MX</v>
     <v>Generic</v>
   </rv>
@@ -3511,60 +3734,59 @@
     <v>26</v>
   </rv>
   <rv s="1">
-    <fb>4132148</fb>
-    <v>11</v>
-  </rv>
-  <rv s="5">
+    <fb>5189970</fb>
+    <v>11</v>
+  </rv>
+  <rv s="6">
     <v>#VALUE!</v>
     <v>es-ES</v>
-    <v>2a651e2b-4cd2-6315-971b-6bddb30dfb4d</v>
+    <v>1696b325-bf35-b9aa-28db-3304c1996498</v>
     <v>536870912</v>
     <v>1</v>
     <v>98</v>
     <v>4</v>
-    <v>5</v>
-    <v>Oaxaca</v>
+    <v>18</v>
+    <v>Nuevo León</v>
     <v>7</v>
     <v>8</v>
     <v>Map</v>
     <v>9</v>
-    <v>10</v>
-    <v>MX-OAX</v>
-    <v>320</v>
-    <v>321</v>
-    <v>321</v>
-    <v>Oaxaca, oficialmente el Estado Libre y Soberano de Oaxaca, es uno de los treinta y un estados que, junto con la Ciudad de México, forman los Estados Unidos Mexicanos. Su capital y ciudad más poblada es Oaxaca de Juárez. Está dividido en 570 ...</v>
+    <v>46</v>
+    <v>MX-NLE</v>
     <v>322</v>
     <v>323</v>
+    <v>323</v>
+    <v>Nuevo León, oficialmente Estado Libre y Soberano de Nuevo León, es uno de los treinta y un estados que, junto con la Ciudad de México, conforman México. Su capital y ciudad más poblada es Monterrey. Está dividido en cincuenta y un municipios.</v>
     <v>324</v>
-    <v>329</v>
+    <v>325</v>
+    <v>326</v>
+    <v>331</v>
+    <v>Nuevo León</v>
+    <v>11</v>
+    <v>332</v>
+    <v>Nuevo León</v>
+    <v>mdp/vdpid/23942</v>
+  </rv>
+  <rv s="0">
+    <v>536870912</v>
     <v>Oaxaca</v>
-    <v>11</v>
-    <v>330</v>
-    <v>Oaxaca</v>
-    <v>mdp/vdpid/24073</v>
-    <v>13</v>
-  </rv>
-  <rv s="0">
-    <v>536870912</v>
-    <v>Puebla</v>
-    <v>e266f3f0-af5e-7537-36e1-118cfcc783a3</v>
+    <v>2a651e2b-4cd2-6315-971b-6bddb30dfb4d</v>
     <v>es-ES</v>
     <v>Map</v>
   </rv>
   <rv s="1">
-    <fb>34306</fb>
-    <v>11</v>
-  </rv>
-  <rv s="0">
-    <v>536870912</v>
-    <v>Puebla de Zaragoza</v>
-    <v>b788c1f6-f16e-53de-050e-1f3553893258</v>
-    <v>es-MX</v>
-    <v>Map</v>
-  </rv>
-  <rv s="1">
-    <fb>1647266</fb>
+    <fb>93793</fb>
+    <v>11</v>
+  </rv>
+  <rv s="0">
+    <v>536870912</v>
+    <v>Oaxaca de Juárez</v>
+    <v>cd8d901e-f100-1e0b-99df-6dc2beae5986</v>
+    <v>es-MX</v>
+    <v>Map</v>
+  </rv>
+  <rv s="1">
+    <fb>1090998</fb>
     <v>11</v>
   </rv>
   <rv s="2">
@@ -3573,37 +3795,37 @@
     <v>99</v>
     <v>7</v>
     <v>0</v>
-    <v>Image of Puebla</v>
+    <v>Image of Oaxaca</v>
   </rv>
   <rv s="3">
-    <v>https://www.bing.com/search?q=Puebla&amp;form=skydnc</v>
+    <v>https://www.bing.com/search?q=Oaxaca&amp;form=skydnc</v>
     <v>Aprenda más con Bing</v>
   </rv>
   <rv s="0">
     <v>805306368</v>
-    <v>Sergio Salomón Céspedes (Gobernador)</v>
-    <v>8d53de06-7c1b-7c4d-fd29-f5d5cfc2700e</v>
-    <v>es-MX</v>
-    <v>Generic</v>
-  </rv>
-  <rv s="0">
-    <v>805306368</v>
-    <v>Alejandro Armenta Mier (Senado)</v>
-    <v>04d5dda8-414a-8839-b8b6-2b6fa050f392</v>
-    <v>es-MX</v>
-    <v>Generic</v>
-  </rv>
-  <rv s="0">
-    <v>805306368</v>
-    <v>Nancy de la Sierra Aramburo (Senado)</v>
-    <v>798d0a8a-9f53-68b1-367c-bc6537577f8a</v>
-    <v>es-MX</v>
-    <v>Generic</v>
-  </rv>
-  <rv s="0">
-    <v>805306368</v>
-    <v>Nadia Navarro Acevedo (Senado)</v>
-    <v>e901e19b-f6bd-b2a5-4c9e-46e244d05828</v>
+    <v>Salomón Jara Cruz (Gobernador)</v>
+    <v>bb5061df-261e-d82a-cf18-5cb9030d70e9</v>
+    <v>es-MX</v>
+    <v>Generic</v>
+  </rv>
+  <rv s="0">
+    <v>805306368</v>
+    <v>Susana Harp (Senado)</v>
+    <v>174b85a8-b36c-2c60-1216-067ddb5b3c5e</v>
+    <v>es-MX</v>
+    <v>Generic</v>
+  </rv>
+  <rv s="0">
+    <v>805306368</v>
+    <v>Adolfo Gómez Hernández (Senado)</v>
+    <v>bdea6849-fc18-c52e-1de9-8235854b4537</v>
+    <v>es-MX</v>
+    <v>Generic</v>
+  </rv>
+  <rv s="0">
+    <v>805306368</v>
+    <v>Raúl Bolaños-Cacho Cué (Senado)</v>
+    <v>550f511a-e23f-93dd-cd6d-68e7179a10b7</v>
     <v>es-MX</v>
     <v>Generic</v>
   </rv>
@@ -3611,59 +3833,60 @@
     <v>27</v>
   </rv>
   <rv s="1">
-    <fb>6168883</fb>
-    <v>11</v>
-  </rv>
-  <rv s="6">
+    <fb>4132148</fb>
+    <v>11</v>
+  </rv>
+  <rv s="5">
     <v>#VALUE!</v>
     <v>es-ES</v>
-    <v>e266f3f0-af5e-7537-36e1-118cfcc783a3</v>
+    <v>2a651e2b-4cd2-6315-971b-6bddb30dfb4d</v>
     <v>536870912</v>
     <v>1</v>
     <v>101</v>
     <v>4</v>
-    <v>18</v>
-    <v>Puebla</v>
+    <v>5</v>
+    <v>Oaxaca</v>
     <v>7</v>
     <v>8</v>
     <v>Map</v>
     <v>9</v>
-    <v>46</v>
-    <v>MX-PUE</v>
-    <v>333</v>
-    <v>334</v>
-    <v>334</v>
-    <v>Puebla, oficialmente el Estado Libre y Soberano de Puebla, es uno de los treinta y un estados que, junto con la Ciudad de México, conforman México; ubicado en el altiplano central de México, su capital y ciudad más grande es Puebla de Zaragoza. ...</v>
+    <v>10</v>
+    <v>MX-OAX</v>
     <v>335</v>
     <v>336</v>
+    <v>336</v>
+    <v>Oaxaca, oficialmente el Estado Libre y Soberano de Oaxaca, es uno de los treinta y un estados que, junto con la Ciudad de México, forman los Estados Unidos Mexicanos. Su capital y ciudad más poblada es Oaxaca de Juárez. Está dividido en 570 ...</v>
     <v>337</v>
-    <v>342</v>
+    <v>338</v>
+    <v>339</v>
+    <v>344</v>
+    <v>Oaxaca</v>
+    <v>11</v>
+    <v>345</v>
+    <v>Oaxaca</v>
+    <v>mdp/vdpid/24073</v>
+    <v>13</v>
+  </rv>
+  <rv s="0">
+    <v>536870912</v>
     <v>Puebla</v>
-    <v>11</v>
-    <v>343</v>
-    <v>Puebla</v>
-    <v>mdp/vdpid/26816</v>
-  </rv>
-  <rv s="0">
-    <v>536870912</v>
-    <v>Querétaro</v>
-    <v>4a2d4179-0f55-70d5-99e7-165b2289a273</v>
+    <v>e266f3f0-af5e-7537-36e1-118cfcc783a3</v>
     <v>es-ES</v>
     <v>Map</v>
   </rv>
   <rv s="1">
-    <fb>11699</fb>
-    <v>11</v>
-  </rv>
-  <rv s="0">
-    <v>536870912</v>
-    <v>Santiago de Querétaro</v>
-    <v>ec2a2278-4e06-2076-4a85-ced55489bf6f</v>
-    <v>es-MX</v>
-    <v>Map</v>
-  </rv>
-  <rv s="1">
-    <fb>555579</fb>
+    <fb>34306</fb>
+    <v>11</v>
+  </rv>
+  <rv s="0">
+    <v>536870912</v>
+    <v>Puebla de Zaragoza</v>
+    <v>b788c1f6-f16e-53de-050e-1f3553893258</v>
+    <v>es-MX</v>
+    <v>Map</v>
+  </rv>
+  <rv s="1">
+    <fb>1647266</fb>
     <v>11</v>
   </rv>
   <rv s="2">
@@ -3672,37 +3895,37 @@
     <v>102</v>
     <v>7</v>
     <v>0</v>
-    <v>Image of Querétaro</v>
+    <v>Image of Puebla</v>
   </rv>
   <rv s="3">
-    <v>https://www.bing.com/search?q=Quer%c3%a9taro&amp;form=skydnc</v>
+    <v>https://www.bing.com/search?q=Puebla&amp;form=skydnc</v>
     <v>Aprenda más con Bing</v>
   </rv>
   <rv s="0">
     <v>805306368</v>
-    <v>Mauricio Kuri (Gobernador)</v>
-    <v>3eda8212-0873-5135-1b54-a65ba6e5f1c6</v>
-    <v>es-MX</v>
-    <v>Generic</v>
-  </rv>
-  <rv s="0">
-    <v>805306368</v>
-    <v>Alfredo Botello Montes (Senado)</v>
-    <v>c50d98b4-3879-247d-8158-e717aa5f887d</v>
-    <v>es-MX</v>
-    <v>Generic</v>
-  </rv>
-  <rv s="0">
-    <v>805306368</v>
-    <v>Estrella Rojas Loreto (Senado)</v>
-    <v>56790dd4-cfee-6f10-7685-dfdf5d442a9f</v>
-    <v>es-MX</v>
-    <v>Generic</v>
-  </rv>
-  <rv s="0">
-    <v>805306368</v>
-    <v>Gilberto Herrera Ruiz (Senado)</v>
-    <v>de388552-e909-2107-ffd7-d110fb09cb89</v>
+    <v>Sergio Salomón Céspedes (Gobernador)</v>
+    <v>8d53de06-7c1b-7c4d-fd29-f5d5cfc2700e</v>
+    <v>es-MX</v>
+    <v>Generic</v>
+  </rv>
+  <rv s="0">
+    <v>805306368</v>
+    <v>Alejandro Armenta Mier (Senado)</v>
+    <v>04d5dda8-414a-8839-b8b6-2b6fa050f392</v>
+    <v>es-MX</v>
+    <v>Generic</v>
+  </rv>
+  <rv s="0">
+    <v>805306368</v>
+    <v>Nancy de la Sierra Aramburo (Senado)</v>
+    <v>798d0a8a-9f53-68b1-367c-bc6537577f8a</v>
+    <v>es-MX</v>
+    <v>Generic</v>
+  </rv>
+  <rv s="0">
+    <v>805306368</v>
+    <v>Nadia Navarro Acevedo (Senado)</v>
+    <v>e901e19b-f6bd-b2a5-4c9e-46e244d05828</v>
     <v>es-MX</v>
     <v>Generic</v>
   </rv>
@@ -3710,67 +3933,59 @@
     <v>28</v>
   </rv>
   <rv s="1">
-    <fb>2368467</fb>
-    <v>11</v>
-  </rv>
-  <rv s="5">
+    <fb>6168883</fb>
+    <v>11</v>
+  </rv>
+  <rv s="6">
     <v>#VALUE!</v>
     <v>es-ES</v>
-    <v>4a2d4179-0f55-70d5-99e7-165b2289a273</v>
+    <v>e266f3f0-af5e-7537-36e1-118cfcc783a3</v>
     <v>536870912</v>
     <v>1</v>
     <v>104</v>
     <v>4</v>
-    <v>5</v>
-    <v>Querétaro</v>
+    <v>18</v>
+    <v>Puebla</v>
     <v>7</v>
     <v>8</v>
     <v>Map</v>
     <v>9</v>
-    <v>10</v>
-    <v>MX-QUE</v>
-    <v>346</v>
-    <v>347</v>
-    <v>347</v>
-    <v>Querétaro, oficialmente el Estado Libre y Soberano de Querétaro, es uno de los treinta y un estados que, junto con la Ciudad de México, forman México. Su capital y ciudad más poblada es Santiago de Querétaro. Está ubicado en la región ...</v>
+    <v>46</v>
+    <v>MX-PUE</v>
     <v>348</v>
     <v>349</v>
+    <v>349</v>
+    <v>Puebla, oficialmente el Estado Libre y Soberano de Puebla, es uno de los treinta y un estados que, junto con la Ciudad de México, conforman México; ubicado en el altiplano central de México, su capital y ciudad más grande es Puebla de Zaragoza. ...</v>
     <v>350</v>
-    <v>355</v>
+    <v>351</v>
+    <v>352</v>
+    <v>357</v>
+    <v>Puebla</v>
+    <v>11</v>
+    <v>358</v>
+    <v>Puebla</v>
+    <v>mdp/vdpid/26816</v>
+  </rv>
+  <rv s="0">
+    <v>536870912</v>
     <v>Querétaro</v>
-    <v>54</v>
-    <v>356</v>
-    <v>Querétaro</v>
-    <v>mdp/vdpid/27102</v>
-    <v>13</v>
-  </rv>
-  <rv s="0">
-    <v>536870912</v>
-    <v>Quintana Roo</v>
-    <v>96bcffec-8d1c-5e86-ab0e-e31d5b9a157c</v>
+    <v>4a2d4179-0f55-70d5-99e7-165b2289a273</v>
     <v>es-ES</v>
     <v>Map</v>
   </rv>
   <rv s="1">
-    <fb>44705</fb>
-    <v>11</v>
-  </rv>
-  <rv s="0">
-    <v>536870912</v>
-    <v>Chetumal</v>
-    <v>07427ec2-8f52-94ff-e0d7-7a9a611f2996</v>
-    <v>es-MX</v>
-    <v>Map</v>
-  </rv>
-  <rv s="0">
-    <v>536870912</v>
-    <v>Cancún</v>
-    <v>f5106a5a-2c36-727c-cd65-16ed42559291</v>
-    <v>es-MX</v>
-    <v>Map</v>
-  </rv>
-  <rv s="1">
-    <fb>517924</fb>
+    <fb>11699</fb>
+    <v>11</v>
+  </rv>
+  <rv s="0">
+    <v>536870912</v>
+    <v>Santiago de Querétaro</v>
+    <v>ec2a2278-4e06-2076-4a85-ced55489bf6f</v>
+    <v>es-MX</v>
+    <v>Map</v>
+  </rv>
+  <rv s="1">
+    <fb>555579</fb>
     <v>11</v>
   </rv>
   <rv s="2">
@@ -3779,16 +3994,37 @@
     <v>105</v>
     <v>7</v>
     <v>0</v>
-    <v>Image of Quintana Roo</v>
+    <v>Image of Querétaro</v>
   </rv>
   <rv s="3">
-    <v>https://www.bing.com/search?q=Quintana+Roo&amp;form=skydnc</v>
+    <v>https://www.bing.com/search?q=Quer%c3%a9taro&amp;form=skydnc</v>
     <v>Aprenda más con Bing</v>
   </rv>
   <rv s="0">
     <v>805306368</v>
-    <v>Mara Lezama (Gobernador)</v>
-    <v>4d4e36d5-fd74-56ab-dca7-c97354c29094</v>
+    <v>Mauricio Kuri (Gobernador)</v>
+    <v>3eda8212-0873-5135-1b54-a65ba6e5f1c6</v>
+    <v>es-MX</v>
+    <v>Generic</v>
+  </rv>
+  <rv s="0">
+    <v>805306368</v>
+    <v>Alfredo Botello Montes (Senado)</v>
+    <v>c50d98b4-3879-247d-8158-e717aa5f887d</v>
+    <v>es-MX</v>
+    <v>Generic</v>
+  </rv>
+  <rv s="0">
+    <v>805306368</v>
+    <v>Estrella Rojas Loreto (Senado)</v>
+    <v>56790dd4-cfee-6f10-7685-dfdf5d442a9f</v>
+    <v>es-MX</v>
+    <v>Generic</v>
+  </rv>
+  <rv s="0">
+    <v>805306368</v>
+    <v>Gilberto Herrera Ruiz (Senado)</v>
+    <v>de388552-e909-2107-ffd7-d110fb09cb89</v>
     <v>es-MX</v>
     <v>Generic</v>
   </rv>
@@ -3796,59 +4032,67 @@
     <v>29</v>
   </rv>
   <rv s="1">
-    <fb>1857985</fb>
-    <v>11</v>
-  </rv>
-  <rv s="6">
+    <fb>2368467</fb>
+    <v>11</v>
+  </rv>
+  <rv s="5">
     <v>#VALUE!</v>
     <v>es-ES</v>
-    <v>96bcffec-8d1c-5e86-ab0e-e31d5b9a157c</v>
+    <v>4a2d4179-0f55-70d5-99e7-165b2289a273</v>
     <v>536870912</v>
     <v>1</v>
     <v>107</v>
     <v>4</v>
-    <v>18</v>
-    <v>Quintana Roo</v>
+    <v>5</v>
+    <v>Querétaro</v>
     <v>7</v>
     <v>8</v>
     <v>Map</v>
     <v>9</v>
     <v>10</v>
-    <v>MX-ROO</v>
-    <v>359</v>
-    <v>360</v>
+    <v>MX-QUE</v>
     <v>361</v>
-    <v>Quintana Roo, oficialmente el Estado Libre y Soberano de Quintana Roo, es uno de los treinta y un estados que, junto con la Ciudad de México, conforman México. Su capital es Chetumal y su ciudad más poblada es Cancún. Está ubicado en la ...</v>
     <v>362</v>
+    <v>362</v>
+    <v>Querétaro, oficialmente el Estado Libre y Soberano de Querétaro, es uno de los treinta y un estados que, junto con la Ciudad de México, forman México. Su capital y ciudad más poblada es Santiago de Querétaro. Está ubicado en la región ...</v>
     <v>363</v>
     <v>364</v>
-    <v>366</v>
+    <v>365</v>
+    <v>370</v>
+    <v>Querétaro</v>
+    <v>54</v>
+    <v>371</v>
+    <v>Querétaro</v>
+    <v>mdp/vdpid/27102</v>
+    <v>13</v>
+  </rv>
+  <rv s="0">
+    <v>536870912</v>
     <v>Quintana Roo</v>
-    <v>11</v>
-    <v>367</v>
-    <v>Quintana Roo</v>
-    <v>mdp/vdpid/27144</v>
-  </rv>
-  <rv s="0">
-    <v>536870912</v>
-    <v>San Luis Potosí</v>
-    <v>c228dff2-2024-525b-1b90-fe82a2f5ccfc</v>
+    <v>96bcffec-8d1c-5e86-ab0e-e31d5b9a157c</v>
     <v>es-ES</v>
     <v>Map</v>
   </rv>
   <rv s="1">
-    <fb>60983</fb>
-    <v>11</v>
-  </rv>
-  <rv s="0">
-    <v>536870912</v>
-    <v>San Luis Potosí</v>
-    <v>4b91e16d-bb25-5c92-09f7-c82710d38a37</v>
-    <v>es-MX</v>
-    <v>Map</v>
-  </rv>
-  <rv s="1">
-    <fb>764696</fb>
+    <fb>44705</fb>
+    <v>11</v>
+  </rv>
+  <rv s="0">
+    <v>536870912</v>
+    <v>Chetumal</v>
+    <v>07427ec2-8f52-94ff-e0d7-7a9a611f2996</v>
+    <v>es-MX</v>
+    <v>Map</v>
+  </rv>
+  <rv s="0">
+    <v>536870912</v>
+    <v>Cancún</v>
+    <v>f5106a5a-2c36-727c-cd65-16ed42559291</v>
+    <v>es-MX</v>
+    <v>Map</v>
+  </rv>
+  <rv s="1">
+    <fb>517924</fb>
     <v>11</v>
   </rv>
   <rv s="2">
@@ -3857,37 +4101,16 @@
     <v>108</v>
     <v>7</v>
     <v>0</v>
-    <v>Image of San Luis Potosí</v>
+    <v>Image of Quintana Roo</v>
   </rv>
   <rv s="3">
-    <v>https://www.bing.com/search?q=San+Luis+Potos%c3%ad&amp;form=skydnc</v>
+    <v>https://www.bing.com/search?q=Quintana+Roo&amp;form=skydnc</v>
     <v>Aprenda más con Bing</v>
   </rv>
   <rv s="0">
     <v>805306368</v>
-    <v>Ricardo Gallardo Cardona (Gobernador)</v>
-    <v>87d664f3-034e-01f0-9b26-b04a3e524a09</v>
-    <v>es-MX</v>
-    <v>Generic</v>
-  </rv>
-  <rv s="0">
-    <v>805306368</v>
-    <v>Marco Antonio Gama Basarte (Senado)</v>
-    <v>a8c63e75-21bf-dbad-50ea-a65e014fe89c</v>
-    <v>es-MX</v>
-    <v>Generic</v>
-  </rv>
-  <rv s="0">
-    <v>805306368</v>
-    <v>Graciela Gaitán Díaz (Senado)</v>
-    <v>4388e690-ddbf-8610-24fd-f8c4e1fee66b</v>
-    <v>es-MX</v>
-    <v>Generic</v>
-  </rv>
-  <rv s="0">
-    <v>805306368</v>
-    <v>Elí César Cervantes Rojas (Senado)</v>
-    <v>ba2a121b-0ffb-fb61-f523-f9674c5cde22</v>
+    <v>Mara Lezama (Gobernador)</v>
+    <v>4d4e36d5-fd74-56ab-dca7-c97354c29094</v>
     <v>es-MX</v>
     <v>Generic</v>
   </rv>
@@ -3895,59 +4118,59 @@
     <v>30</v>
   </rv>
   <rv s="1">
-    <fb>2717820</fb>
+    <fb>1857985</fb>
     <v>11</v>
   </rv>
   <rv s="6">
     <v>#VALUE!</v>
     <v>es-ES</v>
-    <v>c228dff2-2024-525b-1b90-fe82a2f5ccfc</v>
+    <v>96bcffec-8d1c-5e86-ab0e-e31d5b9a157c</v>
     <v>536870912</v>
     <v>1</v>
     <v>110</v>
     <v>4</v>
     <v>18</v>
-    <v>San Luis Potosí</v>
+    <v>Quintana Roo</v>
     <v>7</v>
     <v>8</v>
     <v>Map</v>
     <v>9</v>
-    <v>46</v>
-    <v>MX-SLP</v>
-    <v>370</v>
-    <v>371</v>
-    <v>371</v>
-    <v>San Luis Potosí, oficialmente llamado Estado Libre y Soberano de San Luis Potosí, es uno de los treinta y un estados que, junto con la Ciudad de México, conforman México. Su capital y ciudad más poblada es la homónima San Luis Potosí.</v>
-    <v>372</v>
-    <v>373</v>
+    <v>10</v>
+    <v>MX-ROO</v>
     <v>374</v>
+    <v>375</v>
+    <v>376</v>
+    <v>Quintana Roo, oficialmente el Estado Libre y Soberano de Quintana Roo, es uno de los treinta y un estados que, junto con la Ciudad de México, conforman México. Su capital es Chetumal y su ciudad más poblada es Cancún. Está ubicado en la ...</v>
+    <v>377</v>
+    <v>378</v>
     <v>379</v>
+    <v>381</v>
+    <v>Quintana Roo</v>
+    <v>11</v>
+    <v>382</v>
+    <v>Quintana Roo</v>
+    <v>mdp/vdpid/27144</v>
+  </rv>
+  <rv s="0">
+    <v>536870912</v>
     <v>San Luis Potosí</v>
-    <v>11</v>
-    <v>380</v>
+    <v>c228dff2-2024-525b-1b90-fe82a2f5ccfc</v>
+    <v>es-ES</v>
+    <v>Map</v>
+  </rv>
+  <rv s="1">
+    <fb>60983</fb>
+    <v>11</v>
+  </rv>
+  <rv s="0">
+    <v>536870912</v>
     <v>San Luis Potosí</v>
-    <v>mdp/vdpid/29355</v>
-  </rv>
-  <rv s="0">
-    <v>536870912</v>
-    <v>Sinaloa</v>
-    <v>ef7dcafc-cca2-39b2-e063-e2bbf5b2022e</v>
-    <v>es-ES</v>
-    <v>Map</v>
-  </rv>
-  <rv s="1">
-    <fb>57377</fb>
-    <v>11</v>
-  </rv>
-  <rv s="0">
-    <v>536870912</v>
-    <v>Culiacán</v>
-    <v>cf314b38-177a-0d75-a8de-7bcb83a34b47</v>
-    <v>es-MX</v>
-    <v>Map</v>
-  </rv>
-  <rv s="1">
-    <fb>860602</fb>
+    <v>4b91e16d-bb25-5c92-09f7-c82710d38a37</v>
+    <v>es-MX</v>
+    <v>Map</v>
+  </rv>
+  <rv s="1">
+    <fb>764696</fb>
     <v>11</v>
   </rv>
   <rv s="2">
@@ -3956,37 +4179,37 @@
     <v>111</v>
     <v>7</v>
     <v>0</v>
-    <v>Image of Sinaloa</v>
+    <v>Image of San Luis Potosí</v>
   </rv>
   <rv s="3">
-    <v>https://www.bing.com/search?q=Sinaloa&amp;form=skydnc</v>
+    <v>https://www.bing.com/search?q=San+Luis+Potos%c3%ad&amp;form=skydnc</v>
     <v>Aprenda más con Bing</v>
   </rv>
   <rv s="0">
     <v>805306368</v>
-    <v>Rubén Rocha Moya (Gobernador)</v>
-    <v>30534af2-76ad-31ad-b0af-f85eed5ad27f</v>
-    <v>es-MX</v>
-    <v>Generic</v>
-  </rv>
-  <rv s="0">
-    <v>805306368</v>
-    <v>Raúl de Jesús Elenes Angulo (Senado)</v>
-    <v>87a79327-2583-cf6b-faa4-6df9fc8b90cf</v>
-    <v>es-MX</v>
-    <v>Generic</v>
-  </rv>
-  <rv s="0">
-    <v>805306368</v>
-    <v>Imelda Castro Castro (Senado)</v>
-    <v>612d2ecf-82c7-a76a-1581-3f5045e0bf5d</v>
-    <v>es-MX</v>
-    <v>Generic</v>
-  </rv>
-  <rv s="0">
-    <v>805306368</v>
-    <v>Mario Zamora Gastélum (Senado)</v>
-    <v>b3742f53-014f-9660-ba34-7206dd93ea20</v>
+    <v>Ricardo Gallardo Cardona (Gobernador)</v>
+    <v>87d664f3-034e-01f0-9b26-b04a3e524a09</v>
+    <v>es-MX</v>
+    <v>Generic</v>
+  </rv>
+  <rv s="0">
+    <v>805306368</v>
+    <v>Marco Antonio Gama Basarte (Senado)</v>
+    <v>a8c63e75-21bf-dbad-50ea-a65e014fe89c</v>
+    <v>es-MX</v>
+    <v>Generic</v>
+  </rv>
+  <rv s="0">
+    <v>805306368</v>
+    <v>Graciela Gaitán Díaz (Senado)</v>
+    <v>4388e690-ddbf-8610-24fd-f8c4e1fee66b</v>
+    <v>es-MX</v>
+    <v>Generic</v>
+  </rv>
+  <rv s="0">
+    <v>805306368</v>
+    <v>Elí César Cervantes Rojas (Senado)</v>
+    <v>ba2a121b-0ffb-fb61-f523-f9674c5cde22</v>
     <v>es-MX</v>
     <v>Generic</v>
   </rv>
@@ -3994,59 +4217,59 @@
     <v>31</v>
   </rv>
   <rv s="1">
-    <fb>2966700</fb>
+    <fb>2717820</fb>
     <v>11</v>
   </rv>
   <rv s="6">
     <v>#VALUE!</v>
     <v>es-ES</v>
-    <v>ef7dcafc-cca2-39b2-e063-e2bbf5b2022e</v>
+    <v>c228dff2-2024-525b-1b90-fe82a2f5ccfc</v>
     <v>536870912</v>
     <v>1</v>
     <v>113</v>
     <v>4</v>
     <v>18</v>
-    <v>Sinaloa</v>
+    <v>San Luis Potosí</v>
     <v>7</v>
     <v>8</v>
     <v>Map</v>
     <v>9</v>
     <v>46</v>
-    <v>MX-SIN</v>
-    <v>383</v>
-    <v>384</v>
-    <v>384</v>
-    <v>Sinaloa, oficialmente Estado Libre y Soberano de Sinaloa, es uno de los treinta y un estados que, junto con la Ciudad de México, conforman México. Está ubicado en la región noroeste del país, limitando al norte con Sonora y Chihuahua, al este ...</v>
+    <v>MX-SLP</v>
     <v>385</v>
     <v>386</v>
+    <v>386</v>
+    <v>San Luis Potosí, oficialmente llamado Estado Libre y Soberano de San Luis Potosí, es uno de los treinta y un estados que, junto con la Ciudad de México, conforman México. Su capital y ciudad más poblada es la homónima San Luis Potosí.</v>
     <v>387</v>
-    <v>392</v>
+    <v>388</v>
+    <v>389</v>
+    <v>394</v>
+    <v>San Luis Potosí</v>
+    <v>11</v>
+    <v>395</v>
+    <v>San Luis Potosí</v>
+    <v>mdp/vdpid/29355</v>
+  </rv>
+  <rv s="0">
+    <v>536870912</v>
     <v>Sinaloa</v>
-    <v>11</v>
-    <v>393</v>
-    <v>Sinaloa</v>
-    <v>mdp/vdpid/30942</v>
-  </rv>
-  <rv s="0">
-    <v>536870912</v>
-    <v>Sonora</v>
-    <v>e59e4f16-5e42-af6e-b970-e0ae59046077</v>
+    <v>ef7dcafc-cca2-39b2-e063-e2bbf5b2022e</v>
     <v>es-ES</v>
     <v>Map</v>
   </rv>
   <rv s="1">
-    <fb>179503</fb>
-    <v>11</v>
-  </rv>
-  <rv s="0">
-    <v>536870912</v>
-    <v>Hermosillo</v>
-    <v>4bfe22c7-30ec-d811-cf08-ce47ada19d95</v>
-    <v>es-MX</v>
-    <v>Map</v>
-  </rv>
-  <rv s="1">
-    <fb>909002</fb>
+    <fb>57377</fb>
+    <v>11</v>
+  </rv>
+  <rv s="0">
+    <v>536870912</v>
+    <v>Culiacán</v>
+    <v>cf314b38-177a-0d75-a8de-7bcb83a34b47</v>
+    <v>es-MX</v>
+    <v>Map</v>
+  </rv>
+  <rv s="1">
+    <fb>860602</fb>
     <v>11</v>
   </rv>
   <rv s="2">
@@ -4055,37 +4278,37 @@
     <v>114</v>
     <v>7</v>
     <v>0</v>
-    <v>Image of Sonora</v>
+    <v>Image of Sinaloa</v>
   </rv>
   <rv s="3">
-    <v>https://www.bing.com/search?q=Sonora&amp;form=skydnc</v>
+    <v>https://www.bing.com/search?q=Sinaloa&amp;form=skydnc</v>
     <v>Aprenda más con Bing</v>
   </rv>
   <rv s="0">
     <v>805306368</v>
-    <v>Alfonso Durazo Montaño (Gobernador)</v>
-    <v>1bf2764a-b01c-b260-be29-7f0d8c919518</v>
-    <v>es-MX</v>
-    <v>Generic</v>
-  </rv>
-  <rv s="0">
-    <v>805306368</v>
-    <v>Arturo Bours Griffith (Senado)</v>
-    <v>b9fe33c2-01ce-b279-9100-57d261fa7c50</v>
-    <v>es-MX</v>
-    <v>Generic</v>
-  </rv>
-  <rv s="0">
-    <v>805306368</v>
-    <v>Lilly Téllez (Senado)</v>
-    <v>0b70f1ce-280f-0c82-7747-7e30db7086ce</v>
-    <v>es-MX</v>
-    <v>Generic</v>
-  </rv>
-  <rv s="0">
-    <v>805306368</v>
-    <v>Sylvana Beltrones Sánchez (Senado)</v>
-    <v>fd1e46b2-0f99-5c78-0bf0-05f2b5bdccfc</v>
+    <v>Rubén Rocha Moya (Gobernador)</v>
+    <v>30534af2-76ad-31ad-b0af-f85eed5ad27f</v>
+    <v>es-MX</v>
+    <v>Generic</v>
+  </rv>
+  <rv s="0">
+    <v>805306368</v>
+    <v>Raúl de Jesús Elenes Angulo (Senado)</v>
+    <v>87a79327-2583-cf6b-faa4-6df9fc8b90cf</v>
+    <v>es-MX</v>
+    <v>Generic</v>
+  </rv>
+  <rv s="0">
+    <v>805306368</v>
+    <v>Imelda Castro Castro (Senado)</v>
+    <v>612d2ecf-82c7-a76a-1581-3f5045e0bf5d</v>
+    <v>es-MX</v>
+    <v>Generic</v>
+  </rv>
+  <rv s="0">
+    <v>805306368</v>
+    <v>Mario Zamora Gastélum (Senado)</v>
+    <v>b3742f53-014f-9660-ba34-7206dd93ea20</v>
     <v>es-MX</v>
     <v>Generic</v>
   </rv>
@@ -4093,59 +4316,59 @@
     <v>32</v>
   </rv>
   <rv s="1">
-    <fb>2850330</fb>
+    <fb>2966700</fb>
     <v>11</v>
   </rv>
   <rv s="6">
     <v>#VALUE!</v>
     <v>es-ES</v>
-    <v>e59e4f16-5e42-af6e-b970-e0ae59046077</v>
+    <v>ef7dcafc-cca2-39b2-e063-e2bbf5b2022e</v>
     <v>536870912</v>
     <v>1</v>
     <v>116</v>
     <v>4</v>
     <v>18</v>
-    <v>Sonora</v>
+    <v>Sinaloa</v>
     <v>7</v>
     <v>8</v>
     <v>Map</v>
     <v>9</v>
     <v>46</v>
-    <v>MX-SON</v>
-    <v>396</v>
-    <v>397</v>
-    <v>397</v>
-    <v>Sonora, oficialmente llamado Estado Libre y Soberano de Sonora, es uno de los treinta y un estados que, junto con la Ciudad de México, conforman México. Su capital y ciudad más poblada es Hermosillo. Está ubicado en la región noroeste del país, ...</v>
+    <v>MX-SIN</v>
     <v>398</v>
     <v>399</v>
+    <v>399</v>
+    <v>Sinaloa, oficialmente Estado Libre y Soberano de Sinaloa, es uno de los treinta y un estados que, junto con la Ciudad de México, conforman México. Está ubicado en la región noroeste del país, limitando al norte con Sonora y Chihuahua, al este ...</v>
     <v>400</v>
-    <v>405</v>
+    <v>401</v>
+    <v>402</v>
+    <v>407</v>
+    <v>Sinaloa</v>
+    <v>11</v>
+    <v>408</v>
+    <v>Sinaloa</v>
+    <v>mdp/vdpid/30942</v>
+  </rv>
+  <rv s="0">
+    <v>536870912</v>
     <v>Sonora</v>
-    <v>11</v>
-    <v>406</v>
-    <v>Sonora</v>
-    <v>mdp/vdpid/31328</v>
-  </rv>
-  <rv s="0">
-    <v>536870912</v>
-    <v>Tabasco</v>
-    <v>f96880d9-0a36-58d3-7351-a4c7070c642d</v>
+    <v>e59e4f16-5e42-af6e-b970-e0ae59046077</v>
     <v>es-ES</v>
     <v>Map</v>
   </rv>
   <rv s="1">
-    <fb>24738</fb>
-    <v>11</v>
-  </rv>
-  <rv s="0">
-    <v>536870912</v>
-    <v>Villahermosa</v>
-    <v>7171e244-bb41-21fc-8ea3-b2e3210ed2a9</v>
-    <v>es-MX</v>
-    <v>Map</v>
-  </rv>
-  <rv s="1">
-    <fb>678859</fb>
+    <fb>179503</fb>
+    <v>11</v>
+  </rv>
+  <rv s="0">
+    <v>536870912</v>
+    <v>Hermosillo</v>
+    <v>4bfe22c7-30ec-d811-cf08-ce47ada19d95</v>
+    <v>es-MX</v>
+    <v>Map</v>
+  </rv>
+  <rv s="1">
+    <fb>909002</fb>
     <v>11</v>
   </rv>
   <rv s="2">
@@ -4154,37 +4377,37 @@
     <v>117</v>
     <v>7</v>
     <v>0</v>
-    <v>Image of Tabasco</v>
+    <v>Image of Sonora</v>
   </rv>
   <rv s="3">
-    <v>https://www.bing.com/search?q=Tabasco&amp;form=skydnc</v>
+    <v>https://www.bing.com/search?q=Sonora&amp;form=skydnc</v>
     <v>Aprenda más con Bing</v>
   </rv>
   <rv s="0">
     <v>805306368</v>
-    <v>Javier May Rodríguez (Gobernador)</v>
-    <v>eb064643-d95a-5b4f-e5c7-309080a1dbba</v>
-    <v>es-MX</v>
-    <v>Generic</v>
-  </rv>
-  <rv s="0">
-    <v>805306368</v>
-    <v>Adriana Manzanilla Fojaco (Senado)</v>
-    <v>92be806f-98f8-0da8-e5e0-3a837aacc554</v>
-    <v>es-MX</v>
-    <v>Generic</v>
-  </rv>
-  <rv s="0">
-    <v>805306368</v>
-    <v>Ovidio Peralta Suárez (Senado)</v>
-    <v>cd00d941-4447-7e55-8a34-e3393b2ebb2f</v>
-    <v>es-MX</v>
-    <v>Generic</v>
-  </rv>
-  <rv s="0">
-    <v>805306368</v>
-    <v>Juan Manuel Fócil Pérez (Senado)</v>
-    <v>6487a7c3-edf5-4031-fe66-5c34adf0865c</v>
+    <v>Alfonso Durazo Montaño (Gobernador)</v>
+    <v>1bf2764a-b01c-b260-be29-7f0d8c919518</v>
+    <v>es-MX</v>
+    <v>Generic</v>
+  </rv>
+  <rv s="0">
+    <v>805306368</v>
+    <v>Arturo Bours Griffith (Senado)</v>
+    <v>b9fe33c2-01ce-b279-9100-57d261fa7c50</v>
+    <v>es-MX</v>
+    <v>Generic</v>
+  </rv>
+  <rv s="0">
+    <v>805306368</v>
+    <v>Lilly Téllez (Senado)</v>
+    <v>0b70f1ce-280f-0c82-7747-7e30db7086ce</v>
+    <v>es-MX</v>
+    <v>Generic</v>
+  </rv>
+  <rv s="0">
+    <v>805306368</v>
+    <v>Sylvana Beltrones Sánchez (Senado)</v>
+    <v>fd1e46b2-0f99-5c78-0bf0-05f2b5bdccfc</v>
     <v>es-MX</v>
     <v>Generic</v>
   </rv>
@@ -4192,67 +4415,59 @@
     <v>33</v>
   </rv>
   <rv s="1">
-    <fb>2402598</fb>
-    <v>11</v>
-  </rv>
-  <rv s="5">
+    <fb>2850330</fb>
+    <v>11</v>
+  </rv>
+  <rv s="6">
     <v>#VALUE!</v>
     <v>es-ES</v>
-    <v>f96880d9-0a36-58d3-7351-a4c7070c642d</v>
+    <v>e59e4f16-5e42-af6e-b970-e0ae59046077</v>
     <v>536870912</v>
     <v>1</v>
     <v>119</v>
     <v>4</v>
-    <v>5</v>
-    <v>Tabasco</v>
+    <v>18</v>
+    <v>Sonora</v>
     <v>7</v>
     <v>8</v>
     <v>Map</v>
     <v>9</v>
-    <v>10</v>
-    <v>MX-TAB</v>
-    <v>409</v>
-    <v>410</v>
-    <v>410</v>
-    <v>Tabasco, oficialmente llamado Estado Libre y Soberano de Tabasco, es uno de los treinta y un estados que, junto con la Ciudad de México, conforman México. Su capital y ciudad más poblada es Villahermosa.</v>
+    <v>46</v>
+    <v>MX-SON</v>
     <v>411</v>
     <v>412</v>
+    <v>412</v>
+    <v>Sonora, oficialmente llamado Estado Libre y Soberano de Sonora, es uno de los treinta y un estados que, junto con la Ciudad de México, conforman México. Su capital y ciudad más poblada es Hermosillo. Está ubicado en la región noroeste del país, ...</v>
     <v>413</v>
-    <v>418</v>
+    <v>414</v>
+    <v>415</v>
+    <v>420</v>
+    <v>Sonora</v>
+    <v>11</v>
+    <v>421</v>
+    <v>Sonora</v>
+    <v>mdp/vdpid/31328</v>
+  </rv>
+  <rv s="0">
+    <v>536870912</v>
     <v>Tabasco</v>
-    <v>54</v>
-    <v>419</v>
-    <v>Tabasco</v>
-    <v>mdp/vdpid/32446</v>
-    <v>13</v>
-  </rv>
-  <rv s="0">
-    <v>536870912</v>
-    <v>Tamaulipas</v>
-    <v>6f2fce2f-2090-8583-dbf3-dd9d6fc3cab3</v>
+    <v>f96880d9-0a36-58d3-7351-a4c7070c642d</v>
     <v>es-ES</v>
     <v>Map</v>
   </rv>
   <rv s="1">
-    <fb>80175</fb>
-    <v>11</v>
-  </rv>
-  <rv s="0">
-    <v>536870912</v>
-    <v>Ciudad Victoria</v>
-    <v>3bb5abb5-7a10-1965-b3c7-25f3c08d6d3b</v>
-    <v>es-MX</v>
-    <v>Map</v>
-  </rv>
-  <rv s="0">
-    <v>536870912</v>
-    <v>Reynosa</v>
-    <v>a8ebbb47-c455-97bf-bca0-c929889c1c65</v>
-    <v>es-MX</v>
-    <v>Map</v>
-  </rv>
-  <rv s="1">
-    <fb>1050147</fb>
+    <fb>24738</fb>
+    <v>11</v>
+  </rv>
+  <rv s="0">
+    <v>536870912</v>
+    <v>Villahermosa</v>
+    <v>7171e244-bb41-21fc-8ea3-b2e3210ed2a9</v>
+    <v>es-MX</v>
+    <v>Map</v>
+  </rv>
+  <rv s="1">
+    <fb>678859</fb>
     <v>11</v>
   </rv>
   <rv s="2">
@@ -4261,37 +4476,37 @@
     <v>120</v>
     <v>7</v>
     <v>0</v>
-    <v>Image of Tamaulipas</v>
+    <v>Image of Tabasco</v>
   </rv>
   <rv s="3">
-    <v>https://www.bing.com/search?q=Tamaulipas&amp;form=skydnc</v>
+    <v>https://www.bing.com/search?q=Tabasco&amp;form=skydnc</v>
     <v>Aprenda más con Bing</v>
   </rv>
   <rv s="0">
     <v>805306368</v>
-    <v>Américo Villarreal Anaya (Gobernador)</v>
-    <v>adc0b886-c7b3-5e17-ac8d-68a55c3d83d9</v>
-    <v>es-MX</v>
-    <v>Generic</v>
-  </rv>
-  <rv s="0">
-    <v>805306368</v>
-    <v>Guadalupe Covarrubias Cervantes (Senado)</v>
-    <v>db147e94-0495-2a85-ffda-1a040318da71</v>
-    <v>es-MX</v>
-    <v>Generic</v>
-  </rv>
-  <rv s="0">
-    <v>805306368</v>
-    <v>José Ramón Gómez Leal (Senado)</v>
-    <v>7c75a134-a789-be66-97b4-210fcdab996c</v>
-    <v>es-MX</v>
-    <v>Generic</v>
-  </rv>
-  <rv s="0">
-    <v>805306368</v>
-    <v>Ismael García Cabeza de Vaca (Senado)</v>
-    <v>3bee9907-a83d-7859-6caf-6295fe1d8733</v>
+    <v>Javier May Rodríguez (Gobernador)</v>
+    <v>eb064643-d95a-5b4f-e5c7-309080a1dbba</v>
+    <v>es-MX</v>
+    <v>Generic</v>
+  </rv>
+  <rv s="0">
+    <v>805306368</v>
+    <v>Adriana Manzanilla Fojaco (Senado)</v>
+    <v>92be806f-98f8-0da8-e5e0-3a837aacc554</v>
+    <v>es-MX</v>
+    <v>Generic</v>
+  </rv>
+  <rv s="0">
+    <v>805306368</v>
+    <v>Ovidio Peralta Suárez (Senado)</v>
+    <v>cd00d941-4447-7e55-8a34-e3393b2ebb2f</v>
+    <v>es-MX</v>
+    <v>Generic</v>
+  </rv>
+  <rv s="0">
+    <v>805306368</v>
+    <v>Juan Manuel Fócil Pérez (Senado)</v>
+    <v>6487a7c3-edf5-4031-fe66-5c34adf0865c</v>
     <v>es-MX</v>
     <v>Generic</v>
   </rv>
@@ -4299,67 +4514,67 @@
     <v>34</v>
   </rv>
   <rv s="1">
-    <fb>3527735</fb>
+    <fb>2402598</fb>
     <v>11</v>
   </rv>
   <rv s="5">
     <v>#VALUE!</v>
     <v>es-ES</v>
-    <v>6f2fce2f-2090-8583-dbf3-dd9d6fc3cab3</v>
+    <v>f96880d9-0a36-58d3-7351-a4c7070c642d</v>
     <v>536870912</v>
     <v>1</v>
     <v>122</v>
     <v>4</v>
     <v>5</v>
-    <v>Tamaulipas</v>
+    <v>Tabasco</v>
     <v>7</v>
     <v>8</v>
     <v>Map</v>
     <v>9</v>
     <v>10</v>
-    <v>MX-TAM</v>
-    <v>422</v>
-    <v>423</v>
+    <v>MX-TAB</v>
     <v>424</v>
-    <v>Tamaulipas, oficialmente Estado Libre y Soberano de Tamaulipas, es uno de los treinta y un estados que, junto con la Ciudad de México, forman México. Su capital es Ciudad Victoria y su ciudad más poblada es Reynosa. Fue fundado el 7 de febrero ...</v>
     <v>425</v>
+    <v>425</v>
+    <v>Tabasco, oficialmente llamado Estado Libre y Soberano de Tabasco, es uno de los treinta y un estados que, junto con la Ciudad de México, conforman México. Su capital y ciudad más poblada es Villahermosa.</v>
     <v>426</v>
     <v>427</v>
-    <v>432</v>
+    <v>428</v>
+    <v>433</v>
+    <v>Tabasco</v>
+    <v>54</v>
+    <v>434</v>
+    <v>Tabasco</v>
+    <v>mdp/vdpid/32446</v>
+    <v>13</v>
+  </rv>
+  <rv s="0">
+    <v>536870912</v>
     <v>Tamaulipas</v>
-    <v>11</v>
-    <v>433</v>
-    <v>Tamaulipas</v>
-    <v>mdp/vdpid/32643</v>
-    <v>13</v>
-  </rv>
-  <rv s="0">
-    <v>536870912</v>
-    <v>Tlaxcala</v>
-    <v>77063c53-3a0e-fbf0-30d8-68218fbc38fa</v>
+    <v>6f2fce2f-2090-8583-dbf3-dd9d6fc3cab3</v>
     <v>es-ES</v>
     <v>Map</v>
   </rv>
   <rv s="1">
-    <fb>3991</fb>
-    <v>11</v>
-  </rv>
-  <rv s="0">
-    <v>536870912</v>
-    <v>Tlaxcala de Xicohténcatl</v>
-    <v>090633f2-537e-40a3-8a1d-77d6beab7d95</v>
-    <v>es-MX</v>
-    <v>Map</v>
-  </rv>
-  <rv s="0">
-    <v>536870912</v>
-    <v>San Pablo del Monte</v>
-    <v>f06496e6-9833-a897-d111-296528c8f5d5</v>
-    <v>es-MX</v>
-    <v>Map</v>
-  </rv>
-  <rv s="1">
-    <fb>326530</fb>
+    <fb>80175</fb>
+    <v>11</v>
+  </rv>
+  <rv s="0">
+    <v>536870912</v>
+    <v>Ciudad Victoria</v>
+    <v>3bb5abb5-7a10-1965-b3c7-25f3c08d6d3b</v>
+    <v>es-MX</v>
+    <v>Map</v>
+  </rv>
+  <rv s="0">
+    <v>536870912</v>
+    <v>Reynosa</v>
+    <v>a8ebbb47-c455-97bf-bca0-c929889c1c65</v>
+    <v>es-MX</v>
+    <v>Map</v>
+  </rv>
+  <rv s="1">
+    <fb>1050147</fb>
     <v>11</v>
   </rv>
   <rv s="2">
@@ -4368,37 +4583,37 @@
     <v>123</v>
     <v>7</v>
     <v>0</v>
-    <v>Image of Tlaxcala</v>
+    <v>Image of Tamaulipas</v>
   </rv>
   <rv s="3">
-    <v>https://www.bing.com/search?q=Tlaxcala&amp;form=skydnc</v>
+    <v>https://www.bing.com/search?q=Tamaulipas&amp;form=skydnc</v>
     <v>Aprenda más con Bing</v>
   </rv>
   <rv s="0">
     <v>805306368</v>
-    <v>Lorena Cuéllar Cisneros (Gobernador)</v>
-    <v>2690b7aa-a987-4550-aa41-295b446e79c5</v>
-    <v>es-MX</v>
-    <v>Generic</v>
-  </rv>
-  <rv s="0">
-    <v>805306368</v>
-    <v>Joel Molina Ramírez (Senado)</v>
-    <v>e79c8499-35e1-2966-c988-f7329c6687d3</v>
-    <v>es-MX</v>
-    <v>Generic</v>
-  </rv>
-  <rv s="0">
-    <v>805306368</v>
-    <v>Ana Lilia Rivera Rivera (Senado)</v>
-    <v>2c8eb547-867e-59ae-845a-4f73c70d5eea</v>
-    <v>es-MX</v>
-    <v>Generic</v>
-  </rv>
-  <rv s="0">
-    <v>805306368</v>
-    <v>Minerva Hernández Ramos (Senado)</v>
-    <v>ac7b0bd1-7dfd-1fea-4137-2b29b236dee1</v>
+    <v>Américo Villarreal Anaya (Gobernador)</v>
+    <v>adc0b886-c7b3-5e17-ac8d-68a55c3d83d9</v>
+    <v>es-MX</v>
+    <v>Generic</v>
+  </rv>
+  <rv s="0">
+    <v>805306368</v>
+    <v>Guadalupe Covarrubias Cervantes (Senado)</v>
+    <v>db147e94-0495-2a85-ffda-1a040318da71</v>
+    <v>es-MX</v>
+    <v>Generic</v>
+  </rv>
+  <rv s="0">
+    <v>805306368</v>
+    <v>José Ramón Gómez Leal (Senado)</v>
+    <v>7c75a134-a789-be66-97b4-210fcdab996c</v>
+    <v>es-MX</v>
+    <v>Generic</v>
+  </rv>
+  <rv s="0">
+    <v>805306368</v>
+    <v>Ismael García Cabeza de Vaca (Senado)</v>
+    <v>3bee9907-a83d-7859-6caf-6295fe1d8733</v>
     <v>es-MX</v>
     <v>Generic</v>
   </rv>
@@ -4406,67 +4621,67 @@
     <v>35</v>
   </rv>
   <rv s="1">
-    <fb>1342977</fb>
+    <fb>3527735</fb>
     <v>11</v>
   </rv>
   <rv s="5">
     <v>#VALUE!</v>
     <v>es-ES</v>
-    <v>77063c53-3a0e-fbf0-30d8-68218fbc38fa</v>
+    <v>6f2fce2f-2090-8583-dbf3-dd9d6fc3cab3</v>
     <v>536870912</v>
     <v>1</v>
     <v>125</v>
     <v>4</v>
     <v>5</v>
-    <v>Tlaxcala</v>
+    <v>Tamaulipas</v>
     <v>7</v>
     <v>8</v>
     <v>Map</v>
     <v>9</v>
     <v>10</v>
-    <v>MX-TLA</v>
-    <v>436</v>
+    <v>MX-TAM</v>
     <v>437</v>
     <v>438</v>
-    <v>Tlaxcala, oficialmente el Estado Libre y Soberano de Tlaxcala, es uno de los treinta y un estados que, junto con la Ciudad de México, conforman los Estados Unidos Mexicanos. Su capital es Tlaxcala de Xicohténcatl y, su ciudad más poblada, San ...</v>
     <v>439</v>
+    <v>Tamaulipas, oficialmente Estado Libre y Soberano de Tamaulipas, es uno de los treinta y un estados que, junto con la Ciudad de México, forman México. Su capital es Ciudad Victoria y su ciudad más poblada es Reynosa. Fue fundado el 7 de febrero ...</v>
     <v>440</v>
     <v>441</v>
-    <v>446</v>
+    <v>442</v>
+    <v>447</v>
+    <v>Tamaulipas</v>
+    <v>11</v>
+    <v>448</v>
+    <v>Tamaulipas</v>
+    <v>mdp/vdpid/32643</v>
+    <v>13</v>
+  </rv>
+  <rv s="0">
+    <v>536870912</v>
     <v>Tlaxcala</v>
-    <v>11</v>
-    <v>447</v>
-    <v>Tlaxcala</v>
-    <v>mdp/vdpid/33515</v>
-    <v>13</v>
-  </rv>
-  <rv s="0">
-    <v>536870912</v>
-    <v>Estado de Veracruz</v>
-    <v>10381f79-264a-f2fd-08f8-cc5377683832</v>
+    <v>77063c53-3a0e-fbf0-30d8-68218fbc38fa</v>
     <v>es-ES</v>
     <v>Map</v>
   </rv>
   <rv s="1">
-    <fb>71820</fb>
-    <v>11</v>
-  </rv>
-  <rv s="0">
-    <v>536870912</v>
-    <v>Xalapa-Enríquez</v>
-    <v>decfec25-d20c-79d7-63e6-b65f2cd5bf1a</v>
-    <v>es-MX</v>
-    <v>Map</v>
-  </rv>
-  <rv s="0">
-    <v>536870912</v>
-    <v>Veracruz</v>
-    <v>2db7ec30-1035-4400-73cf-1a3e7764446c</v>
-    <v>es-MX</v>
-    <v>Map</v>
-  </rv>
-  <rv s="1">
-    <fb>2299245</fb>
+    <fb>3991</fb>
+    <v>11</v>
+  </rv>
+  <rv s="0">
+    <v>536870912</v>
+    <v>Tlaxcala de Xicohténcatl</v>
+    <v>090633f2-537e-40a3-8a1d-77d6beab7d95</v>
+    <v>es-MX</v>
+    <v>Map</v>
+  </rv>
+  <rv s="0">
+    <v>536870912</v>
+    <v>San Pablo del Monte</v>
+    <v>f06496e6-9833-a897-d111-296528c8f5d5</v>
+    <v>es-MX</v>
+    <v>Map</v>
+  </rv>
+  <rv s="1">
+    <fb>326530</fb>
     <v>11</v>
   </rv>
   <rv s="2">
@@ -4475,44 +4690,37 @@
     <v>126</v>
     <v>7</v>
     <v>0</v>
-    <v>Image of Estado de Veracruz</v>
+    <v>Image of Tlaxcala</v>
   </rv>
   <rv s="3">
-    <v>https://www.bing.com/search?q=Veracruz+de+Ignacio+de+la+Llave&amp;form=skydnc</v>
+    <v>https://www.bing.com/search?q=Tlaxcala&amp;form=skydnc</v>
     <v>Aprenda más con Bing</v>
   </rv>
   <rv s="0">
     <v>805306368</v>
-    <v>Rocío Nahle (Gobernador)</v>
-    <v>48a4aa04-48b8-2287-13d9-67b6b96043d2</v>
-    <v>es-MX</v>
-    <v>Generic</v>
-  </rv>
-  <rv s="0">
-    <v>805306368</v>
-    <v>Raquel Bonilla Herrera (Senado)</v>
-    <v>76e8052a-c72a-6efe-748d-c8731c829e79</v>
-    <v>es-MX</v>
-    <v>Generic</v>
-  </rv>
-  <rv s="0">
-    <v>805306368</v>
-    <v>nb (Senado)</v>
-    <v>3d15599c-d922-ccf7-021b-17b425cc31c5</v>
-    <v>es-MX</v>
-    <v>Generic</v>
-  </rv>
-  <rv s="0">
-    <v>805306368</v>
-    <v>Manuel Huerta Ladrón de Guevara (Senado)</v>
-    <v>ecd4d6f6-19b0-fc84-fe9f-ebe7e5947d9a</v>
-    <v>es-MX</v>
-    <v>Generic</v>
-  </rv>
-  <rv s="0">
-    <v>805306368</v>
-    <v>Miguel Ángel Yunes Márquez (Senado)</v>
-    <v>ac46d84a-f4f2-4a03-a110-5e1bd9013e62</v>
+    <v>Lorena Cuéllar Cisneros (Gobernador)</v>
+    <v>2690b7aa-a987-4550-aa41-295b446e79c5</v>
+    <v>es-MX</v>
+    <v>Generic</v>
+  </rv>
+  <rv s="0">
+    <v>805306368</v>
+    <v>Joel Molina Ramírez (Senado)</v>
+    <v>e79c8499-35e1-2966-c988-f7329c6687d3</v>
+    <v>es-MX</v>
+    <v>Generic</v>
+  </rv>
+  <rv s="0">
+    <v>805306368</v>
+    <v>Ana Lilia Rivera Rivera (Senado)</v>
+    <v>2c8eb547-867e-59ae-845a-4f73c70d5eea</v>
+    <v>es-MX</v>
+    <v>Generic</v>
+  </rv>
+  <rv s="0">
+    <v>805306368</v>
+    <v>Minerva Hernández Ramos (Senado)</v>
+    <v>ac7b0bd1-7dfd-1fea-4137-2b29b236dee1</v>
     <v>es-MX</v>
     <v>Generic</v>
   </rv>
@@ -4520,38 +4728,38 @@
     <v>36</v>
   </rv>
   <rv s="1">
-    <fb>8062579</fb>
+    <fb>1342977</fb>
     <v>11</v>
   </rv>
   <rv s="5">
     <v>#VALUE!</v>
     <v>es-ES</v>
-    <v>10381f79-264a-f2fd-08f8-cc5377683832</v>
+    <v>77063c53-3a0e-fbf0-30d8-68218fbc38fa</v>
     <v>536870912</v>
     <v>1</v>
     <v>128</v>
     <v>4</v>
     <v>5</v>
-    <v>Estado de Veracruz</v>
+    <v>Tlaxcala</v>
     <v>7</v>
     <v>8</v>
     <v>Map</v>
     <v>9</v>
     <v>10</v>
-    <v>MX-VER</v>
-    <v>450</v>
+    <v>MX-TLA</v>
     <v>451</v>
     <v>452</v>
-    <v>Veracruz, oficialmente llamado Estado Libre y Soberano de Veracruz de Ignacio de la Llave, es uno de los treinta y un estados que, junto con la Ciudad de México, conforman México. Su capital es Xalapa-Enríquez y su ciudad más poblada es ...</v>
     <v>453</v>
+    <v>Tlaxcala, oficialmente el Estado Libre y Soberano de Tlaxcala, es uno de los treinta y un estados que, junto con la Ciudad de México, conforman los Estados Unidos Mexicanos. Su capital es Tlaxcala de Xicohténcatl y, su ciudad más poblada, San ...</v>
     <v>454</v>
     <v>455</v>
+    <v>456</v>
     <v>461</v>
-    <v>Estado de Veracruz</v>
+    <v>Tlaxcala</v>
     <v>11</v>
     <v>462</v>
-    <v>Estado de Veracruz</v>
-    <v>mdp/vdpid/34963</v>
+    <v>Tlaxcala</v>
+    <v>mdp/vdpid/33515</v>
     <v>13</v>
   </rv>
   <rv s="0">
@@ -5433,13 +5641,13 @@
     <spb s="0">
       <v xml:space="preserve">Wikipedia	</v>
       <v xml:space="preserve">CC BY-SA 3.0	</v>
-      <v xml:space="preserve">https://es.wikipedia.org/wiki/Guanajuato	</v>
+      <v xml:space="preserve">https://es.wikipedia.org/wiki/Estado_de_Guerrero	</v>
       <v xml:space="preserve">https://creativecommons.org/licenses/by-sa/3.0	</v>
     </spb>
     <spb s="0">
       <v xml:space="preserve">Wikipedia	</v>
       <v xml:space="preserve">CC-BY-SA	</v>
-      <v xml:space="preserve">http://en.wikipedia.org/wiki/Guanajuato	</v>
+      <v xml:space="preserve">http://en.wikipedia.org/wiki/Guerrero	</v>
       <v xml:space="preserve">http://creativecommons.org/licenses/by-sa/3.0/	</v>
     </spb>
     <spb s="1">
@@ -5462,13 +5670,13 @@
     <spb s="0">
       <v xml:space="preserve">Wikipedia	</v>
       <v xml:space="preserve">CC BY-SA 3.0	</v>
-      <v xml:space="preserve">https://es.wikipedia.org/wiki/Estado_de_Guerrero	</v>
+      <v xml:space="preserve">https://es.wikipedia.org/wiki/Estado_de_Hidalgo	</v>
       <v xml:space="preserve">https://creativecommons.org/licenses/by-sa/3.0	</v>
     </spb>
     <spb s="0">
       <v xml:space="preserve">Wikipedia	</v>
       <v xml:space="preserve">CC-BY-SA	</v>
-      <v xml:space="preserve">http://en.wikipedia.org/wiki/Guerrero	</v>
+      <v xml:space="preserve">http://en.wikipedia.org/wiki/Hidalgo_(state)	</v>
       <v xml:space="preserve">http://creativecommons.org/licenses/by-sa/3.0/	</v>
     </spb>
     <spb s="1">
@@ -5486,13 +5694,13 @@
     <spb s="0">
       <v xml:space="preserve">Wikipedia	</v>
       <v xml:space="preserve">CC BY-SA 3.0	</v>
-      <v xml:space="preserve">https://es.wikipedia.org/wiki/Estado_de_Hidalgo	</v>
+      <v xml:space="preserve">https://es.wikipedia.org/wiki/Estado_de_Veracruz	</v>
       <v xml:space="preserve">https://creativecommons.org/licenses/by-sa/3.0	</v>
     </spb>
     <spb s="0">
       <v xml:space="preserve">Wikipedia	</v>
       <v xml:space="preserve">CC-BY-SA	</v>
-      <v xml:space="preserve">http://en.wikipedia.org/wiki/Hidalgo_(state)	</v>
+      <v xml:space="preserve">http://en.wikipedia.org/wiki/Veracruz	</v>
       <v xml:space="preserve">http://creativecommons.org/licenses/by-sa/3.0/	</v>
     </spb>
     <spb s="1">
@@ -5510,13 +5718,13 @@
     <spb s="0">
       <v xml:space="preserve">Wikipedia	</v>
       <v xml:space="preserve">CC BY-SA 3.0	</v>
-      <v xml:space="preserve">https://es.wikipedia.org/wiki/Jalisco	</v>
+      <v xml:space="preserve">https://es.wikipedia.org/wiki/Guanajuato	</v>
       <v xml:space="preserve">https://creativecommons.org/licenses/by-sa/3.0	</v>
     </spb>
     <spb s="0">
       <v xml:space="preserve">Wikipedia	</v>
       <v xml:space="preserve">CC-BY-SA	</v>
-      <v xml:space="preserve">http://en.wikipedia.org/wiki/Jalisco	</v>
+      <v xml:space="preserve">http://en.wikipedia.org/wiki/Guanajuato	</v>
       <v xml:space="preserve">http://creativecommons.org/licenses/by-sa/3.0/	</v>
     </spb>
     <spb s="1">
@@ -5532,6 +5740,30 @@
       <v>53</v>
     </spb>
     <spb s="0">
+      <v xml:space="preserve">Wikipedia	</v>
+      <v xml:space="preserve">CC BY-SA 3.0	</v>
+      <v xml:space="preserve">https://es.wikipedia.org/wiki/Jalisco	</v>
+      <v xml:space="preserve">https://creativecommons.org/licenses/by-sa/3.0	</v>
+    </spb>
+    <spb s="0">
+      <v xml:space="preserve">Wikipedia	</v>
+      <v xml:space="preserve">CC-BY-SA	</v>
+      <v xml:space="preserve">http://en.wikipedia.org/wiki/Jalisco	</v>
+      <v xml:space="preserve">http://creativecommons.org/licenses/by-sa/3.0/	</v>
+    </spb>
+    <spb s="1">
+      <v>56</v>
+      <v>56</v>
+      <v>1</v>
+      <v>56</v>
+      <v>56</v>
+      <v>57</v>
+      <v>56</v>
+      <v>56</v>
+      <v>56</v>
+      <v>56</v>
+    </spb>
+    <spb s="0">
       <v xml:space="preserve">data.worldbank.org	</v>
       <v xml:space="preserve">	</v>
       <v xml:space="preserve">http://data.worldbank.org/indicator/FP.CPI.TOTL	</v>
@@ -5628,51 +5860,51 @@
       <v xml:space="preserve">	</v>
     </spb>
     <spb s="12">
-      <v>56</v>
-      <v>57</v>
-      <v>58</v>
-      <v>58</v>
-      <v>58</v>
-      <v>58</v>
-      <v>59</v>
-      <v>58</v>
-      <v>58</v>
-      <v>58</v>
       <v>59</v>
       <v>60</v>
-      <v>58</v>
+      <v>61</v>
+      <v>61</v>
+      <v>61</v>
       <v>61</v>
       <v>62</v>
-      <v>58</v>
-      <v>58</v>
+      <v>61</v>
+      <v>61</v>
+      <v>61</v>
+      <v>62</v>
       <v>63</v>
-      <v>62</v>
+      <v>61</v>
       <v>64</v>
       <v>65</v>
+      <v>61</v>
+      <v>61</v>
       <v>66</v>
-      <v>62</v>
-      <v>62</v>
-      <v>62</v>
-      <v>57</v>
-      <v>62</v>
-      <v>58</v>
-      <v>62</v>
+      <v>65</v>
       <v>67</v>
       <v>68</v>
       <v>69</v>
+      <v>65</v>
+      <v>65</v>
+      <v>65</v>
+      <v>60</v>
+      <v>65</v>
+      <v>61</v>
+      <v>65</v>
       <v>70</v>
-      <v>62</v>
-      <v>62</v>
-      <v>62</v>
       <v>71</v>
-      <v>62</v>
-      <v>62</v>
-      <v>62</v>
-      <v>62</v>
-      <v>62</v>
-      <v>62</v>
-      <v>62</v>
-      <v>57</v>
+      <v>72</v>
+      <v>73</v>
+      <v>65</v>
+      <v>65</v>
+      <v>65</v>
+      <v>74</v>
+      <v>65</v>
+      <v>65</v>
+      <v>65</v>
+      <v>65</v>
+      <v>65</v>
+      <v>65</v>
+      <v>65</v>
+      <v>60</v>
     </spb>
     <spb s="13">
       <v>CPI</v>
@@ -5802,30 +6034,6 @@
       <v xml:space="preserve">http://creativecommons.org/licenses/by-sa/3.0/	</v>
     </spb>
     <spb s="1">
-      <v>84</v>
-      <v>84</v>
-      <v>1</v>
-      <v>84</v>
-      <v>84</v>
-      <v>85</v>
-      <v>84</v>
-      <v>84</v>
-      <v>84</v>
-      <v>84</v>
-    </spb>
-    <spb s="0">
-      <v xml:space="preserve">Wikipedia	</v>
-      <v xml:space="preserve">CC BY-SA 3.0	</v>
-      <v xml:space="preserve">https://es.wikipedia.org/wiki/Morelos	</v>
-      <v xml:space="preserve">https://creativecommons.org/licenses/by-sa/3.0	</v>
-    </spb>
-    <spb s="0">
-      <v xml:space="preserve">Wikipedia	</v>
-      <v xml:space="preserve">CC-BY-SA	</v>
-      <v xml:space="preserve">http://en.wikipedia.org/wiki/Morelos	</v>
-      <v xml:space="preserve">http://creativecommons.org/licenses/by-sa/3.0/	</v>
-    </spb>
-    <spb s="1">
       <v>87</v>
       <v>87</v>
       <v>1</v>
@@ -5840,13 +6048,13 @@
     <spb s="0">
       <v xml:space="preserve">Wikipedia	</v>
       <v xml:space="preserve">CC BY-SA 3.0	</v>
-      <v xml:space="preserve">https://es.wikipedia.org/wiki/Nayarit	</v>
+      <v xml:space="preserve">https://es.wikipedia.org/wiki/Morelos	</v>
       <v xml:space="preserve">https://creativecommons.org/licenses/by-sa/3.0	</v>
     </spb>
     <spb s="0">
       <v xml:space="preserve">Wikipedia	</v>
       <v xml:space="preserve">CC-BY-SA	</v>
-      <v xml:space="preserve">http://en.wikipedia.org/wiki/Nayarit	</v>
+      <v xml:space="preserve">http://en.wikipedia.org/wiki/Morelos	</v>
       <v xml:space="preserve">http://creativecommons.org/licenses/by-sa/3.0/	</v>
     </spb>
     <spb s="1">
@@ -5864,13 +6072,13 @@
     <spb s="0">
       <v xml:space="preserve">Wikipedia	</v>
       <v xml:space="preserve">CC BY-SA 3.0	</v>
-      <v xml:space="preserve">https://es.wikipedia.org/wiki/Nuevo_Le%C3%B3n	</v>
+      <v xml:space="preserve">https://es.wikipedia.org/wiki/Nayarit	</v>
       <v xml:space="preserve">https://creativecommons.org/licenses/by-sa/3.0	</v>
     </spb>
     <spb s="0">
       <v xml:space="preserve">Wikipedia	</v>
       <v xml:space="preserve">CC-BY-SA	</v>
-      <v xml:space="preserve">http://en.wikipedia.org/wiki/Nuevo_León	</v>
+      <v xml:space="preserve">http://en.wikipedia.org/wiki/Nayarit	</v>
       <v xml:space="preserve">http://creativecommons.org/licenses/by-sa/3.0/	</v>
     </spb>
     <spb s="1">
@@ -5888,13 +6096,13 @@
     <spb s="0">
       <v xml:space="preserve">Wikipedia	</v>
       <v xml:space="preserve">CC BY-SA 3.0	</v>
-      <v xml:space="preserve">https://es.wikipedia.org/wiki/Oaxaca	</v>
+      <v xml:space="preserve">https://es.wikipedia.org/wiki/Nuevo_Le%C3%B3n	</v>
       <v xml:space="preserve">https://creativecommons.org/licenses/by-sa/3.0	</v>
     </spb>
     <spb s="0">
       <v xml:space="preserve">Wikipedia	</v>
       <v xml:space="preserve">CC-BY-SA	</v>
-      <v xml:space="preserve">http://en.wikipedia.org/wiki/Oaxaca	</v>
+      <v xml:space="preserve">http://en.wikipedia.org/wiki/Nuevo_León	</v>
       <v xml:space="preserve">http://creativecommons.org/licenses/by-sa/3.0/	</v>
     </spb>
     <spb s="1">
@@ -5912,13 +6120,13 @@
     <spb s="0">
       <v xml:space="preserve">Wikipedia	</v>
       <v xml:space="preserve">CC BY-SA 3.0	</v>
-      <v xml:space="preserve">https://es.wikipedia.org/wiki/Puebla	</v>
+      <v xml:space="preserve">https://es.wikipedia.org/wiki/Oaxaca	</v>
       <v xml:space="preserve">https://creativecommons.org/licenses/by-sa/3.0	</v>
     </spb>
     <spb s="0">
       <v xml:space="preserve">Wikipedia	</v>
       <v xml:space="preserve">CC-BY-SA	</v>
-      <v xml:space="preserve">http://en.wikipedia.org/wiki/Puebla	</v>
+      <v xml:space="preserve">http://en.wikipedia.org/wiki/Oaxaca	</v>
       <v xml:space="preserve">http://creativecommons.org/licenses/by-sa/3.0/	</v>
     </spb>
     <spb s="1">
@@ -5936,13 +6144,13 @@
     <spb s="0">
       <v xml:space="preserve">Wikipedia	</v>
       <v xml:space="preserve">CC BY-SA 3.0	</v>
-      <v xml:space="preserve">https://es.wikipedia.org/wiki/Quer%C3%A9taro	</v>
+      <v xml:space="preserve">https://es.wikipedia.org/wiki/Puebla	</v>
       <v xml:space="preserve">https://creativecommons.org/licenses/by-sa/3.0	</v>
     </spb>
     <spb s="0">
       <v xml:space="preserve">Wikipedia	</v>
       <v xml:space="preserve">CC-BY-SA	</v>
-      <v xml:space="preserve">http://en.wikipedia.org/wiki/Querétaro	</v>
+      <v xml:space="preserve">http://en.wikipedia.org/wiki/Puebla	</v>
       <v xml:space="preserve">http://creativecommons.org/licenses/by-sa/3.0/	</v>
     </spb>
     <spb s="1">
@@ -5960,13 +6168,13 @@
     <spb s="0">
       <v xml:space="preserve">Wikipedia	</v>
       <v xml:space="preserve">CC BY-SA 3.0	</v>
-      <v xml:space="preserve">https://es.wikipedia.org/wiki/Quintana_Roo	</v>
+      <v xml:space="preserve">https://es.wikipedia.org/wiki/Quer%C3%A9taro	</v>
       <v xml:space="preserve">https://creativecommons.org/licenses/by-sa/3.0	</v>
     </spb>
     <spb s="0">
       <v xml:space="preserve">Wikipedia	</v>
       <v xml:space="preserve">CC-BY-SA	</v>
-      <v xml:space="preserve">http://en.wikipedia.org/wiki/Quintana_Roo	</v>
+      <v xml:space="preserve">http://en.wikipedia.org/wiki/Querétaro	</v>
       <v xml:space="preserve">http://creativecommons.org/licenses/by-sa/3.0/	</v>
     </spb>
     <spb s="1">
@@ -5984,13 +6192,13 @@
     <spb s="0">
       <v xml:space="preserve">Wikipedia	</v>
       <v xml:space="preserve">CC BY-SA 3.0	</v>
-      <v xml:space="preserve">https://es.wikipedia.org/wiki/San_Luis_Potos%C3%AD	</v>
+      <v xml:space="preserve">https://es.wikipedia.org/wiki/Quintana_Roo	</v>
       <v xml:space="preserve">https://creativecommons.org/licenses/by-sa/3.0	</v>
     </spb>
     <spb s="0">
       <v xml:space="preserve">Wikipedia	</v>
       <v xml:space="preserve">CC-BY-SA	</v>
-      <v xml:space="preserve">http://en.wikipedia.org/wiki/San_Luis_Potosí	</v>
+      <v xml:space="preserve">http://en.wikipedia.org/wiki/Quintana_Roo	</v>
       <v xml:space="preserve">http://creativecommons.org/licenses/by-sa/3.0/	</v>
     </spb>
     <spb s="1">
@@ -6008,13 +6216,13 @@
     <spb s="0">
       <v xml:space="preserve">Wikipedia	</v>
       <v xml:space="preserve">CC BY-SA 3.0	</v>
-      <v xml:space="preserve">https://es.wikipedia.org/wiki/Sinaloa	</v>
+      <v xml:space="preserve">https://es.wikipedia.org/wiki/San_Luis_Potos%C3%AD	</v>
       <v xml:space="preserve">https://creativecommons.org/licenses/by-sa/3.0	</v>
     </spb>
     <spb s="0">
       <v xml:space="preserve">Wikipedia	</v>
       <v xml:space="preserve">CC-BY-SA	</v>
-      <v xml:space="preserve">http://en.wikipedia.org/wiki/Sinaloa	</v>
+      <v xml:space="preserve">http://en.wikipedia.org/wiki/San_Luis_Potosí	</v>
       <v xml:space="preserve">http://creativecommons.org/licenses/by-sa/3.0/	</v>
     </spb>
     <spb s="1">
@@ -6032,13 +6240,13 @@
     <spb s="0">
       <v xml:space="preserve">Wikipedia	</v>
       <v xml:space="preserve">CC BY-SA 3.0	</v>
-      <v xml:space="preserve">https://es.wikipedia.org/wiki/Sonora	</v>
+      <v xml:space="preserve">https://es.wikipedia.org/wiki/Sinaloa	</v>
       <v xml:space="preserve">https://creativecommons.org/licenses/by-sa/3.0	</v>
     </spb>
     <spb s="0">
       <v xml:space="preserve">Wikipedia	</v>
       <v xml:space="preserve">CC-BY-SA	</v>
-      <v xml:space="preserve">http://en.wikipedia.org/wiki/Sonora	</v>
+      <v xml:space="preserve">http://en.wikipedia.org/wiki/Sinaloa	</v>
       <v xml:space="preserve">http://creativecommons.org/licenses/by-sa/3.0/	</v>
     </spb>
     <spb s="1">
@@ -6056,13 +6264,13 @@
     <spb s="0">
       <v xml:space="preserve">Wikipedia	</v>
       <v xml:space="preserve">CC BY-SA 3.0	</v>
-      <v xml:space="preserve">https://es.wikipedia.org/wiki/Tabasco	</v>
+      <v xml:space="preserve">https://es.wikipedia.org/wiki/Sonora	</v>
       <v xml:space="preserve">https://creativecommons.org/licenses/by-sa/3.0	</v>
     </spb>
     <spb s="0">
       <v xml:space="preserve">Wikipedia	</v>
       <v xml:space="preserve">CC-BY-SA	</v>
-      <v xml:space="preserve">http://en.wikipedia.org/wiki/Tabasco	</v>
+      <v xml:space="preserve">http://en.wikipedia.org/wiki/Sonora	</v>
       <v xml:space="preserve">http://creativecommons.org/licenses/by-sa/3.0/	</v>
     </spb>
     <spb s="1">
@@ -6080,13 +6288,13 @@
     <spb s="0">
       <v xml:space="preserve">Wikipedia	</v>
       <v xml:space="preserve">CC BY-SA 3.0	</v>
-      <v xml:space="preserve">https://es.wikipedia.org/wiki/Tamaulipas	</v>
+      <v xml:space="preserve">https://es.wikipedia.org/wiki/Tabasco	</v>
       <v xml:space="preserve">https://creativecommons.org/licenses/by-sa/3.0	</v>
     </spb>
     <spb s="0">
       <v xml:space="preserve">Wikipedia	</v>
       <v xml:space="preserve">CC-BY-SA	</v>
-      <v xml:space="preserve">http://en.wikipedia.org/wiki/Tamaulipas	</v>
+      <v xml:space="preserve">http://en.wikipedia.org/wiki/Tabasco	</v>
       <v xml:space="preserve">http://creativecommons.org/licenses/by-sa/3.0/	</v>
     </spb>
     <spb s="1">
@@ -6104,13 +6312,13 @@
     <spb s="0">
       <v xml:space="preserve">Wikipedia	</v>
       <v xml:space="preserve">CC BY-SA 3.0	</v>
-      <v xml:space="preserve">https://es.wikipedia.org/wiki/Tlaxcala	</v>
+      <v xml:space="preserve">https://es.wikipedia.org/wiki/Tamaulipas	</v>
       <v xml:space="preserve">https://creativecommons.org/licenses/by-sa/3.0	</v>
     </spb>
     <spb s="0">
       <v xml:space="preserve">Wikipedia	</v>
       <v xml:space="preserve">CC-BY-SA	</v>
-      <v xml:space="preserve">http://en.wikipedia.org/wiki/Tlaxcala	</v>
+      <v xml:space="preserve">http://en.wikipedia.org/wiki/Tamaulipas	</v>
       <v xml:space="preserve">http://creativecommons.org/licenses/by-sa/3.0/	</v>
     </spb>
     <spb s="1">
@@ -6128,13 +6336,13 @@
     <spb s="0">
       <v xml:space="preserve">Wikipedia	</v>
       <v xml:space="preserve">CC BY-SA 3.0	</v>
-      <v xml:space="preserve">https://es.wikipedia.org/wiki/Estado_de_Veracruz	</v>
+      <v xml:space="preserve">https://es.wikipedia.org/wiki/Tlaxcala	</v>
       <v xml:space="preserve">https://creativecommons.org/licenses/by-sa/3.0	</v>
     </spb>
     <spb s="0">
       <v xml:space="preserve">Wikipedia	</v>
       <v xml:space="preserve">CC-BY-SA	</v>
-      <v xml:space="preserve">http://en.wikipedia.org/wiki/Veracruz	</v>
+      <v xml:space="preserve">http://en.wikipedia.org/wiki/Tlaxcala	</v>
       <v xml:space="preserve">http://creativecommons.org/licenses/by-sa/3.0/	</v>
     </spb>
     <spb s="1">
@@ -6806,1355 +7014,1677 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B6EEAE0A-2582-4121-8CC4-83FE5CC4BA64}">
-  <dimension ref="A2:D9"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2C4F8EDE-11A8-49A9-90BF-9F65C9F657A5}">
+  <dimension ref="C15:M23"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="4" max="4" width="17.6640625" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="2" spans="1:4" ht="31.2" x14ac:dyDescent="0.3">
-      <c r="A2" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="B2" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="C2" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="D2" s="5" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A3" s="1">
-        <v>2003</v>
-      </c>
-      <c r="B3" s="1">
-        <v>400</v>
-      </c>
-      <c r="C3" s="1">
-        <v>385</v>
-      </c>
-      <c r="D3" s="1"/>
-    </row>
-    <row r="4" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A4" s="6">
-        <v>2006</v>
-      </c>
-      <c r="B4" s="7">
-        <v>410</v>
-      </c>
-      <c r="C4" s="8">
-        <v>406</v>
-      </c>
-      <c r="D4" s="7">
-        <v>410</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A5" s="6">
-        <v>2009</v>
-      </c>
-      <c r="B5" s="7">
-        <v>425</v>
-      </c>
-      <c r="C5" s="8">
-        <v>419</v>
-      </c>
-      <c r="D5" s="7">
-        <v>416</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A6" s="6">
-        <v>2012</v>
-      </c>
-      <c r="B6" s="8">
-        <v>424</v>
-      </c>
-      <c r="C6" s="8">
-        <v>413</v>
-      </c>
-      <c r="D6" s="7">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A7" s="6">
-        <v>2015</v>
-      </c>
-      <c r="B7" s="8">
-        <v>423</v>
-      </c>
-      <c r="C7" s="8">
-        <v>408</v>
-      </c>
-      <c r="D7" s="7">
-        <v>416</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A8" s="6">
-        <v>2018</v>
-      </c>
-      <c r="B8" s="8">
-        <v>420</v>
-      </c>
-      <c r="C8" s="8">
-        <v>409</v>
-      </c>
-      <c r="D8" s="7">
-        <v>419</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A9" s="6">
-        <v>2022</v>
-      </c>
-      <c r="B9" s="7">
-        <v>415</v>
-      </c>
-      <c r="C9" s="8">
-        <v>395</v>
-      </c>
-      <c r="D9" s="7">
-        <v>410</v>
+    <row r="15" spans="3:13" ht="36.6" x14ac:dyDescent="0.7">
+      <c r="C15" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="D15" s="20"/>
+      <c r="E15" s="20"/>
+      <c r="F15" s="20"/>
+      <c r="G15" s="20"/>
+      <c r="H15" s="20"/>
+      <c r="I15" s="20"/>
+      <c r="J15" s="20"/>
+      <c r="K15" s="20"/>
+      <c r="L15" s="20"/>
+      <c r="M15" s="20"/>
+    </row>
+    <row r="17" spans="4:13" x14ac:dyDescent="0.3">
+      <c r="D17" s="12" t="s">
+        <v>51</v>
+      </c>
+      <c r="E17" s="18" t="s">
+        <v>52</v>
+      </c>
+      <c r="F17" s="19"/>
+      <c r="G17" s="19"/>
+      <c r="H17" s="19"/>
+      <c r="I17" s="19"/>
+      <c r="J17" s="19"/>
+      <c r="K17" s="19"/>
+      <c r="L17" s="19"/>
+      <c r="M17" s="19"/>
+    </row>
+    <row r="18" spans="4:13" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="D18" s="13" t="s">
+        <v>45</v>
+      </c>
+      <c r="E18" s="14" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="19" spans="4:13" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="D19" s="13" t="s">
+        <v>46</v>
+      </c>
+      <c r="E19" s="14" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="20" spans="4:13" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="D20" s="13" t="s">
+        <v>47</v>
+      </c>
+      <c r="E20" s="14" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="21" spans="4:13" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="D21" s="13" t="s">
+        <v>48</v>
+      </c>
+      <c r="E21" s="14" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="22" spans="4:13" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="D22" s="13" t="s">
+        <v>49</v>
+      </c>
+      <c r="E22" s="14" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="23" spans="4:13" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="D23" s="13" t="s">
+        <v>50</v>
+      </c>
+      <c r="E23" s="14" t="s">
+        <v>43</v>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="C15:M15"/>
+  </mergeCells>
+  <hyperlinks>
+    <hyperlink ref="D18" location="PISA_general!A1" display="PISA_general" xr:uid="{3B4B6120-642F-4A92-9DF2-7C96DA435902}"/>
+    <hyperlink ref="D19" location="PISA_matematicas!A1" display="PISA_matematicas" xr:uid="{419C01CA-9E6C-4645-AB49-9523E2750951}"/>
+    <hyperlink ref="D20" location="Matrícula_áreas!A1" display="Matrícula_áreas" xr:uid="{A1651F33-4007-477C-B941-3089DBB8E91E}"/>
+    <hyperlink ref="D21" location="Mapa_matrícula!A1" display="Mapa_matrícula" xr:uid="{0DBFFF81-A43E-4EC6-8EDE-519D2F951CDD}"/>
+    <hyperlink ref="D22" location="Mapa_profesionistas!A1" display="Mapa_profesionistas" xr:uid="{5A1A84B2-DAE1-424B-B87E-9D6B304D05B3}"/>
+    <hyperlink ref="D23" location="Mercado_laboral!A1" display="Mercado_laboral" xr:uid="{2CADCCA0-F103-4A01-B551-5DA32117A08A}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BFE6BEF7-23C5-43BE-9E48-D76A01D29EFB}">
-  <dimension ref="A1:C6"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B6EEAE0A-2582-4121-8CC4-83FE5CC4BA64}">
+  <dimension ref="A1:J11"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="21.44140625" customWidth="1"/>
+    <col min="1" max="1" width="5.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.88671875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="8.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A1" s="1"/>
-      <c r="B1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A2" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" s="3">
-        <v>0.61699999999999999</v>
-      </c>
-      <c r="C2" s="3">
-        <v>0.69499999999999995</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A3" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B3" s="3">
-        <f>1-B2-B4</f>
-        <v>0.38</v>
-      </c>
-      <c r="C3" s="3">
-        <f>1-C2-C4</f>
-        <v>0.30400000000000005</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" ht="72" x14ac:dyDescent="0.3">
-      <c r="A4" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="B4" s="3">
-        <v>3.0000000000000001E-3</v>
-      </c>
-      <c r="C4" s="3">
-        <v>1E-3</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A6" s="4"/>
+    <row r="1" spans="1:10" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A1" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B1" s="5"/>
+      <c r="C1" s="4"/>
+      <c r="D1" s="4"/>
+      <c r="E1" s="4"/>
+      <c r="F1" s="4"/>
+      <c r="G1" s="4"/>
+      <c r="H1" s="4"/>
+      <c r="I1" s="4"/>
+      <c r="J1" s="4"/>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A2" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="B2" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2" s="9" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A3" s="15">
+        <v>2003</v>
+      </c>
+      <c r="B3" s="16">
+        <v>400</v>
+      </c>
+      <c r="C3" s="16">
+        <v>385</v>
+      </c>
+      <c r="D3" s="17"/>
+      <c r="I3" s="13" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A4" s="23">
+        <v>2006</v>
+      </c>
+      <c r="B4" s="24">
+        <v>410</v>
+      </c>
+      <c r="C4" s="25">
+        <v>406</v>
+      </c>
+      <c r="D4" s="24">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A5" s="23">
+        <v>2009</v>
+      </c>
+      <c r="B5" s="24">
+        <v>425</v>
+      </c>
+      <c r="C5" s="25">
+        <v>419</v>
+      </c>
+      <c r="D5" s="24">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A6" s="23">
+        <v>2012</v>
+      </c>
+      <c r="B6" s="25">
+        <v>424</v>
+      </c>
+      <c r="C6" s="25">
+        <v>413</v>
+      </c>
+      <c r="D6" s="24">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A7" s="23">
+        <v>2015</v>
+      </c>
+      <c r="B7" s="25">
+        <v>423</v>
+      </c>
+      <c r="C7" s="25">
+        <v>408</v>
+      </c>
+      <c r="D7" s="24">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A8" s="23">
+        <v>2018</v>
+      </c>
+      <c r="B8" s="25">
+        <v>420</v>
+      </c>
+      <c r="C8" s="25">
+        <v>409</v>
+      </c>
+      <c r="D8" s="24">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A9" s="23">
+        <v>2022</v>
+      </c>
+      <c r="B9" s="24">
+        <v>415</v>
+      </c>
+      <c r="C9" s="25">
+        <v>395</v>
+      </c>
+      <c r="D9" s="24">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A11" s="26" t="s">
+        <v>34</v>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="I3" location="Portada!A1" display="regresar al incio" xr:uid="{F5128A3D-0F46-4601-980D-AF484F9088B6}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9EA24DC8-1518-42A8-9E88-4CF98C338C75}">
-  <dimension ref="A1:C11"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BFE6BEF7-23C5-43BE-9E48-D76A01D29EFB}">
+  <dimension ref="A1:J7"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="61.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21.44140625" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B1" t="s">
+    <row r="1" spans="1:10" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A1" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B1" s="5"/>
+      <c r="C1" s="4"/>
+      <c r="D1" s="4"/>
+      <c r="E1" s="4"/>
+      <c r="F1" s="4"/>
+      <c r="G1" s="4"/>
+      <c r="H1" s="4"/>
+      <c r="I1" s="4"/>
+      <c r="J1" s="4"/>
+    </row>
+    <row r="2" spans="1:10" s="8" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="B2" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>9</v>
-      </c>
-      <c r="B2" s="9">
-        <v>0.74959332986704297</v>
-      </c>
-      <c r="C2" s="9">
-        <v>0.25040667013295698</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>10</v>
-      </c>
-      <c r="B3" s="9">
-        <v>0.68625917369854761</v>
-      </c>
-      <c r="C3" s="9">
-        <v>0.31374082630145234</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>11</v>
-      </c>
-      <c r="B4" s="9">
-        <v>0.61433152163884885</v>
-      </c>
-      <c r="C4" s="9">
-        <v>0.38566847836115115</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>12</v>
-      </c>
-      <c r="B5" s="9">
-        <v>0.60315161505553594</v>
-      </c>
-      <c r="C5" s="9">
-        <v>0.39684838494446406</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
-        <v>13</v>
-      </c>
-      <c r="B6" s="9">
-        <v>0.57144837957021288</v>
-      </c>
-      <c r="C6" s="9">
-        <v>0.42855162042978717</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
-        <v>14</v>
-      </c>
-      <c r="B7" s="9">
-        <v>0.52060949624999298</v>
-      </c>
-      <c r="C7" s="9">
-        <v>0.47939050375000708</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
-        <v>15</v>
-      </c>
-      <c r="B8" s="9">
-        <v>0.49916076219302469</v>
-      </c>
-      <c r="C8" s="9">
-        <v>0.50083923780697526</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
-        <v>16</v>
-      </c>
-      <c r="B9" s="9">
-        <v>0.45070015574677408</v>
-      </c>
-      <c r="C9" s="9">
-        <v>0.54929984425322598</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
-        <v>17</v>
-      </c>
-      <c r="B10" s="9">
-        <v>0.31936942563769455</v>
-      </c>
-      <c r="C10" s="9">
-        <v>0.68063057436230545</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A11" t="s">
-        <v>18</v>
-      </c>
-      <c r="B11" s="9">
-        <v>0.24437125784754721</v>
-      </c>
-      <c r="C11" s="9">
-        <v>0.75562874215245279</v>
+      <c r="D2" s="7"/>
+      <c r="E2" s="7"/>
+      <c r="F2" s="7"/>
+      <c r="G2" s="7"/>
+      <c r="H2" s="7"/>
+      <c r="I2" s="13" t="s">
+        <v>44</v>
+      </c>
+      <c r="J2" s="7"/>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A3" s="21" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" s="22">
+        <v>0.61699999999999999</v>
+      </c>
+      <c r="C3" s="22">
+        <v>0.69499999999999995</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A4" s="21" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" s="22">
+        <f>1-B3-B5</f>
+        <v>0.38</v>
+      </c>
+      <c r="C4" s="22">
+        <f>1-C3-C5</f>
+        <v>0.30400000000000005</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A5" s="21" t="s">
+        <v>2</v>
+      </c>
+      <c r="B5" s="22">
+        <v>3.0000000000000001E-3</v>
+      </c>
+      <c r="C5" s="22">
+        <v>1E-3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A7" s="10" t="s">
+        <v>35</v>
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="I2" location="Portada!A1" display="regresar al incio" xr:uid="{38AB4ABD-B1CC-4438-BD6A-FA825BF6F375}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A8730AF1-D244-41D4-BD0A-5D7DE70CE7D1}">
-  <dimension ref="A1:D33"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9EA24DC8-1518-42A8-9E88-4CF98C338C75}">
+  <dimension ref="A1:J14"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="38.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="38.5546875" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
-        <v>20</v>
-      </c>
-      <c r="B1" t="s">
+    <row r="1" spans="1:10" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A1" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B1" s="5"/>
+      <c r="C1" s="4"/>
+      <c r="D1" s="4"/>
+      <c r="E1" s="4"/>
+      <c r="F1" s="4"/>
+      <c r="G1" s="4"/>
+      <c r="H1" s="4"/>
+      <c r="I1" s="4"/>
+      <c r="J1" s="4"/>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A2" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="I2" s="13" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3" s="2">
+        <v>0.74959332986704297</v>
+      </c>
+      <c r="C3" s="2">
+        <v>0.25040667013295698</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A4" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B4" s="2">
+        <v>0.68625917369854761</v>
+      </c>
+      <c r="C4" s="2">
+        <v>0.31374082630145234</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A5" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B5" s="2">
+        <v>0.61433152163884885</v>
+      </c>
+      <c r="C5" s="2">
+        <v>0.38566847836115115</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A6" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6" s="2">
+        <v>0.60315161505553594</v>
+      </c>
+      <c r="C6" s="2">
+        <v>0.39684838494446406</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A7" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B7" s="2">
+        <v>0.57144837957021288</v>
+      </c>
+      <c r="C7" s="2">
+        <v>0.42855162042978717</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A8" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B8" s="2">
+        <v>0.52060949624999298</v>
+      </c>
+      <c r="C8" s="2">
+        <v>0.47939050375000708</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A9" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="C1" t="s">
+      <c r="B9" s="2">
+        <v>0.49916076219302469</v>
+      </c>
+      <c r="C9" s="2">
+        <v>0.50083923780697526</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A10" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="D1" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A2" t="e" vm="1">
-        <v>#VALUE!</v>
-      </c>
-      <c r="B2">
-        <v>6151</v>
-      </c>
-      <c r="C2" s="10">
-        <v>39575</v>
-      </c>
-      <c r="D2" s="9">
-        <f>B2/C2</f>
-        <v>0.15542640555906506</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A3" t="e" vm="2">
-        <v>#VALUE!</v>
-      </c>
-      <c r="B3">
-        <v>14592</v>
-      </c>
-      <c r="C3" s="10">
-        <v>81780</v>
-      </c>
-      <c r="D3" s="9">
-        <f t="shared" ref="D3:D33" si="0">B3/C3</f>
-        <v>0.17842993396918563</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A4" t="e" vm="3">
-        <v>#VALUE!</v>
-      </c>
-      <c r="B4">
-        <v>2325</v>
-      </c>
-      <c r="C4" s="10">
-        <v>14812</v>
-      </c>
-      <c r="D4" s="9">
-        <f t="shared" si="0"/>
-        <v>0.1569673237915204</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A5" t="e" vm="4">
-        <v>#VALUE!</v>
-      </c>
-      <c r="B5">
-        <v>3689</v>
-      </c>
-      <c r="C5" s="10">
-        <v>28457</v>
-      </c>
-      <c r="D5" s="9">
-        <f t="shared" si="0"/>
-        <v>0.12963418491056683</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A6" t="e" vm="5">
-        <v>#VALUE!</v>
-      </c>
-      <c r="B6">
-        <v>9009</v>
-      </c>
-      <c r="C6" s="10">
-        <v>65503</v>
-      </c>
-      <c r="D6" s="9">
-        <f t="shared" si="0"/>
-        <v>0.13753568538845548</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A7" t="e" vm="6">
-        <v>#VALUE!</v>
-      </c>
-      <c r="B7">
-        <v>15183</v>
-      </c>
-      <c r="C7" s="10">
-        <v>79491</v>
-      </c>
-      <c r="D7" s="9">
-        <f t="shared" si="0"/>
-        <v>0.19100275502887118</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A8" t="e" vm="7">
-        <v>#VALUE!</v>
-      </c>
-      <c r="B8">
-        <v>83888</v>
-      </c>
-      <c r="C8" s="10">
-        <v>549998</v>
-      </c>
-      <c r="D8" s="9">
-        <f t="shared" si="0"/>
-        <v>0.15252419099705816</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A9" t="e" vm="8">
-        <v>#VALUE!</v>
-      </c>
-      <c r="B9">
-        <v>16095</v>
-      </c>
-      <c r="C9" s="10">
-        <v>77678</v>
-      </c>
-      <c r="D9" s="9">
-        <f t="shared" si="0"/>
-        <v>0.20720152424109786</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A10" t="e" vm="9">
-        <v>#VALUE!</v>
-      </c>
-      <c r="B10">
-        <v>2048</v>
-      </c>
-      <c r="C10" s="10">
-        <v>16678</v>
-      </c>
-      <c r="D10" s="9">
-        <f t="shared" si="0"/>
-        <v>0.12279649838110085</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A11" t="e" vm="10">
-        <v>#VALUE!</v>
-      </c>
-      <c r="B11">
-        <v>5911</v>
-      </c>
-      <c r="C11" s="10">
-        <v>35925</v>
-      </c>
-      <c r="D11" s="9">
-        <f t="shared" si="0"/>
-        <v>0.16453723034098816</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A12" t="e" vm="11">
-        <v>#VALUE!</v>
-      </c>
-      <c r="B12">
-        <v>23511</v>
-      </c>
-      <c r="C12" s="10">
-        <v>123896</v>
-      </c>
-      <c r="D12" s="9">
-        <f t="shared" si="0"/>
-        <v>0.18976399560922064</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A13" t="e" vm="12">
-        <v>#VALUE!</v>
-      </c>
-      <c r="B13">
-        <v>6191</v>
-      </c>
-      <c r="C13" s="10">
-        <v>46951</v>
-      </c>
-      <c r="D13" s="9">
-        <f t="shared" si="0"/>
-        <v>0.13186087623266809</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A14" t="e" vm="13">
-        <v>#VALUE!</v>
-      </c>
-      <c r="B14">
-        <v>13212</v>
-      </c>
-      <c r="C14" s="10">
-        <v>66166</v>
-      </c>
-      <c r="D14" s="9">
-        <f t="shared" si="0"/>
-        <v>0.19967959374905542</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A15" t="e" vm="14">
-        <v>#VALUE!</v>
-      </c>
-      <c r="B15">
-        <v>21887</v>
-      </c>
-      <c r="C15" s="10">
-        <v>173844</v>
-      </c>
-      <c r="D15" s="9">
-        <f t="shared" si="0"/>
-        <v>0.12590023239225973</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A16" t="e" vm="15">
-        <v>#VALUE!</v>
-      </c>
-      <c r="B16">
-        <v>47975</v>
-      </c>
-      <c r="C16" s="10">
-        <v>329508</v>
-      </c>
-      <c r="D16" s="9">
-        <f t="shared" si="0"/>
-        <v>0.14559585806717895</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A17" t="e" vm="16">
-        <v>#VALUE!</v>
-      </c>
-      <c r="B17">
-        <v>12829</v>
-      </c>
-      <c r="C17" s="10">
-        <v>76204</v>
-      </c>
-      <c r="D17" s="9">
-        <f t="shared" si="0"/>
-        <v>0.16835074274316308</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A18" t="e" vm="17">
-        <v>#VALUE!</v>
-      </c>
-      <c r="B18">
-        <v>7162</v>
-      </c>
-      <c r="C18" s="10">
-        <v>43606</v>
-      </c>
-      <c r="D18" s="9">
-        <f t="shared" si="0"/>
-        <v>0.16424345273586205</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A19" t="e" vm="18">
-        <v>#VALUE!</v>
-      </c>
-      <c r="B19">
-        <v>2386</v>
-      </c>
-      <c r="C19" s="10">
-        <v>29062</v>
-      </c>
-      <c r="D19" s="9">
-        <f t="shared" si="0"/>
-        <v>8.2100337210102542E-2</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A20" t="e" vm="19">
-        <v>#VALUE!</v>
-      </c>
-      <c r="B20">
-        <v>25489</v>
-      </c>
-      <c r="C20" s="10">
-        <v>165701</v>
-      </c>
-      <c r="D20" s="9">
-        <f t="shared" si="0"/>
-        <v>0.15382526357716611</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A21" t="e" vm="20">
-        <v>#VALUE!</v>
-      </c>
-      <c r="B21">
-        <v>7379</v>
-      </c>
-      <c r="C21" s="10">
-        <v>50808</v>
-      </c>
-      <c r="D21" s="9">
-        <f t="shared" si="0"/>
-        <v>0.14523303416784758</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A22" t="e" vm="21">
-        <v>#VALUE!</v>
-      </c>
-      <c r="B22">
-        <v>27590</v>
-      </c>
-      <c r="C22" s="10">
-        <v>198515</v>
-      </c>
-      <c r="D22" s="9">
-        <f t="shared" si="0"/>
-        <v>0.13898194091126614</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A23" t="e" vm="22">
-        <v>#VALUE!</v>
-      </c>
-      <c r="B23">
-        <v>11436</v>
-      </c>
-      <c r="C23" s="10">
-        <v>58780</v>
-      </c>
-      <c r="D23" s="9">
-        <f t="shared" si="0"/>
-        <v>0.19455597141884995</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A24" t="e" vm="23">
-        <v>#VALUE!</v>
-      </c>
-      <c r="B24">
-        <v>3204</v>
-      </c>
-      <c r="C24" s="10">
-        <v>30387</v>
-      </c>
-      <c r="D24" s="9">
-        <f t="shared" si="0"/>
-        <v>0.10543982624148485</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A25" t="e" vm="24">
-        <v>#VALUE!</v>
-      </c>
-      <c r="B25">
-        <v>11333</v>
-      </c>
-      <c r="C25" s="10">
-        <v>49513</v>
-      </c>
-      <c r="D25" s="9">
-        <f t="shared" si="0"/>
-        <v>0.22888938258639147</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A26" t="e" vm="25">
-        <v>#VALUE!</v>
-      </c>
-      <c r="B26">
-        <v>11280</v>
-      </c>
-      <c r="C26" s="10">
-        <v>95483</v>
-      </c>
-      <c r="D26" s="9">
-        <f t="shared" si="0"/>
-        <v>0.11813621272896746</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A27" t="e" vm="26">
-        <v>#VALUE!</v>
-      </c>
-      <c r="B27">
-        <v>13707</v>
-      </c>
-      <c r="C27" s="10">
-        <v>71190</v>
-      </c>
-      <c r="D27" s="9">
-        <f t="shared" si="0"/>
-        <v>0.19254108723135271</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A28" t="e" vm="27">
-        <v>#VALUE!</v>
-      </c>
-      <c r="B28">
-        <v>9924</v>
-      </c>
-      <c r="C28" s="10">
-        <v>55959</v>
-      </c>
-      <c r="D28" s="9">
-        <f t="shared" si="0"/>
-        <v>0.17734412695008847</v>
-      </c>
-    </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A29" t="e" vm="28">
-        <v>#VALUE!</v>
-      </c>
-      <c r="B29">
-        <v>12633</v>
-      </c>
-      <c r="C29" s="10">
-        <v>86772</v>
-      </c>
-      <c r="D29" s="9">
-        <f t="shared" si="0"/>
-        <v>0.14558843866685106</v>
-      </c>
-    </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A30" t="e" vm="29">
-        <v>#VALUE!</v>
-      </c>
-      <c r="B30">
-        <v>4127</v>
-      </c>
-      <c r="C30" s="10">
-        <v>23066</v>
-      </c>
-      <c r="D30" s="9">
-        <f t="shared" si="0"/>
-        <v>0.17892135610855806</v>
-      </c>
-    </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A31" t="e" vm="30">
-        <v>#VALUE!</v>
-      </c>
-      <c r="B31">
-        <v>27555</v>
-      </c>
-      <c r="C31" s="10">
-        <v>145256</v>
-      </c>
-      <c r="D31" s="9">
-        <f t="shared" si="0"/>
-        <v>0.18969956490609682</v>
-      </c>
-    </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A32" t="e" vm="31">
-        <v>#VALUE!</v>
-      </c>
-      <c r="B32">
-        <v>7638</v>
-      </c>
-      <c r="C32" s="10">
-        <v>48412</v>
-      </c>
-      <c r="D32" s="9">
-        <f t="shared" si="0"/>
-        <v>0.15777080062794349</v>
-      </c>
-    </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A33" t="e" vm="32">
-        <v>#VALUE!</v>
-      </c>
-      <c r="B33">
-        <v>5539</v>
-      </c>
-      <c r="C33" s="10">
-        <v>29638</v>
-      </c>
-      <c r="D33" s="9">
-        <f t="shared" si="0"/>
-        <v>0.18688845401174167</v>
+      <c r="B10" s="2">
+        <v>0.45070015574677408</v>
+      </c>
+      <c r="C10" s="2">
+        <v>0.54929984425322598</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A11" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B11" s="2">
+        <v>0.31936942563769455</v>
+      </c>
+      <c r="C11" s="2">
+        <v>0.68063057436230545</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A12" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B12" s="2">
+        <v>0.24437125784754721</v>
+      </c>
+      <c r="C12" s="2">
+        <v>0.75562874215245279</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A14" s="10" t="s">
+        <v>36</v>
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="I2" location="Portada!A1" display="regresar al incio" xr:uid="{1D0C3AF6-2F5A-4EEE-A037-EFFAE3BAA8C7}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7B4819FD-4228-4324-BCD5-74CF4BAEFFAF}">
-  <dimension ref="A1:D33"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A8730AF1-D244-41D4-BD0A-5D7DE70CE7D1}">
+  <dimension ref="A1:J37"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="18.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19.5546875" customWidth="1"/>
+    <col min="3" max="3" width="17.44140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="17" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.5546875" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
-        <v>20</v>
-      </c>
-      <c r="B1" t="s">
-        <v>32</v>
-      </c>
-      <c r="C1" t="s">
-        <v>27</v>
-      </c>
-      <c r="D1" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A2" t="e" vm="8">
+    <row r="1" spans="1:10" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A1" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="B1" s="5"/>
+      <c r="C1" s="4"/>
+      <c r="D1" s="4"/>
+      <c r="E1" s="4"/>
+      <c r="F1" s="4"/>
+      <c r="G1" s="4"/>
+      <c r="H1" s="4"/>
+      <c r="I1" s="4"/>
+      <c r="J1" s="4"/>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A2" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="B2" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="C2" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="D2" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="I2" s="13" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="e" vm="1">
         <v>#VALUE!</v>
       </c>
-      <c r="B2">
-        <v>248765</v>
-      </c>
-      <c r="C2">
-        <v>45476</v>
-      </c>
-      <c r="D2" s="9">
-        <v>0.18280706691053805</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A3" t="e" vm="22">
+      <c r="B3" s="3">
+        <v>6151</v>
+      </c>
+      <c r="C3" s="3">
+        <v>39575</v>
+      </c>
+      <c r="D3" s="2">
+        <f t="shared" ref="D3:D34" si="0">B3/C3</f>
+        <v>0.15542640555906506</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A4" s="1" t="e" vm="2">
         <v>#VALUE!</v>
       </c>
-      <c r="B3">
-        <v>215564</v>
-      </c>
-      <c r="C3">
-        <v>38034</v>
-      </c>
-      <c r="D3" s="9">
-        <v>0.17643947969048634</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A4" t="e" vm="19">
+      <c r="B4" s="3">
+        <v>14592</v>
+      </c>
+      <c r="C4" s="3">
+        <v>81780</v>
+      </c>
+      <c r="D4" s="2">
+        <f t="shared" si="0"/>
+        <v>0.17842993396918563</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A5" s="1" t="e" vm="3">
         <v>#VALUE!</v>
       </c>
-      <c r="B4">
-        <v>473109</v>
-      </c>
-      <c r="C4">
-        <v>81729</v>
-      </c>
-      <c r="D4" s="9">
-        <v>0.17274877459528354</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A5" t="e" vm="4">
+      <c r="B5" s="3">
+        <v>2325</v>
+      </c>
+      <c r="C5" s="3">
+        <v>14812</v>
+      </c>
+      <c r="D5" s="2">
+        <f t="shared" si="0"/>
+        <v>0.1569673237915204</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A6" s="1" t="e" vm="4">
         <v>#VALUE!</v>
       </c>
-      <c r="B5">
-        <v>66015</v>
-      </c>
-      <c r="C5">
-        <v>10467</v>
-      </c>
-      <c r="D5" s="9">
-        <v>0.15855487389229719</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A6" t="e" vm="27">
+      <c r="B6" s="3">
+        <v>3689</v>
+      </c>
+      <c r="C6" s="3">
+        <v>28457</v>
+      </c>
+      <c r="D6" s="2">
+        <f t="shared" si="0"/>
+        <v>0.12963418491056683</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A7" s="1" t="e" vm="5">
         <v>#VALUE!</v>
       </c>
-      <c r="B6">
-        <v>150940</v>
-      </c>
-      <c r="C6">
-        <v>23857</v>
-      </c>
-      <c r="D6" s="9">
-        <v>0.15805618126407844</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A7" t="e" vm="24">
+      <c r="B7" s="3">
+        <v>9009</v>
+      </c>
+      <c r="C7" s="3">
+        <v>65503</v>
+      </c>
+      <c r="D7" s="2">
+        <f t="shared" si="0"/>
+        <v>0.13753568538845548</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A8" s="1" t="e" vm="6">
         <v>#VALUE!</v>
       </c>
-      <c r="B7">
-        <v>179874</v>
-      </c>
-      <c r="C7">
-        <v>28232</v>
-      </c>
-      <c r="D7" s="9">
-        <v>0.15695431246316865</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A8" t="e" vm="28">
+      <c r="B8" s="3">
+        <v>15183</v>
+      </c>
+      <c r="C8" s="3">
+        <v>79491</v>
+      </c>
+      <c r="D8" s="2">
+        <f t="shared" si="0"/>
+        <v>0.19100275502887118</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A9" s="1" t="e" vm="7">
         <v>#VALUE!</v>
       </c>
-      <c r="B8">
-        <v>279097</v>
-      </c>
-      <c r="C8">
-        <v>43540</v>
-      </c>
-      <c r="D8" s="9">
-        <v>0.15600311002984626</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A9" t="e" vm="6">
+      <c r="B9" s="3">
+        <v>83888</v>
+      </c>
+      <c r="C9" s="3">
+        <v>549998</v>
+      </c>
+      <c r="D9" s="2">
+        <f t="shared" si="0"/>
+        <v>0.15252419099705816</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A10" s="1" t="e" vm="8">
         <v>#VALUE!</v>
       </c>
-      <c r="B9">
-        <v>260148</v>
-      </c>
-      <c r="C9">
-        <v>40344</v>
-      </c>
-      <c r="D9" s="9">
-        <v>0.15508095391853868</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A10" t="e" vm="10">
+      <c r="B10" s="3">
+        <v>16095</v>
+      </c>
+      <c r="C10" s="3">
+        <v>77678</v>
+      </c>
+      <c r="D10" s="2">
+        <f t="shared" si="0"/>
+        <v>0.20720152424109786</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A11" s="1" t="e" vm="9">
         <v>#VALUE!</v>
       </c>
-      <c r="B10">
-        <v>131589</v>
-      </c>
-      <c r="C10">
-        <v>20404</v>
-      </c>
-      <c r="D10" s="9">
-        <v>0.15505855352651057</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A11" t="e" vm="7">
+      <c r="B11" s="3">
+        <v>2048</v>
+      </c>
+      <c r="C11" s="3">
+        <v>16678</v>
+      </c>
+      <c r="D11" s="2">
+        <f t="shared" si="0"/>
+        <v>0.12279649838110085</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A12" s="1" t="e" vm="10">
         <v>#VALUE!</v>
       </c>
-      <c r="B11">
-        <v>1170969</v>
-      </c>
-      <c r="C11">
-        <v>171851</v>
-      </c>
-      <c r="D11" s="9">
-        <v>0.14675964948687797</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A12" t="e" vm="17">
+      <c r="B12" s="3">
+        <v>5911</v>
+      </c>
+      <c r="C12" s="3">
+        <v>35925</v>
+      </c>
+      <c r="D12" s="2">
+        <f t="shared" si="0"/>
+        <v>0.16453723034098816</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A13" s="1" t="e" vm="11">
         <v>#VALUE!</v>
       </c>
-      <c r="B12">
-        <v>142296</v>
-      </c>
-      <c r="C12">
-        <v>18800</v>
-      </c>
-      <c r="D12" s="9">
-        <v>0.13211896328779446</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A13" t="e" vm="23">
+      <c r="B13" s="3">
+        <v>6191</v>
+      </c>
+      <c r="C13" s="3">
+        <v>46951</v>
+      </c>
+      <c r="D13" s="2">
+        <f t="shared" si="0"/>
+        <v>0.13186087623266809</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A14" s="1" t="e" vm="12">
         <v>#VALUE!</v>
       </c>
-      <c r="B13">
-        <v>128260</v>
-      </c>
-      <c r="C13">
-        <v>16920</v>
-      </c>
-      <c r="D13" s="9">
-        <v>0.13191953843754872</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A14" t="e" vm="32">
+      <c r="B14" s="3">
+        <v>13212</v>
+      </c>
+      <c r="C14" s="3">
+        <v>66166</v>
+      </c>
+      <c r="D14" s="2">
+        <f t="shared" si="0"/>
+        <v>0.19967959374905542</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A15" s="1" t="e" vm="13">
         <v>#VALUE!</v>
       </c>
-      <c r="B14">
-        <v>97654</v>
-      </c>
-      <c r="C14">
-        <v>12648</v>
-      </c>
-      <c r="D14" s="9">
-        <v>0.12951850410633461</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A15" t="e" vm="1">
+      <c r="B15" s="3">
+        <v>27555</v>
+      </c>
+      <c r="C15" s="3">
+        <v>145256</v>
+      </c>
+      <c r="D15" s="2">
+        <f t="shared" si="0"/>
+        <v>0.18969956490609682</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A16" s="1" t="e" vm="14">
         <v>#VALUE!</v>
       </c>
-      <c r="B15">
-        <v>112118</v>
-      </c>
-      <c r="C15">
-        <v>14473</v>
-      </c>
-      <c r="D15" s="9">
-        <v>0.12908721168768619</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A16" t="e" vm="29">
+      <c r="B16" s="3">
+        <v>23511</v>
+      </c>
+      <c r="C16" s="3">
+        <v>123896</v>
+      </c>
+      <c r="D16" s="2">
+        <f t="shared" si="0"/>
+        <v>0.18976399560922064</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A17" s="1" t="e" vm="15">
         <v>#VALUE!</v>
       </c>
-      <c r="B16">
-        <v>86952</v>
-      </c>
-      <c r="C16">
-        <v>10802</v>
-      </c>
-      <c r="D16" s="9">
-        <v>0.12422945993191646</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A17" t="e" vm="30">
+      <c r="B17" s="3">
+        <v>21887</v>
+      </c>
+      <c r="C17" s="3">
+        <v>173844</v>
+      </c>
+      <c r="D17" s="2">
+        <f t="shared" si="0"/>
+        <v>0.12590023239225973</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A18" s="1" t="e" vm="16">
         <v>#VALUE!</v>
       </c>
-      <c r="B17">
-        <v>471138</v>
-      </c>
-      <c r="C17">
-        <v>58201</v>
-      </c>
-      <c r="D17" s="9">
-        <v>0.12353280779729081</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A18" t="e" vm="2">
+      <c r="B18" s="3">
+        <v>47975</v>
+      </c>
+      <c r="C18" s="3">
+        <v>329508</v>
+      </c>
+      <c r="D18" s="2">
+        <f t="shared" si="0"/>
+        <v>0.14559585806717895</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A19" s="1" t="e" vm="17">
         <v>#VALUE!</v>
       </c>
-      <c r="B18">
-        <v>239042</v>
-      </c>
-      <c r="C18">
-        <v>29278</v>
-      </c>
-      <c r="D18" s="9">
-        <v>0.12248056826833778</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A19" t="e" vm="26">
+      <c r="B19" s="3">
+        <v>12829</v>
+      </c>
+      <c r="C19" s="3">
+        <v>76204</v>
+      </c>
+      <c r="D19" s="2">
+        <f t="shared" si="0"/>
+        <v>0.16835074274316308</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A20" s="1" t="e" vm="18">
         <v>#VALUE!</v>
       </c>
-      <c r="B19">
-        <v>230707</v>
-      </c>
-      <c r="C19">
-        <v>28028</v>
-      </c>
-      <c r="D19" s="9">
-        <v>0.12148742777635703</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A20" t="e" vm="16">
+      <c r="B20" s="3">
+        <v>7162</v>
+      </c>
+      <c r="C20" s="3">
+        <v>43606</v>
+      </c>
+      <c r="D20" s="2">
+        <f t="shared" si="0"/>
+        <v>0.16424345273586205</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A21" s="1" t="e" vm="19">
         <v>#VALUE!</v>
       </c>
-      <c r="B20">
-        <v>272895</v>
-      </c>
-      <c r="C20">
-        <v>32690</v>
-      </c>
-      <c r="D20" s="9">
-        <v>0.11978966269077851</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A21" t="e" vm="3">
+      <c r="B21" s="3">
+        <v>2386</v>
+      </c>
+      <c r="C21" s="3">
+        <v>29062</v>
+      </c>
+      <c r="D21" s="2">
+        <f t="shared" si="0"/>
+        <v>8.2100337210102542E-2</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A22" s="1" t="e" vm="20">
         <v>#VALUE!</v>
       </c>
-      <c r="B21">
-        <v>58863</v>
-      </c>
-      <c r="C21">
-        <v>7004</v>
-      </c>
-      <c r="D21" s="9">
-        <v>0.11898815894534767</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A22" t="e" vm="31">
+      <c r="B22" s="3">
+        <v>25489</v>
+      </c>
+      <c r="C22" s="3">
+        <v>165701</v>
+      </c>
+      <c r="D22" s="2">
+        <f t="shared" si="0"/>
+        <v>0.15382526357716611</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A23" s="1" t="e" vm="21">
         <v>#VALUE!</v>
       </c>
-      <c r="B22">
-        <v>166078</v>
-      </c>
-      <c r="C22">
-        <v>19548</v>
-      </c>
-      <c r="D22" s="9">
-        <v>0.11770372957285131</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A23" t="e" vm="25">
+      <c r="B23" s="3">
+        <v>7379</v>
+      </c>
+      <c r="C23" s="3">
+        <v>50808</v>
+      </c>
+      <c r="D23" s="2">
+        <f t="shared" si="0"/>
+        <v>0.14523303416784758</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A24" s="1" t="e" vm="22">
         <v>#VALUE!</v>
       </c>
-      <c r="B23">
-        <v>252270</v>
-      </c>
-      <c r="C23">
-        <v>29617</v>
-      </c>
-      <c r="D23" s="9">
-        <v>0.11740198993142269</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A24" t="e" vm="14">
+      <c r="B24" s="3">
+        <v>27590</v>
+      </c>
+      <c r="C24" s="3">
+        <v>198515</v>
+      </c>
+      <c r="D24" s="2">
+        <f t="shared" si="0"/>
+        <v>0.13898194091126614</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A25" s="1" t="e" vm="23">
         <v>#VALUE!</v>
       </c>
-      <c r="B24">
-        <v>550428</v>
-      </c>
-      <c r="C24">
-        <v>64580</v>
-      </c>
-      <c r="D24" s="9">
-        <v>0.11732688017324699</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A25" t="e" vm="21">
+      <c r="B25" s="3">
+        <v>11436</v>
+      </c>
+      <c r="C25" s="3">
+        <v>58780</v>
+      </c>
+      <c r="D25" s="2">
+        <f t="shared" si="0"/>
+        <v>0.19455597141884995</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A26" s="1" t="e" vm="24">
         <v>#VALUE!</v>
       </c>
-      <c r="B25">
-        <v>428774</v>
-      </c>
-      <c r="C25">
-        <v>49447</v>
-      </c>
-      <c r="D25" s="9">
-        <v>0.11532182455092893</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A26" t="e" vm="15">
+      <c r="B26" s="3">
+        <v>3204</v>
+      </c>
+      <c r="C26" s="3">
+        <v>30387</v>
+      </c>
+      <c r="D26" s="2">
+        <f t="shared" si="0"/>
+        <v>0.10543982624148485</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A27" s="1" t="e" vm="25">
         <v>#VALUE!</v>
       </c>
-      <c r="B26">
-        <v>1298652</v>
-      </c>
-      <c r="C26">
-        <v>149003</v>
-      </c>
-      <c r="D26" s="9">
-        <v>0.11473666540381873</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A27" t="e" vm="20">
+      <c r="B27" s="3">
+        <v>11333</v>
+      </c>
+      <c r="C27" s="3">
+        <v>49513</v>
+      </c>
+      <c r="D27" s="2">
+        <f t="shared" si="0"/>
+        <v>0.22888938258639147</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A28" s="1" t="e" vm="26">
         <v>#VALUE!</v>
       </c>
-      <c r="B27">
-        <v>189665</v>
-      </c>
-      <c r="C27">
-        <v>21593</v>
-      </c>
-      <c r="D27" s="9">
-        <v>0.11384810059842354</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A28" t="e" vm="13">
+      <c r="B28" s="3">
+        <v>11280</v>
+      </c>
+      <c r="C28" s="3">
+        <v>95483</v>
+      </c>
+      <c r="D28" s="2">
+        <f t="shared" si="0"/>
+        <v>0.11813621272896746</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A29" s="1" t="e" vm="27">
         <v>#VALUE!</v>
       </c>
-      <c r="B28">
-        <v>172802</v>
-      </c>
-      <c r="C28">
-        <v>19640</v>
-      </c>
-      <c r="D28" s="9">
-        <v>0.11365609194338029</v>
-      </c>
-    </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A29" t="e" vm="11">
+      <c r="B29" s="3">
+        <v>13707</v>
+      </c>
+      <c r="C29" s="3">
+        <v>71190</v>
+      </c>
+      <c r="D29" s="2">
+        <f t="shared" si="0"/>
+        <v>0.19254108723135271</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A30" s="1" t="e" vm="28">
         <v>#VALUE!</v>
       </c>
-      <c r="B29">
-        <v>356523</v>
-      </c>
-      <c r="C29">
-        <v>37491</v>
-      </c>
-      <c r="D29" s="9">
-        <v>0.10515731102902197</v>
-      </c>
-    </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A30" t="e" vm="12">
+      <c r="B30" s="3">
+        <v>9924</v>
+      </c>
+      <c r="C30" s="3">
+        <v>55959</v>
+      </c>
+      <c r="D30" s="2">
+        <f t="shared" si="0"/>
+        <v>0.17734412695008847</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A31" s="1" t="e" vm="29">
         <v>#VALUE!</v>
       </c>
-      <c r="B30">
-        <v>177857</v>
-      </c>
-      <c r="C30">
-        <v>18028</v>
-      </c>
-      <c r="D30" s="9">
-        <v>0.10136233041151037</v>
-      </c>
-    </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A31" t="e" vm="5">
+      <c r="B31" s="3">
+        <v>12633</v>
+      </c>
+      <c r="C31" s="3">
+        <v>86772</v>
+      </c>
+      <c r="D31" s="2">
+        <f t="shared" si="0"/>
+        <v>0.14558843866685106</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A32" s="1" t="e" vm="30">
         <v>#VALUE!</v>
       </c>
-      <c r="B31">
-        <v>252269</v>
-      </c>
-      <c r="C31">
-        <v>24062</v>
-      </c>
-      <c r="D31" s="9">
-        <v>9.5382310153050903E-2</v>
-      </c>
-    </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A32" t="e" vm="18">
+      <c r="B32" s="3">
+        <v>4127</v>
+      </c>
+      <c r="C32" s="3">
+        <v>23066</v>
+      </c>
+      <c r="D32" s="2">
+        <f t="shared" si="0"/>
+        <v>0.17892135610855806</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A33" s="1" t="e" vm="31">
         <v>#VALUE!</v>
       </c>
-      <c r="B32">
-        <v>91255</v>
-      </c>
-      <c r="C32">
-        <v>7813</v>
-      </c>
-      <c r="D32" s="9">
-        <v>8.5617226453345019E-2</v>
-      </c>
-    </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A33" t="e" vm="9">
+      <c r="B33" s="3">
+        <v>7638</v>
+      </c>
+      <c r="C33" s="3">
+        <v>48412</v>
+      </c>
+      <c r="D33" s="2">
+        <f t="shared" si="0"/>
+        <v>0.15777080062794349</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A34" s="1" t="e" vm="32">
         <v>#VALUE!</v>
       </c>
-      <c r="B33">
-        <v>58411</v>
-      </c>
-      <c r="C33">
-        <v>4919</v>
-      </c>
-      <c r="D33" s="9">
-        <v>8.4213589906010855E-2</v>
+      <c r="B34" s="3">
+        <v>5539</v>
+      </c>
+      <c r="C34" s="3">
+        <v>29638</v>
+      </c>
+      <c r="D34" s="2">
+        <f t="shared" si="0"/>
+        <v>0.18688845401174167</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B37" s="11" t="s">
+        <v>36</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D33" xr:uid="{7B4819FD-4228-4324-BCD5-74CF4BAEFFAF}"/>
+  <hyperlinks>
+    <hyperlink ref="I2" location="Portada!A1" display="regresar al incio" xr:uid="{3D9A03F6-F4E0-4C37-AC2D-4BA32CD936EF}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7B4819FD-4228-4324-BCD5-74CF4BAEFFAF}">
+  <dimension ref="A1:J37"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="18.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="21.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="21.6640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A1" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="B1" s="5"/>
+      <c r="C1" s="4"/>
+      <c r="D1" s="4"/>
+      <c r="E1" s="4"/>
+      <c r="F1" s="4"/>
+      <c r="G1" s="4"/>
+      <c r="H1" s="4"/>
+      <c r="I1" s="4"/>
+      <c r="J1" s="4"/>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A2" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="B2" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="D2" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="I2" s="13" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="e" vm="1">
+        <v>#VALUE!</v>
+      </c>
+      <c r="B3" s="3">
+        <v>14473</v>
+      </c>
+      <c r="C3" s="3">
+        <v>112118</v>
+      </c>
+      <c r="D3" s="2">
+        <f t="shared" ref="D3:D34" si="0">B3/C3</f>
+        <v>0.12908721168768619</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A4" s="1" t="e" vm="2">
+        <v>#VALUE!</v>
+      </c>
+      <c r="B4" s="3">
+        <v>29278</v>
+      </c>
+      <c r="C4" s="3">
+        <v>239042</v>
+      </c>
+      <c r="D4" s="2">
+        <f t="shared" si="0"/>
+        <v>0.12248056826833778</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A5" s="1" t="e" vm="3">
+        <v>#VALUE!</v>
+      </c>
+      <c r="B5" s="3">
+        <v>7004</v>
+      </c>
+      <c r="C5" s="3">
+        <v>58863</v>
+      </c>
+      <c r="D5" s="2">
+        <f t="shared" si="0"/>
+        <v>0.11898815894534767</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A6" s="1" t="e" vm="4">
+        <v>#VALUE!</v>
+      </c>
+      <c r="B6" s="3">
+        <v>10467</v>
+      </c>
+      <c r="C6" s="3">
+        <v>66015</v>
+      </c>
+      <c r="D6" s="2">
+        <f t="shared" si="0"/>
+        <v>0.15855487389229719</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A7" s="1" t="e" vm="5">
+        <v>#VALUE!</v>
+      </c>
+      <c r="B7" s="3">
+        <v>24062</v>
+      </c>
+      <c r="C7" s="3">
+        <v>252269</v>
+      </c>
+      <c r="D7" s="2">
+        <f t="shared" si="0"/>
+        <v>9.5382310153050903E-2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A8" s="1" t="e" vm="6">
+        <v>#VALUE!</v>
+      </c>
+      <c r="B8" s="3">
+        <v>40344</v>
+      </c>
+      <c r="C8" s="3">
+        <v>260148</v>
+      </c>
+      <c r="D8" s="2">
+        <f t="shared" si="0"/>
+        <v>0.15508095391853868</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A9" s="1" t="e" vm="7">
+        <v>#VALUE!</v>
+      </c>
+      <c r="B9" s="3">
+        <v>171851</v>
+      </c>
+      <c r="C9" s="3">
+        <v>1170969</v>
+      </c>
+      <c r="D9" s="2">
+        <f t="shared" si="0"/>
+        <v>0.14675964948687797</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A10" s="1" t="e" vm="8">
+        <v>#VALUE!</v>
+      </c>
+      <c r="B10" s="3">
+        <v>45476</v>
+      </c>
+      <c r="C10" s="3">
+        <v>248765</v>
+      </c>
+      <c r="D10" s="2">
+        <f t="shared" si="0"/>
+        <v>0.18280706691053805</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A11" s="1" t="e" vm="9">
+        <v>#VALUE!</v>
+      </c>
+      <c r="B11" s="3">
+        <v>4919</v>
+      </c>
+      <c r="C11" s="3">
+        <v>58411</v>
+      </c>
+      <c r="D11" s="2">
+        <f t="shared" si="0"/>
+        <v>8.4213589906010855E-2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A12" s="1" t="e" vm="10">
+        <v>#VALUE!</v>
+      </c>
+      <c r="B12" s="3">
+        <v>20404</v>
+      </c>
+      <c r="C12" s="3">
+        <v>131589</v>
+      </c>
+      <c r="D12" s="2">
+        <f t="shared" si="0"/>
+        <v>0.15505855352651057</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A13" s="1" t="e" vm="11">
+        <v>#VALUE!</v>
+      </c>
+      <c r="B13" s="3">
+        <v>18028</v>
+      </c>
+      <c r="C13" s="3">
+        <v>177857</v>
+      </c>
+      <c r="D13" s="2">
+        <f t="shared" si="0"/>
+        <v>0.10136233041151037</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A14" s="1" t="e" vm="12">
+        <v>#VALUE!</v>
+      </c>
+      <c r="B14" s="3">
+        <v>19640</v>
+      </c>
+      <c r="C14" s="3">
+        <v>172802</v>
+      </c>
+      <c r="D14" s="2">
+        <f t="shared" si="0"/>
+        <v>0.11365609194338029</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A15" s="1" t="e" vm="13">
+        <v>#VALUE!</v>
+      </c>
+      <c r="B15" s="3">
+        <v>58201</v>
+      </c>
+      <c r="C15" s="3">
+        <v>471138</v>
+      </c>
+      <c r="D15" s="2">
+        <f t="shared" si="0"/>
+        <v>0.12353280779729081</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A16" s="1" t="e" vm="14">
+        <v>#VALUE!</v>
+      </c>
+      <c r="B16" s="3">
+        <v>37491</v>
+      </c>
+      <c r="C16" s="3">
+        <v>356523</v>
+      </c>
+      <c r="D16" s="2">
+        <f t="shared" si="0"/>
+        <v>0.10515731102902197</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A17" s="1" t="e" vm="15">
+        <v>#VALUE!</v>
+      </c>
+      <c r="B17" s="3">
+        <v>64580</v>
+      </c>
+      <c r="C17" s="3">
+        <v>550428</v>
+      </c>
+      <c r="D17" s="2">
+        <f t="shared" si="0"/>
+        <v>0.11732688017324699</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A18" s="1" t="e" vm="16">
+        <v>#VALUE!</v>
+      </c>
+      <c r="B18" s="3">
+        <v>149003</v>
+      </c>
+      <c r="C18" s="3">
+        <v>1298652</v>
+      </c>
+      <c r="D18" s="2">
+        <f t="shared" si="0"/>
+        <v>0.11473666540381873</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A19" s="1" t="e" vm="17">
+        <v>#VALUE!</v>
+      </c>
+      <c r="B19" s="3">
+        <v>32690</v>
+      </c>
+      <c r="C19" s="3">
+        <v>272895</v>
+      </c>
+      <c r="D19" s="2">
+        <f t="shared" si="0"/>
+        <v>0.11978966269077851</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A20" s="1" t="e" vm="18">
+        <v>#VALUE!</v>
+      </c>
+      <c r="B20" s="3">
+        <v>18800</v>
+      </c>
+      <c r="C20" s="3">
+        <v>142296</v>
+      </c>
+      <c r="D20" s="2">
+        <f t="shared" si="0"/>
+        <v>0.13211896328779446</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A21" s="1" t="e" vm="19">
+        <v>#VALUE!</v>
+      </c>
+      <c r="B21" s="3">
+        <v>7813</v>
+      </c>
+      <c r="C21" s="3">
+        <v>91255</v>
+      </c>
+      <c r="D21" s="2">
+        <f t="shared" si="0"/>
+        <v>8.5617226453345019E-2</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A22" s="1" t="e" vm="20">
+        <v>#VALUE!</v>
+      </c>
+      <c r="B22" s="3">
+        <v>81729</v>
+      </c>
+      <c r="C22" s="3">
+        <v>473109</v>
+      </c>
+      <c r="D22" s="2">
+        <f t="shared" si="0"/>
+        <v>0.17274877459528354</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A23" s="1" t="e" vm="21">
+        <v>#VALUE!</v>
+      </c>
+      <c r="B23" s="3">
+        <v>21593</v>
+      </c>
+      <c r="C23" s="3">
+        <v>189665</v>
+      </c>
+      <c r="D23" s="2">
+        <f t="shared" si="0"/>
+        <v>0.11384810059842354</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A24" s="1" t="e" vm="22">
+        <v>#VALUE!</v>
+      </c>
+      <c r="B24" s="3">
+        <v>49447</v>
+      </c>
+      <c r="C24" s="3">
+        <v>428774</v>
+      </c>
+      <c r="D24" s="2">
+        <f t="shared" si="0"/>
+        <v>0.11532182455092893</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A25" s="1" t="e" vm="23">
+        <v>#VALUE!</v>
+      </c>
+      <c r="B25" s="3">
+        <v>38034</v>
+      </c>
+      <c r="C25" s="3">
+        <v>215564</v>
+      </c>
+      <c r="D25" s="2">
+        <f t="shared" si="0"/>
+        <v>0.17643947969048634</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A26" s="1" t="e" vm="24">
+        <v>#VALUE!</v>
+      </c>
+      <c r="B26" s="3">
+        <v>16920</v>
+      </c>
+      <c r="C26" s="3">
+        <v>128260</v>
+      </c>
+      <c r="D26" s="2">
+        <f t="shared" si="0"/>
+        <v>0.13191953843754872</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A27" s="1" t="e" vm="25">
+        <v>#VALUE!</v>
+      </c>
+      <c r="B27" s="3">
+        <v>28232</v>
+      </c>
+      <c r="C27" s="3">
+        <v>179874</v>
+      </c>
+      <c r="D27" s="2">
+        <f t="shared" si="0"/>
+        <v>0.15695431246316865</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A28" s="1" t="e" vm="26">
+        <v>#VALUE!</v>
+      </c>
+      <c r="B28" s="3">
+        <v>29617</v>
+      </c>
+      <c r="C28" s="3">
+        <v>252270</v>
+      </c>
+      <c r="D28" s="2">
+        <f t="shared" si="0"/>
+        <v>0.11740198993142269</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A29" s="1" t="e" vm="27">
+        <v>#VALUE!</v>
+      </c>
+      <c r="B29" s="3">
+        <v>28028</v>
+      </c>
+      <c r="C29" s="3">
+        <v>230707</v>
+      </c>
+      <c r="D29" s="2">
+        <f t="shared" si="0"/>
+        <v>0.12148742777635703</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A30" s="1" t="e" vm="28">
+        <v>#VALUE!</v>
+      </c>
+      <c r="B30" s="3">
+        <v>23857</v>
+      </c>
+      <c r="C30" s="3">
+        <v>150940</v>
+      </c>
+      <c r="D30" s="2">
+        <f t="shared" si="0"/>
+        <v>0.15805618126407844</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A31" s="1" t="e" vm="29">
+        <v>#VALUE!</v>
+      </c>
+      <c r="B31" s="3">
+        <v>43540</v>
+      </c>
+      <c r="C31" s="3">
+        <v>279097</v>
+      </c>
+      <c r="D31" s="2">
+        <f t="shared" si="0"/>
+        <v>0.15600311002984626</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A32" s="1" t="e" vm="30">
+        <v>#VALUE!</v>
+      </c>
+      <c r="B32" s="3">
+        <v>10802</v>
+      </c>
+      <c r="C32" s="3">
+        <v>86952</v>
+      </c>
+      <c r="D32" s="2">
+        <f t="shared" si="0"/>
+        <v>0.12422945993191646</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A33" s="1" t="e" vm="31">
+        <v>#VALUE!</v>
+      </c>
+      <c r="B33" s="3">
+        <v>19548</v>
+      </c>
+      <c r="C33" s="3">
+        <v>166078</v>
+      </c>
+      <c r="D33" s="2">
+        <f t="shared" si="0"/>
+        <v>0.11770372957285131</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A34" s="1" t="e" vm="32">
+        <v>#VALUE!</v>
+      </c>
+      <c r="B34" s="3">
+        <v>12648</v>
+      </c>
+      <c r="C34" s="3">
+        <v>97654</v>
+      </c>
+      <c r="D34" s="2">
+        <f t="shared" si="0"/>
+        <v>0.12951850410633461</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B37" s="10" t="s">
+        <v>37</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="I2" location="Portada!A1" display="regresar al incio" xr:uid="{00103B82-1992-418A-9B55-9AB595CC5195}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ED2ED3F3-562A-4AFF-8AAA-762EA32CAE47}">
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:J7"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="17.21875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="31.21875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.6640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="13.33203125" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
-        <v>23</v>
-      </c>
-      <c r="B1" t="s">
-        <v>24</v>
-      </c>
-      <c r="C1" t="s">
-        <v>25</v>
-      </c>
-      <c r="D1" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>27</v>
-      </c>
-      <c r="B2" s="9">
+    <row r="1" spans="1:10" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A1" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="B1" s="5"/>
+      <c r="C1" s="4"/>
+      <c r="D1" s="4"/>
+      <c r="E1" s="4"/>
+      <c r="F1" s="4"/>
+      <c r="G1" s="4"/>
+      <c r="H1" s="4"/>
+      <c r="I1" s="4"/>
+      <c r="J1" s="4"/>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A2" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="B2" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="C2" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="D2" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="I2" s="13" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B3" s="2">
         <v>0.74</v>
       </c>
-      <c r="C2" s="9">
+      <c r="C3" s="2">
         <v>0.77</v>
       </c>
-      <c r="D2" s="9">
+      <c r="D3" s="2">
         <v>0.15</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A4" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B4" s="2">
+        <v>0.7</v>
+      </c>
+      <c r="C4" s="2">
+        <v>0.74</v>
+      </c>
+      <c r="D4" s="2">
+        <v>0.18</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A5" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="B3" s="9">
-        <v>0.7</v>
-      </c>
-      <c r="C3" s="9">
-        <v>0.74</v>
-      </c>
-      <c r="D3" s="9">
-        <v>0.18</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>28</v>
-      </c>
-      <c r="B4" s="9">
+      <c r="B5" s="2">
         <v>0.46</v>
       </c>
-      <c r="C4" s="9">
+      <c r="C5" s="2">
         <v>0.44</v>
       </c>
-      <c r="D4" s="9">
+      <c r="D5" s="2">
         <v>0.14000000000000001</v>
       </c>
     </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A7" s="10" t="s">
+        <v>37</v>
+      </c>
+    </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="I2" location="Portada!A1" display="regresar al incio" xr:uid="{E4DB5263-0BD9-4BD7-86B7-2DCDC83C724F}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>